--- a/epepep_structure.xlsx
+++ b/epepep_structure.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D253D9-CE5E-4BAF-8665-1B0AA6385EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Word" sheetId="2" r:id="rId1"/>

--- a/epepep_structure.xlsx
+++ b/epepep_structure.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\annwa\OneDrive\Desktop\Workspace\epepep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D253D9-CE5E-4BAF-8665-1B0AA6385EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F87FBE7-17B2-4CDC-A447-94E6A3290433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Word" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="795">
   <si>
     <t>Unit</t>
   </si>
@@ -1466,9 +1466,6 @@
     <t>sei3 wai4</t>
   </si>
   <si>
-    <t>個案|照顧|聖誕|貢獻|更加|降低|背景|禁止|鏡頭|四圍|觀眾|關注|酒店|廣吿|投訴|門票</t>
-  </si>
-  <si>
     <t>大</t>
   </si>
   <si>
@@ -1815,9 +1812,6 @@
   </si>
   <si>
     <t>mou4 haan6</t>
-  </si>
-  <si>
-    <t>運動|任務|混亂|誤會|健康|第三|代表|系統|甚至|受到|例如|調查|關係|經驗|改善|總共|透露|訓練|成立|無限|</t>
   </si>
   <si>
     <t>Colour_colour</t>
@@ -1851,9 +1845,6 @@
     <t>他他提工工工工完工他完半半工他完提他制制半制他他提制半半制半半他工他工工講工提工工提他他講工提工工完工講講完工他工他他工他完工他</t>
   </si>
   <si>
-    <t>#e0e0e0,#808080,#9900ff,#ffffff</t>
-  </si>
-  <si>
     <t>#D5FDFF,#a4c2f4,#93E8FF,#1155cc,,#FFF4D1</t>
   </si>
   <si>
@@ -1896,9 +1887,6 @@
     <t>maa5</t>
   </si>
   <si>
-    <t>網</t>
-  </si>
-  <si>
     <t>mong5</t>
   </si>
   <si>
@@ -1941,12 +1929,6 @@
     <t>jan5</t>
   </si>
   <si>
-    <t>米</t>
-  </si>
-  <si>
-    <t>mai5</t>
-  </si>
-  <si>
     <t>遠</t>
   </si>
   <si>
@@ -1996,9 +1978,6 @@
   </si>
   <si>
     <t>勇</t>
-  </si>
-  <si>
-    <t>jung5</t>
   </si>
   <si>
     <t>染</t>
@@ -2058,9 +2037,6 @@
 第六調: #FFFFFF</t>
   </si>
   <si>
-    <t>奶!眼米</t>
-  </si>
-  <si>
     <t>螞蟻</t>
   </si>
   <si>
@@ -2070,9 +2046,6 @@
     <t>武</t>
   </si>
   <si>
-    <t>美理晚武也每引遠滿朗</t>
-  </si>
-  <si>
     <t>母語</t>
   </si>
   <si>
@@ -2094,9 +2067,6 @@
     <t>maa5 mei5</t>
   </si>
   <si>
-    <t>勇何染第件笑權</t>
-  </si>
-  <si>
     <t>領先</t>
   </si>
   <si>
@@ -2224,9 +2194,6 @@
   </si>
   <si>
     <t>!神免署永</t>
-  </si>
-  <si>
-    <t>勇勇勇勇勇染染染染染何何何權勇染勇權件笑笑第何染權第件笑笑件件權染權第笑笑第何勇勇勇何權權何染染染染勇勇勇勇染染勇染染染勇勇勇勇</t>
   </si>
   <si>
     <t>,,#864300,#525252,#FFF3E2,#FFFFFF</t>
@@ -2263,18 +2230,12 @@
     <t>miu5</t>
   </si>
   <si>
-    <t>秒我你腦買碼網與</t>
-  </si>
-  <si>
     <t>魯莽</t>
   </si>
   <si>
     <t>lou5 mong5</t>
   </si>
   <si>
-    <t>螞蟻|母語|魯莽|馬尾|領先|野豬|了解|敏感|挽救|軟化|儲存|偶然|冷淡|偉大|温暖|風雨|展覽|小鳥|快艇|器皿|行李|牛腩|伴舞|廟宇</t>
-  </si>
-  <si>
     <t>萬萬望望望萬萬望望投望望萬萬萬望聯投聯萬望望望投投瀉聯聯萬萬聯聯案瀉案投投投投案瀉品案瀉聯聯瀉品品班品案瀉瀉品品班班班品品品班班</t>
   </si>
   <si>
@@ -2294,6 +2255,192 @@
   </si>
   <si>
     <t>廣東話的第五調是低升調，調值為23。通常對應普通話第三聲（較多）､第四聲（較少）。</t>
+  </si>
+  <si>
+    <t>#e0e0e0,#808080,#9900ff,#ffffff,,</t>
+  </si>
+  <si>
+    <t>抗爭</t>
+  </si>
+  <si>
+    <t>kong3 zang1</t>
+  </si>
+  <si>
+    <t>破產</t>
+  </si>
+  <si>
+    <t>po3 caan2</t>
+  </si>
+  <si>
+    <t>肺炎</t>
+  </si>
+  <si>
+    <t>fai3 jim4</t>
+  </si>
+  <si>
+    <t>機構</t>
+  </si>
+  <si>
+    <t>gei1 kau3</t>
+  </si>
+  <si>
+    <t>口罩</t>
+  </si>
+  <si>
+    <t>hau2 zaau3</t>
+  </si>
+  <si>
+    <t>人數</t>
+  </si>
+  <si>
+    <t>jan4 sou3</t>
+  </si>
+  <si>
+    <t>個案|照顧|聖誕|貢獻|抗爭|更加|降低|背景|破產|禁止|鏡頭|四圍|肺炎|觀眾|機構|關注|酒店|廣吿|口罩|投訴|門票|人數</t>
+  </si>
+  <si>
+    <t>罷工</t>
+  </si>
+  <si>
+    <t>baa6 gung1</t>
+  </si>
+  <si>
+    <t>效果</t>
+  </si>
+  <si>
+    <t>haau6 gwo2</t>
+  </si>
+  <si>
+    <t>預計</t>
+  </si>
+  <si>
+    <t>jyu6 gai3</t>
+  </si>
+  <si>
+    <t>病人</t>
+  </si>
+  <si>
+    <t>beng6 jan4</t>
+  </si>
+  <si>
+    <t>方便</t>
+  </si>
+  <si>
+    <t>fong1 bin6</t>
+  </si>
+  <si>
+    <t>口號</t>
+  </si>
+  <si>
+    <t>hau2 hou6</t>
+  </si>
+  <si>
+    <t>破壞</t>
+  </si>
+  <si>
+    <t>po3 waai6</t>
+  </si>
+  <si>
+    <t>旗下</t>
+  </si>
+  <si>
+    <t>kei4 haa6</t>
+  </si>
+  <si>
+    <t>運動|任務|混亂|誤會|健康|第三|罷工|效果|代表|系統|甚至|受到|預計|病人|例如|調查|關係|方便|經驗|口號|改善|總共|透露|訓練|破壞|旗下|成立|無限|</t>
+  </si>
+  <si>
+    <t>有些</t>
+  </si>
+  <si>
+    <t>jau5 se1</t>
+  </si>
+  <si>
+    <t>妥</t>
+  </si>
+  <si>
+    <t>to5</t>
+  </si>
+  <si>
+    <t>勇敢</t>
+  </si>
+  <si>
+    <t>jung5 gam2</t>
+  </si>
+  <si>
+    <t>妥何染第件笑權</t>
+  </si>
+  <si>
+    <t>妥妥妥妥妥染染染染染何何何權妥染妥權件笑笑第何染權第件笑笑件件權染權第笑笑第何妥妥妥何權權何染染染染妥妥妥妥染染妥染染染妥妥妥妥</t>
+  </si>
+  <si>
+    <t>猛獸</t>
+  </si>
+  <si>
+    <t>maang5 sau3</t>
+  </si>
+  <si>
+    <t>友情</t>
+  </si>
+  <si>
+    <t>jau5 cing4</t>
+  </si>
+  <si>
+    <t>網站</t>
+  </si>
+  <si>
+    <t>mong5 zaam6</t>
+  </si>
+  <si>
+    <t>惘</t>
+  </si>
+  <si>
+    <t>秒我你腦買碼惘與</t>
+  </si>
+  <si>
+    <t>優雅</t>
+  </si>
+  <si>
+    <t>jau1 ngaa5</t>
+  </si>
+  <si>
+    <t>口吻</t>
+  </si>
+  <si>
+    <t>hau2 man5</t>
+  </si>
+  <si>
+    <t>過癮</t>
+  </si>
+  <si>
+    <t>gwo3 jan5</t>
+  </si>
+  <si>
+    <t>煩惱</t>
+  </si>
+  <si>
+    <t>faan4 nou5</t>
+  </si>
+  <si>
+    <t>糯米</t>
+  </si>
+  <si>
+    <t>no6 mai5</t>
+  </si>
+  <si>
+    <t>懶</t>
+  </si>
+  <si>
+    <t>laan5</t>
+  </si>
+  <si>
+    <t>奶!眼美</t>
+  </si>
+  <si>
+    <t>懶理晚武也每引遠滿朗</t>
+  </si>
+  <si>
+    <t>螞蟻|母語|魯莽|馬尾|領先|野豬|有些|勇敢|了解|敏感|挽救|軟化|猛獸|友情|儲存|偶然|冷淡|偉大|網站|優雅|温暖|風雨|展覽|小鳥|口吻|過癮|快艇|器皿|行李|牛腩|煩惱|糯米|伴舞|廟宇</t>
   </si>
 </sst>
 </file>
@@ -2685,7 +2832,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2978,6 +3125,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3231,10 +3381,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C995"/>
+  <dimension ref="A1:C1008"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="12.59765625" style="49" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="104" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" style="49" customWidth="1"/>
     <col min="3" max="3" width="12.59765625" style="50" customWidth="1"/>
     <col min="4" max="6" width="12.59765625" customWidth="1"/>
   </cols>
@@ -4872,7 +5023,7 @@
         <v>3</v>
       </c>
       <c r="B149" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="C149" t="s">
         <v>341</v>
@@ -5166,68 +5317,68 @@
     </row>
     <row r="176" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B176" t="s">
-        <v>474</v>
+        <v>734</v>
       </c>
       <c r="C176" t="s">
-        <v>475</v>
+        <v>735</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B177" t="s">
-        <v>476</v>
+        <v>736</v>
       </c>
       <c r="C177" t="s">
-        <v>477</v>
+        <v>737</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B178" t="s">
-        <v>478</v>
+        <v>738</v>
       </c>
       <c r="C178" t="s">
-        <v>479</v>
+        <v>739</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B179" t="s">
-        <v>480</v>
+        <v>740</v>
       </c>
       <c r="C179" t="s">
-        <v>481</v>
+        <v>741</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B180" t="s">
-        <v>482</v>
+        <v>742</v>
       </c>
       <c r="C180" t="s">
-        <v>483</v>
+        <v>743</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B181" t="s">
-        <v>484</v>
+        <v>744</v>
       </c>
       <c r="C181" t="s">
-        <v>485</v>
+        <v>745</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5235,10 +5386,10 @@
         <v>4</v>
       </c>
       <c r="B182" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="C182" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5246,10 +5397,10 @@
         <v>4</v>
       </c>
       <c r="B183" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="C183" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5257,10 +5408,10 @@
         <v>4</v>
       </c>
       <c r="B184" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="C184" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5268,10 +5419,10 @@
         <v>4</v>
       </c>
       <c r="B185" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="C185" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5279,10 +5430,10 @@
         <v>4</v>
       </c>
       <c r="B186" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="C186" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5290,10 +5441,10 @@
         <v>4</v>
       </c>
       <c r="B187" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="C187" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5301,10 +5452,10 @@
         <v>4</v>
       </c>
       <c r="B188" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="C188" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5312,10 +5463,10 @@
         <v>4</v>
       </c>
       <c r="B189" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="C189" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5323,10 +5474,10 @@
         <v>4</v>
       </c>
       <c r="B190" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="C190" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5334,10 +5485,10 @@
         <v>4</v>
       </c>
       <c r="B191" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="C191" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5345,10 +5496,10 @@
         <v>4</v>
       </c>
       <c r="B192" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="C192" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5356,10 +5507,10 @@
         <v>4</v>
       </c>
       <c r="B193" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="C193" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5367,10 +5518,10 @@
         <v>4</v>
       </c>
       <c r="B194" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="C194" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5378,10 +5529,10 @@
         <v>4</v>
       </c>
       <c r="B195" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="C195" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5389,10 +5540,10 @@
         <v>4</v>
       </c>
       <c r="B196" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="C196" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5400,10 +5551,10 @@
         <v>4</v>
       </c>
       <c r="B197" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="C197" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5411,10 +5562,10 @@
         <v>4</v>
       </c>
       <c r="B198" t="s">
-        <v>536</v>
+        <v>505</v>
       </c>
       <c r="C198" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5422,10 +5573,10 @@
         <v>4</v>
       </c>
       <c r="B199" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="C199" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5433,10 +5584,10 @@
         <v>4</v>
       </c>
       <c r="B200" t="s">
-        <v>129</v>
+        <v>509</v>
       </c>
       <c r="C200" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5444,10 +5595,10 @@
         <v>4</v>
       </c>
       <c r="B201" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="C201" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5455,10 +5606,10 @@
         <v>4</v>
       </c>
       <c r="B202" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="C202" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5466,10 +5617,10 @@
         <v>4</v>
       </c>
       <c r="B203" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="C203" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5477,10 +5628,10 @@
         <v>4</v>
       </c>
       <c r="B204" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="C204" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5488,10 +5639,10 @@
         <v>4</v>
       </c>
       <c r="B205" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="C205" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5499,10 +5650,10 @@
         <v>4</v>
       </c>
       <c r="B206" t="s">
-        <v>533</v>
+        <v>129</v>
       </c>
       <c r="C206" t="s">
-        <v>304</v>
+        <v>521</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5510,10 +5661,10 @@
         <v>4</v>
       </c>
       <c r="B207" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="C207" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5521,10 +5672,10 @@
         <v>4</v>
       </c>
       <c r="B208" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="C208" t="s">
-        <v>540</v>
+        <v>525</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5532,21 +5683,21 @@
         <v>4</v>
       </c>
       <c r="B209" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="C209" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="48">
         <v>4</v>
       </c>
-      <c r="B210" s="103" t="s">
-        <v>731</v>
-      </c>
-      <c r="C210" s="102" t="s">
-        <v>732</v>
+      <c r="B210" t="s">
+        <v>528</v>
+      </c>
+      <c r="C210" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5554,10 +5705,10 @@
         <v>4</v>
       </c>
       <c r="B211" t="s">
-        <v>544</v>
+        <v>530</v>
       </c>
       <c r="C211" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5565,10 +5716,10 @@
         <v>4</v>
       </c>
       <c r="B212" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="C212" t="s">
-        <v>547</v>
+        <v>304</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5576,10 +5727,10 @@
         <v>4</v>
       </c>
       <c r="B213" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="C213" t="s">
-        <v>551</v>
+        <v>534</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5587,10 +5738,10 @@
         <v>4</v>
       </c>
       <c r="B214" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="C214" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5598,21 +5749,21 @@
         <v>4</v>
       </c>
       <c r="B215" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="C215" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A216" s="48">
         <v>4</v>
       </c>
-      <c r="B216" t="s">
-        <v>556</v>
-      </c>
-      <c r="C216" t="s">
-        <v>557</v>
+      <c r="B216" s="103" t="s">
+        <v>720</v>
+      </c>
+      <c r="C216" s="102" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5620,10 +5771,10 @@
         <v>4</v>
       </c>
       <c r="B217" t="s">
-        <v>558</v>
+        <v>543</v>
       </c>
       <c r="C217" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5631,10 +5782,10 @@
         <v>4</v>
       </c>
       <c r="B218" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="C218" t="s">
-        <v>561</v>
+        <v>546</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5642,10 +5793,10 @@
         <v>4</v>
       </c>
       <c r="B219" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="C219" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5653,10 +5804,10 @@
         <v>4</v>
       </c>
       <c r="B220" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="C220" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5664,10 +5815,10 @@
         <v>4</v>
       </c>
       <c r="B221" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="C221" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5675,10 +5826,10 @@
         <v>4</v>
       </c>
       <c r="B222" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="C222" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5686,10 +5837,10 @@
         <v>4</v>
       </c>
       <c r="B223" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="C223" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5697,10 +5848,10 @@
         <v>4</v>
       </c>
       <c r="B224" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="C224" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5708,10 +5859,10 @@
         <v>4</v>
       </c>
       <c r="B225" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="C225" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5719,10 +5870,10 @@
         <v>4</v>
       </c>
       <c r="B226" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="C226" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5730,10 +5881,10 @@
         <v>4</v>
       </c>
       <c r="B227" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="C227" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5741,10 +5892,10 @@
         <v>4</v>
       </c>
       <c r="B228" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="C228" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5752,10 +5903,10 @@
         <v>4</v>
       </c>
       <c r="B229" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="C229" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5763,10 +5914,10 @@
         <v>4</v>
       </c>
       <c r="B230" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="C230" t="s">
-        <v>585</v>
+        <v>572</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5774,10 +5925,10 @@
         <v>4</v>
       </c>
       <c r="B231" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="C231" t="s">
-        <v>587</v>
+        <v>574</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5785,186 +5936,186 @@
         <v>4</v>
       </c>
       <c r="B232" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="C232" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A233" s="48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B233" t="s">
-        <v>733</v>
+        <v>577</v>
       </c>
       <c r="C233" t="s">
-        <v>734</v>
+        <v>578</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A234" s="48">
-        <v>5</v>
-      </c>
-      <c r="B234" s="93" t="s">
-        <v>602</v>
-      </c>
-      <c r="C234" s="93" t="s">
-        <v>603</v>
+        <v>4</v>
+      </c>
+      <c r="B234" t="s">
+        <v>579</v>
+      </c>
+      <c r="C234" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A235" s="48">
-        <v>5</v>
-      </c>
-      <c r="B235" s="93" t="s">
-        <v>604</v>
-      </c>
-      <c r="C235" s="93" t="s">
-        <v>605</v>
+        <v>4</v>
+      </c>
+      <c r="B235" t="s">
+        <v>581</v>
+      </c>
+      <c r="C235" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A236" s="48">
-        <v>5</v>
-      </c>
-      <c r="B236" s="95" t="s">
-        <v>675</v>
-      </c>
-      <c r="C236" s="95" t="s">
-        <v>676</v>
+        <v>4</v>
+      </c>
+      <c r="B236" t="s">
+        <v>583</v>
+      </c>
+      <c r="C236" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A237" s="48">
-        <v>5</v>
-      </c>
-      <c r="B237" s="93" t="s">
-        <v>610</v>
-      </c>
-      <c r="C237" s="93" t="s">
-        <v>611</v>
+        <v>4</v>
+      </c>
+      <c r="B237" t="s">
+        <v>585</v>
+      </c>
+      <c r="C237" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A238" s="48">
-        <v>5</v>
-      </c>
-      <c r="B238" s="95" t="s">
-        <v>677</v>
-      </c>
-      <c r="C238" s="93" t="s">
-        <v>614</v>
+        <v>4</v>
+      </c>
+      <c r="B238" t="s">
+        <v>587</v>
+      </c>
+      <c r="C238" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A239" s="48">
-        <v>5</v>
-      </c>
-      <c r="B239" s="93" t="s">
-        <v>615</v>
-      </c>
-      <c r="C239" s="93" t="s">
-        <v>616</v>
+        <v>4</v>
+      </c>
+      <c r="B239" t="s">
+        <v>747</v>
+      </c>
+      <c r="C239" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A240" s="48">
-        <v>5</v>
-      </c>
-      <c r="B240" s="93" t="s">
-        <v>612</v>
-      </c>
-      <c r="C240" s="93" t="s">
-        <v>613</v>
+        <v>4</v>
+      </c>
+      <c r="B240" t="s">
+        <v>749</v>
+      </c>
+      <c r="C240" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A241" s="48">
-        <v>5</v>
-      </c>
-      <c r="B241" s="93" t="s">
-        <v>606</v>
-      </c>
-      <c r="C241" s="93" t="s">
-        <v>607</v>
+        <v>4</v>
+      </c>
+      <c r="B241" t="s">
+        <v>751</v>
+      </c>
+      <c r="C241" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A242" s="48">
-        <v>5</v>
-      </c>
-      <c r="B242" s="93" t="s">
-        <v>608</v>
-      </c>
-      <c r="C242" s="93" t="s">
-        <v>609</v>
+        <v>4</v>
+      </c>
+      <c r="B242" t="s">
+        <v>753</v>
+      </c>
+      <c r="C242" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A243" s="48">
-        <v>5</v>
-      </c>
-      <c r="B243" s="93" t="s">
-        <v>617</v>
-      </c>
-      <c r="C243" s="93" t="s">
-        <v>618</v>
+        <v>4</v>
+      </c>
+      <c r="B243" t="s">
+        <v>755</v>
+      </c>
+      <c r="C243" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A244" s="48">
-        <v>5</v>
-      </c>
-      <c r="B244" s="95" t="s">
-        <v>671</v>
-      </c>
-      <c r="C244" s="93" t="s">
-        <v>619</v>
+        <v>4</v>
+      </c>
+      <c r="B244" t="s">
+        <v>757</v>
+      </c>
+      <c r="C244" t="s">
+        <v>758</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="48">
-        <v>5</v>
-      </c>
-      <c r="B245" s="93" t="s">
-        <v>620</v>
-      </c>
-      <c r="C245" s="93" t="s">
-        <v>621</v>
+        <v>4</v>
+      </c>
+      <c r="B245" t="s">
+        <v>759</v>
+      </c>
+      <c r="C245" t="s">
+        <v>760</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A246" s="48">
-        <v>5</v>
-      </c>
-      <c r="B246" s="93" t="s">
-        <v>626</v>
-      </c>
-      <c r="C246" s="93" t="s">
-        <v>627</v>
+        <v>4</v>
+      </c>
+      <c r="B246" t="s">
+        <v>761</v>
+      </c>
+      <c r="C246" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="48">
         <v>5</v>
       </c>
-      <c r="B247" s="93" t="s">
-        <v>628</v>
-      </c>
-      <c r="C247" s="94" t="s">
-        <v>629</v>
+      <c r="B247" t="s">
+        <v>722</v>
+      </c>
+      <c r="C247" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="48">
         <v>5</v>
       </c>
-      <c r="B248" s="95" t="s">
-        <v>632</v>
+      <c r="B248" s="93" t="s">
+        <v>599</v>
       </c>
       <c r="C248" s="93" t="s">
-        <v>633</v>
+        <v>600</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5972,21 +6123,21 @@
         <v>5</v>
       </c>
       <c r="B249" s="93" t="s">
-        <v>634</v>
+        <v>601</v>
       </c>
       <c r="C249" s="93" t="s">
-        <v>635</v>
+        <v>602</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A250" s="48">
         <v>5</v>
       </c>
-      <c r="B250" s="93" t="s">
-        <v>636</v>
-      </c>
-      <c r="C250" s="93" t="s">
-        <v>637</v>
+      <c r="B250" s="95" t="s">
+        <v>666</v>
+      </c>
+      <c r="C250" s="95" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5994,21 +6145,21 @@
         <v>5</v>
       </c>
       <c r="B251" s="93" t="s">
-        <v>622</v>
+        <v>607</v>
       </c>
       <c r="C251" s="93" t="s">
-        <v>623</v>
+        <v>608</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A252" s="48">
         <v>5</v>
       </c>
-      <c r="B252" s="93" t="s">
-        <v>638</v>
+      <c r="B252" s="95" t="s">
+        <v>668</v>
       </c>
       <c r="C252" s="93" t="s">
-        <v>639</v>
+        <v>611</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6016,10 +6167,10 @@
         <v>5</v>
       </c>
       <c r="B253" s="93" t="s">
-        <v>640</v>
+        <v>778</v>
       </c>
       <c r="C253" s="93" t="s">
-        <v>641</v>
+        <v>612</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6027,10 +6178,10 @@
         <v>5</v>
       </c>
       <c r="B254" s="93" t="s">
-        <v>642</v>
+        <v>609</v>
       </c>
       <c r="C254" s="93" t="s">
-        <v>643</v>
+        <v>610</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6038,32 +6189,32 @@
         <v>5</v>
       </c>
       <c r="B255" s="93" t="s">
-        <v>644</v>
+        <v>603</v>
       </c>
       <c r="C255" s="93" t="s">
-        <v>645</v>
+        <v>604</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A256" s="48">
         <v>5</v>
       </c>
-      <c r="B256" s="95" t="s">
-        <v>721</v>
+      <c r="B256" s="93" t="s">
+        <v>605</v>
       </c>
       <c r="C256" s="93" t="s">
-        <v>722</v>
+        <v>606</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A257" s="48">
         <v>5</v>
       </c>
-      <c r="B257" s="95" t="s">
-        <v>648</v>
+      <c r="B257" s="93" t="s">
+        <v>613</v>
       </c>
       <c r="C257" s="93" t="s">
-        <v>649</v>
+        <v>614</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6071,43 +6222,43 @@
         <v>5</v>
       </c>
       <c r="B258" s="95" t="s">
-        <v>650</v>
+        <v>663</v>
       </c>
       <c r="C258" s="93" t="s">
-        <v>651</v>
+        <v>615</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A259" s="48">
         <v>5</v>
       </c>
-      <c r="B259" s="95" t="s">
-        <v>652</v>
+      <c r="B259" s="93" t="s">
+        <v>616</v>
       </c>
       <c r="C259" s="93" t="s">
-        <v>653</v>
+        <v>617</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A260" s="48">
         <v>5</v>
       </c>
-      <c r="B260" s="95" t="s">
-        <v>655</v>
+      <c r="B260" s="93" t="s">
+        <v>622</v>
       </c>
       <c r="C260" s="93" t="s">
-        <v>656</v>
+        <v>623</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A261" s="48">
         <v>5</v>
       </c>
-      <c r="B261" s="95" t="s">
-        <v>657</v>
-      </c>
-      <c r="C261" s="93" t="s">
-        <v>658</v>
+      <c r="B261" s="93" t="s">
+        <v>624</v>
+      </c>
+      <c r="C261" s="94" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6115,10 +6266,10 @@
         <v>5</v>
       </c>
       <c r="B262" s="95" t="s">
-        <v>663</v>
+        <v>626</v>
       </c>
       <c r="C262" s="93" t="s">
-        <v>664</v>
+        <v>627</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6126,21 +6277,21 @@
         <v>5</v>
       </c>
       <c r="B263" s="93" t="s">
-        <v>659</v>
+        <v>628</v>
       </c>
       <c r="C263" s="93" t="s">
-        <v>660</v>
+        <v>629</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A264" s="48">
         <v>5</v>
       </c>
-      <c r="B264" s="95" t="s">
-        <v>661</v>
+      <c r="B264" s="93" t="s">
+        <v>630</v>
       </c>
       <c r="C264" s="93" t="s">
-        <v>662</v>
+        <v>631</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6148,43 +6299,43 @@
         <v>5</v>
       </c>
       <c r="B265" s="93" t="s">
-        <v>665</v>
+        <v>618</v>
       </c>
       <c r="C265" s="93" t="s">
-        <v>666</v>
+        <v>619</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A266" s="48">
         <v>5</v>
       </c>
-      <c r="B266" s="95" t="s">
-        <v>624</v>
+      <c r="B266" s="93" t="s">
+        <v>632</v>
       </c>
       <c r="C266" s="93" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A267" s="48">
         <v>5</v>
       </c>
-      <c r="B267" s="95" t="s">
-        <v>646</v>
+      <c r="B267" s="93" t="s">
+        <v>634</v>
       </c>
       <c r="C267" s="93" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A268" s="48">
         <v>5</v>
       </c>
-      <c r="B268" s="95" t="s">
-        <v>630</v>
+      <c r="B268" s="93" t="s">
+        <v>636</v>
       </c>
       <c r="C268" s="93" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6192,87 +6343,87 @@
         <v>5</v>
       </c>
       <c r="B269" s="93" t="s">
-        <v>669</v>
+        <v>638</v>
       </c>
       <c r="C269" s="93" t="s">
-        <v>670</v>
+        <v>639</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A270" s="48">
         <v>5</v>
       </c>
-      <c r="B270" s="93" t="s">
-        <v>673</v>
+      <c r="B270" s="95" t="s">
+        <v>711</v>
       </c>
       <c r="C270" s="93" t="s">
-        <v>674</v>
+        <v>712</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A271" s="48">
         <v>5</v>
       </c>
-      <c r="B271" t="s">
-        <v>736</v>
-      </c>
-      <c r="C271" t="s">
-        <v>737</v>
+      <c r="B271" s="95" t="s">
+        <v>766</v>
+      </c>
+      <c r="C271" s="93" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A272" s="48">
         <v>5</v>
       </c>
-      <c r="B272" s="93" t="s">
-        <v>678</v>
+      <c r="B272" s="95" t="s">
+        <v>643</v>
       </c>
       <c r="C272" s="93" t="s">
-        <v>679</v>
+        <v>644</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A273" s="48">
         <v>5</v>
       </c>
-      <c r="B273" s="93" t="s">
-        <v>681</v>
+      <c r="B273" s="95" t="s">
+        <v>645</v>
       </c>
       <c r="C273" s="93" t="s">
-        <v>682</v>
+        <v>646</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A274" s="48">
         <v>5</v>
       </c>
-      <c r="B274" s="93" t="s">
-        <v>683</v>
+      <c r="B274" s="95" t="s">
+        <v>648</v>
       </c>
       <c r="C274" s="93" t="s">
-        <v>684</v>
+        <v>649</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A275" s="48">
         <v>5</v>
       </c>
-      <c r="B275" s="93" t="s">
-        <v>685</v>
+      <c r="B275" s="95" t="s">
+        <v>650</v>
       </c>
       <c r="C275" s="93" t="s">
-        <v>686</v>
+        <v>651</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A276" s="48">
         <v>5</v>
       </c>
-      <c r="B276" s="93" t="s">
-        <v>687</v>
+      <c r="B276" s="95" t="s">
+        <v>656</v>
       </c>
       <c r="C276" s="93" t="s">
-        <v>688</v>
+        <v>657</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6280,21 +6431,21 @@
         <v>5</v>
       </c>
       <c r="B277" s="93" t="s">
-        <v>689</v>
+        <v>652</v>
       </c>
       <c r="C277" s="93" t="s">
-        <v>690</v>
+        <v>653</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A278" s="48">
         <v>5</v>
       </c>
-      <c r="B278" s="93" t="s">
-        <v>691</v>
+      <c r="B278" s="95" t="s">
+        <v>654</v>
       </c>
       <c r="C278" s="93" t="s">
-        <v>692</v>
+        <v>655</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6302,43 +6453,43 @@
         <v>5</v>
       </c>
       <c r="B279" s="93" t="s">
-        <v>693</v>
+        <v>658</v>
       </c>
       <c r="C279" s="93" t="s">
-        <v>694</v>
+        <v>659</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A280" s="48">
         <v>5</v>
       </c>
-      <c r="B280" s="93" t="s">
-        <v>695</v>
+      <c r="B280" s="95" t="s">
+        <v>620</v>
       </c>
       <c r="C280" s="93" t="s">
-        <v>696</v>
+        <v>621</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A281" s="48">
         <v>5</v>
       </c>
-      <c r="B281" s="93" t="s">
-        <v>719</v>
+      <c r="B281" s="95" t="s">
+        <v>640</v>
       </c>
       <c r="C281" s="93" t="s">
-        <v>720</v>
+        <v>641</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A282" s="48">
         <v>5</v>
       </c>
-      <c r="B282" s="93" t="s">
-        <v>697</v>
-      </c>
-      <c r="C282" s="93" t="s">
-        <v>698</v>
+      <c r="B282" t="s">
+        <v>790</v>
+      </c>
+      <c r="C282" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6346,10 +6497,10 @@
         <v>5</v>
       </c>
       <c r="B283" s="93" t="s">
-        <v>699</v>
+        <v>661</v>
       </c>
       <c r="C283" s="93" t="s">
-        <v>700</v>
+        <v>662</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6357,21 +6508,21 @@
         <v>5</v>
       </c>
       <c r="B284" s="93" t="s">
-        <v>701</v>
+        <v>664</v>
       </c>
       <c r="C284" s="93" t="s">
-        <v>702</v>
+        <v>665</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A285" s="48">
         <v>5</v>
       </c>
-      <c r="B285" s="93" t="s">
-        <v>703</v>
-      </c>
-      <c r="C285" s="93" t="s">
-        <v>704</v>
+      <c r="B285" t="s">
+        <v>724</v>
+      </c>
+      <c r="C285" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6379,10 +6530,10 @@
         <v>5</v>
       </c>
       <c r="B286" s="93" t="s">
-        <v>705</v>
+        <v>669</v>
       </c>
       <c r="C286" s="93" t="s">
-        <v>706</v>
+        <v>670</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6390,10 +6541,10 @@
         <v>5</v>
       </c>
       <c r="B287" s="93" t="s">
-        <v>707</v>
+        <v>671</v>
       </c>
       <c r="C287" s="93" t="s">
-        <v>708</v>
+        <v>672</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6401,10 +6552,10 @@
         <v>5</v>
       </c>
       <c r="B288" s="93" t="s">
-        <v>709</v>
+        <v>673</v>
       </c>
       <c r="C288" s="93" t="s">
-        <v>710</v>
+        <v>674</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6412,10 +6563,10 @@
         <v>5</v>
       </c>
       <c r="B289" s="93" t="s">
-        <v>711</v>
+        <v>675</v>
       </c>
       <c r="C289" s="93" t="s">
-        <v>712</v>
+        <v>676</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6423,10 +6574,10 @@
         <v>5</v>
       </c>
       <c r="B290" s="93" t="s">
-        <v>713</v>
+        <v>677</v>
       </c>
       <c r="C290" s="93" t="s">
-        <v>714</v>
+        <v>678</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6434,10 +6585,10 @@
         <v>5</v>
       </c>
       <c r="B291" s="93" t="s">
-        <v>715</v>
+        <v>679</v>
       </c>
       <c r="C291" s="93" t="s">
-        <v>716</v>
+        <v>680</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6445,40 +6596,280 @@
         <v>5</v>
       </c>
       <c r="B292" s="93" t="s">
-        <v>717</v>
+        <v>681</v>
       </c>
       <c r="C292" s="93" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="294" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="295" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="296" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="297" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="298" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="299" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="300" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="301" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="302" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="303" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="304" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+        <v>682</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A293" s="48">
+        <v>5</v>
+      </c>
+      <c r="B293" s="93" t="s">
+        <v>683</v>
+      </c>
+      <c r="C293" s="93" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A294" s="48">
+        <v>5</v>
+      </c>
+      <c r="B294" s="93" t="s">
+        <v>685</v>
+      </c>
+      <c r="C294" s="93" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A295" s="48">
+        <v>5</v>
+      </c>
+      <c r="B295" s="93" t="s">
+        <v>709</v>
+      </c>
+      <c r="C295" s="93" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A296" s="48">
+        <v>5</v>
+      </c>
+      <c r="B296" s="93" t="s">
+        <v>687</v>
+      </c>
+      <c r="C296" s="93" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A297" s="48">
+        <v>5</v>
+      </c>
+      <c r="B297" s="93" t="s">
+        <v>689</v>
+      </c>
+      <c r="C297" s="93" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A298" s="48">
+        <v>5</v>
+      </c>
+      <c r="B298" s="93" t="s">
+        <v>691</v>
+      </c>
+      <c r="C298" s="93" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A299" s="48">
+        <v>5</v>
+      </c>
+      <c r="B299" s="93" t="s">
+        <v>693</v>
+      </c>
+      <c r="C299" s="93" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A300" s="48">
+        <v>5</v>
+      </c>
+      <c r="B300" s="93" t="s">
+        <v>695</v>
+      </c>
+      <c r="C300" s="93" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A301" s="48">
+        <v>5</v>
+      </c>
+      <c r="B301" s="93" t="s">
+        <v>697</v>
+      </c>
+      <c r="C301" s="93" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A302" s="48">
+        <v>5</v>
+      </c>
+      <c r="B302" s="93" t="s">
+        <v>699</v>
+      </c>
+      <c r="C302" s="93" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A303" s="48">
+        <v>5</v>
+      </c>
+      <c r="B303" s="93" t="s">
+        <v>701</v>
+      </c>
+      <c r="C303" s="93" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A304" s="48">
+        <v>5</v>
+      </c>
+      <c r="B304" s="93" t="s">
+        <v>703</v>
+      </c>
+      <c r="C304" s="93" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A305" s="48">
+        <v>5</v>
+      </c>
+      <c r="B305" s="93" t="s">
+        <v>705</v>
+      </c>
+      <c r="C305" s="93" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A306" s="48">
+        <v>5</v>
+      </c>
+      <c r="B306" s="93" t="s">
+        <v>707</v>
+      </c>
+      <c r="C306" s="93" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A307" s="104">
+        <v>5</v>
+      </c>
+      <c r="B307" t="s">
+        <v>764</v>
+      </c>
+      <c r="C307" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A308" s="104">
+        <v>5</v>
+      </c>
+      <c r="B308" s="49" t="s">
+        <v>768</v>
+      </c>
+      <c r="C308" s="50" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A309" s="104">
+        <v>5</v>
+      </c>
+      <c r="B309" t="s">
+        <v>772</v>
+      </c>
+      <c r="C309" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A310" s="104">
+        <v>5</v>
+      </c>
+      <c r="B310" s="49" t="s">
+        <v>774</v>
+      </c>
+      <c r="C310" s="50" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A311" s="104">
+        <v>5</v>
+      </c>
+      <c r="B311" t="s">
+        <v>776</v>
+      </c>
+      <c r="C311" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A312" s="104">
+        <v>5</v>
+      </c>
+      <c r="B312" t="s">
+        <v>780</v>
+      </c>
+      <c r="C312" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A313" s="104">
+        <v>5</v>
+      </c>
+      <c r="B313" t="s">
+        <v>782</v>
+      </c>
+      <c r="C313" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A314" s="104">
+        <v>5</v>
+      </c>
+      <c r="B314" t="s">
+        <v>784</v>
+      </c>
+      <c r="C314" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A315" s="104">
+        <v>5</v>
+      </c>
+      <c r="B315" t="s">
+        <v>786</v>
+      </c>
+      <c r="C315" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A316" s="104">
+        <v>5</v>
+      </c>
+      <c r="B316" s="49" t="s">
+        <v>788</v>
+      </c>
+      <c r="C316" s="50" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="318" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="319" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="320" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -7154,12 +7545,25 @@
     <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <conditionalFormatting sqref="B176:B209 B211:B232">
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+  <conditionalFormatting sqref="C248:C281">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C234:C268">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="B182:B215 B217:B238">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7210,7 +7614,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>278</v>
@@ -7817,10 +8221,10 @@
         <v>3</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C22" s="51" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -8121,10 +8525,10 @@
         <v>4</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="C32" s="44" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -8145,28 +8549,28 @@
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="79" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F33" s="80" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G33" s="80" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H33" s="80" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I33" s="80" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="J33" s="80" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K33" s="80" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L33" s="81" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
@@ -8178,28 +8582,28 @@
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="82" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F34" s="23" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G34" s="83" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H34" s="83" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I34" s="83" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J34" s="83" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K34" s="83" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L34" s="84" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
@@ -8211,28 +8615,28 @@
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="24" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F35" s="23" t="s">
+        <v>532</v>
+      </c>
+      <c r="G35" s="23" t="s">
         <v>533</v>
       </c>
-      <c r="G35" s="23" t="s">
-        <v>534</v>
-      </c>
       <c r="H35" s="83" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I35" s="83" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="J35" s="83" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K35" s="83" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L35" s="25" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
@@ -8244,28 +8648,28 @@
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="24" t="s">
+        <v>532</v>
+      </c>
+      <c r="F36" s="26" t="s">
+        <v>720</v>
+      </c>
+      <c r="G36" s="23" t="s">
         <v>533</v>
       </c>
-      <c r="F36" s="26" t="s">
-        <v>731</v>
-      </c>
-      <c r="G36" s="23" t="s">
-        <v>534</v>
-      </c>
       <c r="H36" s="23" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I36" s="83" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J36" s="83" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K36" s="23" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L36" s="25" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
@@ -8277,28 +8681,28 @@
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="27" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="G37" s="26" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I37" s="23" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="J37" s="23" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K37" s="23" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L37" s="29" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
@@ -8310,28 +8714,28 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="27" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="F38" s="90" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G38" s="26" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="I38" s="23" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J38" s="23" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K38" s="26" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="L38" s="92" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
@@ -8343,28 +8747,28 @@
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="89" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F39" s="87" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G39" s="90" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H39" s="26" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I39" s="26" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="J39" s="26" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="K39" s="90" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L39" s="92" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
@@ -8376,28 +8780,28 @@
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="85" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F40" s="86" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G40" s="86" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H40" s="91" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I40" s="91" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="J40" s="91" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="K40" s="86" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L40" s="88" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
@@ -8425,10 +8829,10 @@
         <v>5</v>
       </c>
       <c r="B42" s="51" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="C42" s="51" t="s">
-        <v>680</v>
+        <v>770</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -8449,28 +8853,28 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="32" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="F43" s="33" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="G43" s="33" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="H43" s="33" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="I43" s="33" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="J43" s="33" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="K43" s="33" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="L43" s="34" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
@@ -8482,28 +8886,28 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="35" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="G44" s="97" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="H44" s="96" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="I44" s="96" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="J44" s="96" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="K44" s="31" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="L44" s="36" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
@@ -8515,28 +8919,28 @@
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="35" t="s">
+        <v>642</v>
+      </c>
+      <c r="F45" s="100" t="s">
+        <v>656</v>
+      </c>
+      <c r="G45" s="51" t="s">
+        <v>650</v>
+      </c>
+      <c r="H45" s="101" t="s">
+        <v>658</v>
+      </c>
+      <c r="I45" s="101" t="s">
+        <v>658</v>
+      </c>
+      <c r="J45" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="F45" s="100" t="s">
-        <v>663</v>
-      </c>
-      <c r="G45" s="51" t="s">
-        <v>657</v>
-      </c>
-      <c r="H45" s="101" t="s">
-        <v>665</v>
-      </c>
-      <c r="I45" s="101" t="s">
-        <v>665</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>655</v>
-      </c>
       <c r="K45" s="97" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="L45" s="36" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
@@ -8548,28 +8952,28 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="99" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="G46" s="51" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="H46" s="101" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="I46" s="101" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="J46" s="51" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="L46" s="98" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
@@ -8581,28 +8985,28 @@
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="35" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="F47" s="96" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="H47" s="101" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="I47" s="101" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="K47" s="96" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="L47" s="36" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
@@ -8614,28 +9018,28 @@
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="35" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="F48" s="31" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="G48" s="97" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="H48" s="97" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="I48" s="97" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="J48" s="96" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="K48" s="31" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="L48" s="36" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
@@ -8647,28 +9051,28 @@
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="35" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="F49" s="31" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="G49" s="31" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="H49" s="31" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="I49" s="31" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="J49" s="31" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="K49" s="31" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="L49" s="36" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
@@ -8680,28 +9084,28 @@
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="37" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="G50" s="38" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="H50" s="38" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="I50" s="38" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="J50" s="38" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="K50" s="38" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="L50" s="39" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
@@ -12746,7 +13150,7 @@
     <col min="1" max="1" width="7.3984375" customWidth="1"/>
     <col min="2" max="2" width="17.59765625" customWidth="1"/>
     <col min="3" max="3" width="18.86328125" customWidth="1"/>
-    <col min="4" max="4" width="47.1328125" customWidth="1"/>
+    <col min="4" max="4" width="52.53125" customWidth="1"/>
     <col min="5" max="8" width="18.86328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12814,7 +13218,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="51" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -12868,7 +13272,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -12970,13 +13374,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -12988,13 +13392,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -13102,7 +13506,7 @@
         <v>11</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="E20" s="48"/>
       <c r="F20" s="1"/>
@@ -13186,13 +13590,13 @@
         <v>2</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E25" s="48"/>
       <c r="F25" s="1"/>
@@ -13204,13 +13608,13 @@
         <v>2</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E26" s="48"/>
       <c r="F26" s="1"/>
@@ -13246,7 +13650,7 @@
         <v>24</v>
       </c>
       <c r="D28" s="51" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
@@ -13318,7 +13722,7 @@
         <v>11</v>
       </c>
       <c r="D32" s="51" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -13390,7 +13794,7 @@
         <v>18</v>
       </c>
       <c r="D36" s="44" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -13398,15 +13802,17 @@
       <c r="H36" s="1"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="3"/>
+      <c r="A37" s="3">
+        <v>3</v>
+      </c>
       <c r="B37" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>600</v>
+        <v>733</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -13418,13 +13824,13 @@
         <v>3</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -13460,7 +13866,7 @@
         <v>24</v>
       </c>
       <c r="D40" s="51" t="s">
-        <v>473</v>
+        <v>746</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
@@ -13532,7 +13938,7 @@
         <v>11</v>
       </c>
       <c r="D44" s="51" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -13550,7 +13956,7 @@
         <v>13</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -13568,7 +13974,7 @@
         <v>15</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -13586,7 +13992,7 @@
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -13604,7 +14010,7 @@
         <v>18</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -13612,15 +14018,17 @@
       <c r="H48" s="1"/>
     </row>
     <row r="49" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="3"/>
+      <c r="A49" s="3">
+        <v>4</v>
+      </c>
       <c r="B49" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -13632,13 +14040,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D50" s="51" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -13656,14 +14064,14 @@
         <v>21</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:8" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="3">
         <v>4</v>
       </c>
@@ -13674,7 +14082,7 @@
         <v>24</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>590</v>
+        <v>763</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -13746,7 +14154,7 @@
         <v>11</v>
       </c>
       <c r="D56" s="51" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
@@ -13764,7 +14172,7 @@
         <v>13</v>
       </c>
       <c r="D57" s="51" t="s">
-        <v>735</v>
+        <v>779</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
@@ -13782,7 +14190,7 @@
         <v>15</v>
       </c>
       <c r="D58" s="51" t="s">
-        <v>672</v>
+        <v>793</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
@@ -13800,7 +14208,7 @@
         <v>17</v>
       </c>
       <c r="D59" s="51" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
@@ -13818,7 +14226,7 @@
         <v>18</v>
       </c>
       <c r="D60" s="51" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
@@ -13826,15 +14234,17 @@
       <c r="H60" s="1"/>
     </row>
     <row r="61" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="3"/>
+      <c r="A61" s="3">
+        <v>5</v>
+      </c>
       <c r="B61" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D61" s="51" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
@@ -13846,13 +14256,13 @@
         <v>5</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D62" s="51" t="s">
-        <v>724</v>
+        <v>771</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
@@ -13870,7 +14280,7 @@
         <v>21</v>
       </c>
       <c r="D63" s="51" t="s">
-        <v>668</v>
+        <v>792</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
@@ -13888,7 +14298,7 @@
         <v>24</v>
       </c>
       <c r="D64" s="51" t="s">
-        <v>738</v>
+        <v>794</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>

--- a/epepep_structure.xlsx
+++ b/epepep_structure.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\annwa\OneDrive\Desktop\Workspace\epepep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F87FBE7-17B2-4CDC-A447-94E6A3290433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BFD159-966D-490D-864F-D79A2B0095A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1028" yWindow="2055" windowWidth="12262" windowHeight="8933" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Word" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="923">
   <si>
     <t>Unit</t>
   </si>
@@ -1800,12 +1800,6 @@
   </si>
   <si>
     <t>fan3 lin6</t>
-  </si>
-  <si>
-    <t>成立</t>
-  </si>
-  <si>
-    <t>sing4 laap6</t>
   </si>
   <si>
     <t>無限</t>
@@ -2347,9 +2341,6 @@
     <t>kei4 haa6</t>
   </si>
   <si>
-    <t>運動|任務|混亂|誤會|健康|第三|罷工|效果|代表|系統|甚至|受到|預計|病人|例如|調查|關係|方便|經驗|口號|改善|總共|透露|訓練|破壞|旗下|成立|無限|</t>
-  </si>
-  <si>
     <t>有些</t>
   </si>
   <si>
@@ -2441,6 +2432,399 @@
   </si>
   <si>
     <t>螞蟻|母語|魯莽|馬尾|領先|野豬|有些|勇敢|了解|敏感|挽救|軟化|猛獸|友情|儲存|偶然|冷淡|偉大|網站|優雅|温暖|風雨|展覽|小鳥|口吻|過癮|快艇|器皿|行李|牛腩|煩惱|糯米|伴舞|廟宇</t>
+  </si>
+  <si>
+    <t>運動|任務|混亂|誤會|健康|第三|罷工|效果|代表|系統|甚至|受到|預計|病人|例如|調查|關係|方便|經驗|口號|改善|總共|透露|訓練|破壞|旗下|嚴重|無限|</t>
+  </si>
+  <si>
+    <t>嚴重</t>
+  </si>
+  <si>
+    <t>jim4 zung6</t>
+  </si>
+  <si>
+    <t>开</t>
+  </si>
+  <si>
+    <t>经</t>
+  </si>
+  <si>
+    <t>机</t>
+  </si>
+  <si>
+    <t>车</t>
+  </si>
+  <si>
+    <t>关</t>
+  </si>
+  <si>
+    <t>单</t>
+  </si>
+  <si>
+    <t>该</t>
+  </si>
+  <si>
+    <t>当</t>
+  </si>
+  <si>
+    <t>选</t>
+  </si>
+  <si>
+    <t>点</t>
+  </si>
+  <si>
+    <t>分钟</t>
+  </si>
+  <si>
+    <t>餐厅</t>
+  </si>
+  <si>
+    <t>空间</t>
+  </si>
+  <si>
+    <t>专家</t>
+  </si>
+  <si>
+    <t>申请</t>
+  </si>
+  <si>
+    <t>风险</t>
+  </si>
+  <si>
+    <t>参考</t>
+  </si>
+  <si>
+    <t>喜欢</t>
+  </si>
+  <si>
+    <t>广东</t>
+  </si>
+  <si>
+    <t>补充</t>
+  </si>
+  <si>
+    <t>采访</t>
+  </si>
+  <si>
+    <t>检讨</t>
+  </si>
+  <si>
+    <t>饮品</t>
+  </si>
+  <si>
+    <t>门</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>来</t>
+  </si>
+  <si>
+    <t>员</t>
+  </si>
+  <si>
+    <t>头</t>
+  </si>
+  <si>
+    <t>连</t>
+  </si>
+  <si>
+    <t>题</t>
+  </si>
+  <si>
+    <t>龙</t>
+  </si>
+  <si>
+    <t>红</t>
+  </si>
+  <si>
+    <t>条</t>
+  </si>
+  <si>
+    <t>银行</t>
+  </si>
+  <si>
+    <t>传媒</t>
+  </si>
+  <si>
+    <t>当年</t>
+  </si>
+  <si>
+    <t>高层</t>
+  </si>
+  <si>
+    <t>检查</t>
+  </si>
+  <si>
+    <t>减肥</t>
+  </si>
+  <si>
+    <t>黄金</t>
+  </si>
+  <si>
+    <t>离开</t>
+  </si>
+  <si>
+    <t>团体</t>
+  </si>
+  <si>
+    <t>筹款</t>
+  </si>
+  <si>
+    <t>过</t>
+  </si>
+  <si>
+    <t>见</t>
+  </si>
+  <si>
+    <t>价</t>
+  </si>
+  <si>
+    <t>记</t>
+  </si>
+  <si>
+    <t>报</t>
+  </si>
+  <si>
+    <t>气</t>
+  </si>
+  <si>
+    <t>战</t>
+  </si>
+  <si>
+    <t>变</t>
+  </si>
+  <si>
+    <t>赛</t>
+  </si>
+  <si>
+    <t>爱</t>
+  </si>
+  <si>
+    <t>伞</t>
+  </si>
+  <si>
+    <t>讲</t>
+  </si>
+  <si>
+    <t>个案</t>
+  </si>
+  <si>
+    <t>照顾</t>
+  </si>
+  <si>
+    <t>圣诞</t>
+  </si>
+  <si>
+    <t>贡献</t>
+  </si>
+  <si>
+    <t>观众</t>
+  </si>
+  <si>
+    <t>关注</t>
+  </si>
+  <si>
+    <t>广吿</t>
+  </si>
+  <si>
+    <t>投诉</t>
+  </si>
+  <si>
+    <t>门票</t>
+  </si>
+  <si>
+    <t>镜头</t>
+  </si>
+  <si>
+    <t>四围</t>
+  </si>
+  <si>
+    <t>抗争</t>
+  </si>
+  <si>
+    <t>破产</t>
+  </si>
+  <si>
+    <t>机构</t>
+  </si>
+  <si>
+    <t>人数</t>
+  </si>
+  <si>
+    <t>为</t>
+  </si>
+  <si>
+    <t>话</t>
+  </si>
+  <si>
+    <t>现</t>
+  </si>
+  <si>
+    <t>动</t>
+  </si>
+  <si>
+    <t>问</t>
+  </si>
+  <si>
+    <t>电</t>
+  </si>
+  <si>
+    <t>币</t>
+  </si>
+  <si>
+    <t>梦</t>
+  </si>
+  <si>
+    <t>认</t>
+  </si>
+  <si>
+    <t>万</t>
+  </si>
+  <si>
+    <t>联</t>
+  </si>
+  <si>
+    <t>费</t>
+  </si>
+  <si>
+    <t>泻</t>
+  </si>
+  <si>
+    <t>运动</t>
+  </si>
+  <si>
+    <t>任务</t>
+  </si>
+  <si>
+    <t>混乱</t>
+  </si>
+  <si>
+    <t>误会</t>
+  </si>
+  <si>
+    <t>系统</t>
+  </si>
+  <si>
+    <t>调查</t>
+  </si>
+  <si>
+    <t>关係</t>
+  </si>
+  <si>
+    <t>经验</t>
+  </si>
+  <si>
+    <t>总共</t>
+  </si>
+  <si>
+    <t>训练</t>
+  </si>
+  <si>
+    <t>严重</t>
+  </si>
+  <si>
+    <t>无限</t>
+  </si>
+  <si>
+    <t>罢工</t>
+  </si>
+  <si>
+    <t>预计</t>
+  </si>
+  <si>
+    <t>口号</t>
+  </si>
+  <si>
+    <t>破坏</t>
+  </si>
+  <si>
+    <t>脑</t>
+  </si>
+  <si>
+    <t>买</t>
+  </si>
+  <si>
+    <t>码</t>
+  </si>
+  <si>
+    <t>与</t>
+  </si>
+  <si>
+    <t>远</t>
+  </si>
+  <si>
+    <t>满</t>
+  </si>
+  <si>
+    <t>礼</t>
+  </si>
+  <si>
+    <t>权</t>
+  </si>
+  <si>
+    <t>懒</t>
+  </si>
+  <si>
+    <t>蚂蚁</t>
+  </si>
+  <si>
+    <t>母语</t>
+  </si>
+  <si>
+    <t>鲁莽</t>
+  </si>
+  <si>
+    <t>马尾</t>
+  </si>
+  <si>
+    <t>领先</t>
+  </si>
+  <si>
+    <t>野猪</t>
+  </si>
+  <si>
+    <t>软化</t>
+  </si>
+  <si>
+    <t>储存</t>
+  </si>
+  <si>
+    <t>伟大</t>
+  </si>
+  <si>
+    <t>风雨</t>
+  </si>
+  <si>
+    <t>展览</t>
+  </si>
+  <si>
+    <t>小鸟</t>
+  </si>
+  <si>
+    <t>庙宇</t>
+  </si>
+  <si>
+    <t>猛兽</t>
+  </si>
+  <si>
+    <t>网站</t>
+  </si>
+  <si>
+    <t>优雅</t>
+  </si>
+  <si>
+    <t>过瘾</t>
+  </si>
+  <si>
+    <t>烦恼</t>
+  </si>
+  <si>
+    <t>Simplified</t>
+  </si>
+  <si>
+    <t>只（是）</t>
   </si>
 </sst>
 </file>
@@ -3381,1127 +3765,1430 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C1008"/>
+  <dimension ref="A1:D1008"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="104" customWidth="1"/>
-    <col min="2" max="2" width="12.59765625" style="49" customWidth="1"/>
-    <col min="3" max="3" width="12.59765625" style="50" customWidth="1"/>
-    <col min="4" max="6" width="12.59765625" customWidth="1"/>
+    <col min="2" max="3" width="12.59765625" style="49" customWidth="1"/>
+    <col min="4" max="4" width="12.59765625" style="50" customWidth="1"/>
+    <col min="5" max="7" width="12.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="46" t="s">
+        <v>921</v>
+      </c>
+      <c r="D1" s="52" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="48">
         <v>1</v>
       </c>
       <c r="B2" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="50" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="48">
         <v>1</v>
       </c>
       <c r="B3" s="47" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="50" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="48">
         <v>1</v>
       </c>
       <c r="B4" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="47" t="s">
+        <v>795</v>
+      </c>
+      <c r="D4" s="50" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="48">
         <v>1</v>
       </c>
       <c r="B5" s="47" t="s">
         <v>137</v>
       </c>
-      <c r="C5" s="50" t="s">
+      <c r="C5" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="D5" s="50" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="48">
         <v>1</v>
       </c>
       <c r="B6" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="50" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="48">
         <v>1</v>
       </c>
       <c r="B7" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="47" t="s">
+        <v>796</v>
+      </c>
+      <c r="D7" s="50" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="48">
         <v>1</v>
       </c>
       <c r="B8" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="D8" s="50" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="48">
         <v>1</v>
       </c>
       <c r="B9" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="47" t="s">
+        <v>797</v>
+      </c>
+      <c r="D9" s="50" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="48">
         <v>1</v>
       </c>
       <c r="B10" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="47" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" s="50" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="48">
         <v>1</v>
       </c>
       <c r="B11" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="50" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="48">
         <v>1</v>
       </c>
       <c r="B12" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="C12" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" s="50" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="48">
         <v>1</v>
       </c>
       <c r="B13" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="50" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="48">
         <v>1</v>
       </c>
       <c r="B14" s="47" t="s">
         <v>152</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="D14" s="50" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="48">
         <v>1</v>
       </c>
       <c r="B15" s="47" t="s">
         <v>154</v>
       </c>
-      <c r="C15" s="50" t="s">
+      <c r="C15" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="D15" s="50" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="48">
         <v>1</v>
       </c>
       <c r="B16" s="47" t="s">
         <v>161</v>
       </c>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="47" t="s">
+        <v>161</v>
+      </c>
+      <c r="D16" s="50" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="48">
         <v>1</v>
       </c>
       <c r="B17" s="47" t="s">
         <v>163</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="47" t="s">
+        <v>163</v>
+      </c>
+      <c r="D17" s="50" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="48">
         <v>1</v>
       </c>
       <c r="B18" s="47" t="s">
         <v>165</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="47" t="s">
+        <v>798</v>
+      </c>
+      <c r="D18" s="50" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="48">
         <v>1</v>
       </c>
       <c r="B19" s="47" t="s">
         <v>167</v>
       </c>
-      <c r="C19" s="50" t="s">
+      <c r="C19" s="47" t="s">
+        <v>799</v>
+      </c>
+      <c r="D19" s="50" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="48">
         <v>1</v>
       </c>
       <c r="B20" s="47" t="s">
         <v>147</v>
       </c>
-      <c r="C20" s="50" t="s">
+      <c r="C20" s="47" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="50" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="48">
         <v>1</v>
       </c>
       <c r="B21" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="D21" s="50" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="48">
         <v>1</v>
       </c>
       <c r="B22" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="C22" s="50" t="s">
+      <c r="C22" s="47" t="s">
+        <v>800</v>
+      </c>
+      <c r="D22" s="50" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="48">
         <v>1</v>
       </c>
       <c r="B23" s="47" t="s">
         <v>171</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="D23" s="50" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="48">
         <v>1</v>
       </c>
       <c r="B24" s="47" t="s">
         <v>229</v>
       </c>
-      <c r="C24" s="50" t="s">
+      <c r="C24" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="D24" s="50" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="48">
         <v>1</v>
       </c>
       <c r="B25" s="47" t="s">
         <v>175</v>
       </c>
-      <c r="C25" s="50" t="s">
+      <c r="C25" s="47" t="s">
+        <v>801</v>
+      </c>
+      <c r="D25" s="50" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="48">
         <v>1</v>
       </c>
       <c r="B26" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="C26" s="50" t="s">
+      <c r="C26" s="47" t="s">
+        <v>156</v>
+      </c>
+      <c r="D26" s="50" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="48">
         <v>1</v>
       </c>
       <c r="B27" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="50" t="s">
+      <c r="C27" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" s="50" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="48">
         <v>1</v>
       </c>
       <c r="B28" s="47" t="s">
         <v>273</v>
       </c>
-      <c r="C28" s="50" t="s">
+      <c r="C28" s="47" t="s">
+        <v>273</v>
+      </c>
+      <c r="D28" s="50" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="48">
         <v>1</v>
       </c>
       <c r="B29" s="47" t="s">
         <v>205</v>
       </c>
-      <c r="C29" s="50" t="s">
+      <c r="C29" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="D29" s="50" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="48">
         <v>1</v>
       </c>
       <c r="B30" s="47" t="s">
         <v>169</v>
       </c>
-      <c r="C30" s="50" t="s">
+      <c r="C30" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="D30" s="50" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="48">
         <v>1</v>
       </c>
       <c r="B31" s="47" t="s">
         <v>214</v>
       </c>
-      <c r="C31" s="50" t="s">
+      <c r="C31" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="D31" s="50" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="48">
         <v>1</v>
       </c>
       <c r="B32" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="50" t="s">
+      <c r="C32" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="50" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="48">
         <v>1</v>
       </c>
       <c r="B33" s="47" t="s">
         <v>217</v>
       </c>
-      <c r="C33" s="50" t="s">
+      <c r="C33" s="47" t="s">
+        <v>217</v>
+      </c>
+      <c r="D33" s="50" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="48">
         <v>1</v>
       </c>
       <c r="B34" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="50" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="48">
         <v>1</v>
       </c>
       <c r="B35" s="47" t="s">
         <v>179</v>
       </c>
-      <c r="C35" s="50" t="s">
+      <c r="C35" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="D35" s="50" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="48">
         <v>1</v>
       </c>
       <c r="B36" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="C36" s="50" t="s">
+      <c r="C36" s="47" t="s">
+        <v>802</v>
+      </c>
+      <c r="D36" s="50" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="48">
         <v>1</v>
       </c>
       <c r="B37" s="47" t="s">
         <v>210</v>
       </c>
-      <c r="C37" s="50" t="s">
+      <c r="C37" s="47" t="s">
+        <v>210</v>
+      </c>
+      <c r="D37" s="50" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="48">
         <v>1</v>
       </c>
       <c r="B38" s="47" t="s">
         <v>255</v>
       </c>
-      <c r="C38" s="50" t="s">
+      <c r="C38" s="47" t="s">
+        <v>803</v>
+      </c>
+      <c r="D38" s="50" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="48">
         <v>1</v>
       </c>
       <c r="B39" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="C39" s="50" t="s">
+      <c r="C39" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="D39" s="50" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="48">
         <v>1</v>
       </c>
       <c r="B40" s="47" t="s">
         <v>183</v>
       </c>
-      <c r="C40" s="50" t="s">
+      <c r="C40" s="47" t="s">
+        <v>183</v>
+      </c>
+      <c r="D40" s="50" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="48">
         <v>1</v>
       </c>
       <c r="B41" s="47" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="50" t="s">
+      <c r="C41" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="D41" s="50" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="48">
         <v>1</v>
       </c>
       <c r="B42" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="C42" s="50" t="s">
+      <c r="C42" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="D42" s="50" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="48">
         <v>1</v>
       </c>
       <c r="B43" s="47" t="s">
         <v>188</v>
       </c>
-      <c r="C43" s="50" t="s">
+      <c r="C43" s="47" t="s">
+        <v>804</v>
+      </c>
+      <c r="D43" s="50" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="48">
         <v>1</v>
       </c>
       <c r="B44" s="47" t="s">
         <v>190</v>
       </c>
-      <c r="C44" s="50" t="s">
+      <c r="C44" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="D44" s="50" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="48">
         <v>1</v>
       </c>
       <c r="B45" s="47" t="s">
         <v>192</v>
       </c>
-      <c r="C45" s="50" t="s">
+      <c r="C45" s="47" t="s">
+        <v>192</v>
+      </c>
+      <c r="D45" s="50" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="48">
         <v>1</v>
       </c>
       <c r="B46" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="C46" s="50" t="s">
+      <c r="C46" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="D46" s="50" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="48">
         <v>1</v>
       </c>
       <c r="B47" s="47" t="s">
         <v>196</v>
       </c>
-      <c r="C47" s="50" t="s">
+      <c r="C47" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="D47" s="50" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="48">
         <v>1</v>
       </c>
       <c r="B48" s="47" t="s">
         <v>198</v>
       </c>
-      <c r="C48" s="50" t="s">
+      <c r="C48" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="D48" s="50" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="48">
         <v>1</v>
       </c>
       <c r="B49" s="47" t="s">
         <v>200</v>
       </c>
-      <c r="C49" s="50" t="s">
+      <c r="C49" s="47" t="s">
+        <v>200</v>
+      </c>
+      <c r="D49" s="50" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="48">
         <v>1</v>
       </c>
       <c r="B50" s="47" t="s">
         <v>194</v>
       </c>
-      <c r="C50" s="50" t="s">
+      <c r="C50" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="D50" s="50" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="48">
         <v>1</v>
       </c>
       <c r="B51" s="47" t="s">
         <v>203</v>
       </c>
-      <c r="C51" s="50" t="s">
+      <c r="C51" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="D51" s="50" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="48">
         <v>1</v>
       </c>
       <c r="B52" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="C52" s="50" t="s">
+      <c r="C52" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="D52" s="50" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="48">
         <v>1</v>
       </c>
       <c r="B53" s="47" t="s">
         <v>207</v>
       </c>
-      <c r="C53" s="50" t="s">
+      <c r="C53" s="47" t="s">
+        <v>207</v>
+      </c>
+      <c r="D53" s="50" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="48">
         <v>1</v>
       </c>
       <c r="B54" s="47" t="s">
         <v>236</v>
       </c>
-      <c r="C54" s="50" t="s">
+      <c r="C54" s="47" t="s">
+        <v>236</v>
+      </c>
+      <c r="D54" s="50" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="48">
         <v>1</v>
       </c>
       <c r="B55" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="C55" s="50" t="s">
+      <c r="C55" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="D55" s="50" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="48">
         <v>1</v>
       </c>
       <c r="B56" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="C56" s="50" t="s">
+      <c r="C56" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="D56" s="50" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="48">
         <v>1</v>
       </c>
       <c r="B57" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="C57" s="50" t="s">
+      <c r="C57" s="49" t="s">
+        <v>805</v>
+      </c>
+      <c r="D57" s="50" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="48">
         <v>1</v>
       </c>
       <c r="B58" s="49" t="s">
         <v>221</v>
       </c>
-      <c r="C58" s="50" t="s">
+      <c r="C58" s="49" t="s">
+        <v>806</v>
+      </c>
+      <c r="D58" s="50" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="48">
         <v>1</v>
       </c>
       <c r="B59" s="49" t="s">
         <v>223</v>
       </c>
-      <c r="C59" s="50" t="s">
+      <c r="C59" s="49" t="s">
+        <v>807</v>
+      </c>
+      <c r="D59" s="50" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="48">
         <v>1</v>
       </c>
       <c r="B60" s="49" t="s">
         <v>225</v>
       </c>
-      <c r="C60" s="50" t="s">
+      <c r="C60" s="49" t="s">
+        <v>808</v>
+      </c>
+      <c r="D60" s="50" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="48">
         <v>1</v>
       </c>
       <c r="B61" s="49" t="s">
         <v>239</v>
       </c>
-      <c r="C61" s="50" t="s">
+      <c r="C61" s="49" t="s">
+        <v>809</v>
+      </c>
+      <c r="D61" s="50" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="48">
         <v>1</v>
       </c>
       <c r="B62" s="49" t="s">
         <v>241</v>
       </c>
-      <c r="C62" s="50" t="s">
+      <c r="C62" s="49" t="s">
+        <v>241</v>
+      </c>
+      <c r="D62" s="50" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="48">
         <v>1</v>
       </c>
       <c r="B63" s="49" t="s">
         <v>243</v>
       </c>
-      <c r="C63" s="50" t="s">
+      <c r="C63" s="49" t="s">
+        <v>810</v>
+      </c>
+      <c r="D63" s="50" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="48">
         <v>1</v>
       </c>
       <c r="B64" s="49" t="s">
         <v>245</v>
       </c>
-      <c r="C64" s="50" t="s">
+      <c r="C64" s="49" t="s">
+        <v>811</v>
+      </c>
+      <c r="D64" s="50" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="48">
         <v>1</v>
       </c>
       <c r="B65" s="49" t="s">
         <v>247</v>
       </c>
-      <c r="C65" s="50" t="s">
+      <c r="C65" s="49" t="s">
+        <v>812</v>
+      </c>
+      <c r="D65" s="50" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="48">
         <v>1</v>
       </c>
       <c r="B66" s="49" t="s">
         <v>249</v>
       </c>
-      <c r="C66" s="50" t="s">
+      <c r="C66" s="49" t="s">
+        <v>813</v>
+      </c>
+      <c r="D66" s="50" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="48">
         <v>1</v>
       </c>
       <c r="B67" s="49" t="s">
         <v>251</v>
       </c>
-      <c r="C67" s="50" t="s">
+      <c r="C67" s="49" t="s">
+        <v>814</v>
+      </c>
+      <c r="D67" s="50" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="48">
         <v>1</v>
       </c>
       <c r="B68" s="49" t="s">
         <v>253</v>
       </c>
-      <c r="C68" s="50" t="s">
+      <c r="C68" s="49" t="s">
+        <v>253</v>
+      </c>
+      <c r="D68" s="50" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="48">
         <v>1</v>
       </c>
       <c r="B69" s="49" t="s">
         <v>257</v>
       </c>
-      <c r="C69" s="50" t="s">
+      <c r="C69" s="49" t="s">
+        <v>815</v>
+      </c>
+      <c r="D69" s="50" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="48">
         <v>1</v>
       </c>
       <c r="B70" s="49" t="s">
         <v>259</v>
       </c>
-      <c r="C70" s="50" t="s">
+      <c r="C70" s="49" t="s">
+        <v>259</v>
+      </c>
+      <c r="D70" s="50" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="48">
         <v>1</v>
       </c>
       <c r="B71" s="49" t="s">
         <v>261</v>
       </c>
-      <c r="C71" s="50" t="s">
+      <c r="C71" s="49" t="s">
+        <v>816</v>
+      </c>
+      <c r="D71" s="50" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="48">
         <v>1</v>
       </c>
       <c r="B72" s="49" t="s">
         <v>263</v>
       </c>
-      <c r="C72" s="50" t="s">
+      <c r="C72" s="49" t="s">
+        <v>817</v>
+      </c>
+      <c r="D72" s="50" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="48">
         <v>2</v>
       </c>
       <c r="B73" s="48" t="s">
         <v>279</v>
       </c>
-      <c r="C73" s="53" t="s">
+      <c r="C73" s="48" t="s">
+        <v>279</v>
+      </c>
+      <c r="D73" s="53" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="48">
         <v>2</v>
       </c>
       <c r="B74" s="48" t="s">
         <v>281</v>
       </c>
-      <c r="C74" s="53" t="s">
+      <c r="C74" s="48" t="s">
+        <v>281</v>
+      </c>
+      <c r="D74" s="53" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="48">
         <v>2</v>
       </c>
       <c r="B75" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="C75" s="53" t="s">
+      <c r="C75" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="D75" s="53" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="48">
         <v>2</v>
       </c>
       <c r="B76" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="C76" s="53" t="s">
+      <c r="C76" s="48" t="s">
+        <v>283</v>
+      </c>
+      <c r="D76" s="53" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="48">
         <v>2</v>
       </c>
       <c r="B77" s="48" t="s">
         <v>323</v>
       </c>
-      <c r="C77" s="53" t="s">
+      <c r="C77" s="48" t="s">
+        <v>818</v>
+      </c>
+      <c r="D77" s="53" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="48">
         <v>2</v>
       </c>
       <c r="B78" s="48" t="s">
         <v>285</v>
       </c>
-      <c r="C78" s="53" t="s">
+      <c r="C78" s="48" t="s">
+        <v>819</v>
+      </c>
+      <c r="D78" s="53" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="48">
         <v>2</v>
       </c>
       <c r="B79" s="48" t="s">
         <v>287</v>
       </c>
-      <c r="C79" s="53" t="s">
+      <c r="C79" s="48" t="s">
+        <v>287</v>
+      </c>
+      <c r="D79" s="53" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="48">
         <v>2</v>
       </c>
       <c r="B80" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="C80" s="53" t="s">
+      <c r="C80" s="48" t="s">
+        <v>820</v>
+      </c>
+      <c r="D80" s="53" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="48">
         <v>2</v>
       </c>
       <c r="B81" s="48" t="s">
         <v>289</v>
       </c>
-      <c r="C81" s="53" t="s">
+      <c r="C81" s="48" t="s">
+        <v>289</v>
+      </c>
+      <c r="D81" s="53" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="48">
         <v>2</v>
       </c>
       <c r="B82" s="48" t="s">
         <v>291</v>
       </c>
-      <c r="C82" s="53" t="s">
+      <c r="C82" s="48" t="s">
+        <v>291</v>
+      </c>
+      <c r="D82" s="53" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="48">
         <v>2</v>
       </c>
       <c r="B83" s="48" t="s">
         <v>293</v>
       </c>
-      <c r="C83" s="53" t="s">
+      <c r="C83" s="48" t="s">
+        <v>293</v>
+      </c>
+      <c r="D83" s="53" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="48">
         <v>2</v>
       </c>
       <c r="B84" s="48" t="s">
         <v>295</v>
       </c>
-      <c r="C84" s="53" t="s">
+      <c r="C84" s="48" t="s">
+        <v>295</v>
+      </c>
+      <c r="D84" s="53" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="48">
         <v>2</v>
       </c>
       <c r="B85" s="48" t="s">
         <v>297</v>
       </c>
-      <c r="C85" s="53" t="s">
+      <c r="C85" s="48" t="s">
+        <v>297</v>
+      </c>
+      <c r="D85" s="53" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="48">
         <v>2</v>
       </c>
       <c r="B86" s="48" t="s">
         <v>300</v>
       </c>
-      <c r="C86" s="53" t="s">
+      <c r="C86" s="48" t="s">
+        <v>300</v>
+      </c>
+      <c r="D86" s="53" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="48">
         <v>2</v>
       </c>
       <c r="B87" s="48" t="s">
         <v>301</v>
       </c>
-      <c r="C87" s="53" t="s">
+      <c r="C87" s="48" t="s">
+        <v>821</v>
+      </c>
+      <c r="D87" s="53" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="48">
         <v>2</v>
       </c>
       <c r="B88" s="48" t="s">
         <v>303</v>
       </c>
-      <c r="C88" s="53" t="s">
+      <c r="C88" s="48" t="s">
+        <v>822</v>
+      </c>
+      <c r="D88" s="53" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="48">
         <v>2</v>
       </c>
       <c r="B89" s="48" t="s">
         <v>305</v>
       </c>
-      <c r="C89" s="53" t="s">
+      <c r="C89" s="48" t="s">
+        <v>305</v>
+      </c>
+      <c r="D89" s="53" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="48">
         <v>2</v>
       </c>
       <c r="B90" s="48" t="s">
         <v>307</v>
       </c>
-      <c r="C90" s="53" t="s">
+      <c r="C90" s="48" t="s">
+        <v>307</v>
+      </c>
+      <c r="D90" s="53" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="48">
         <v>2</v>
       </c>
       <c r="B91" s="48" t="s">
         <v>310</v>
       </c>
-      <c r="C91" s="53" t="s">
+      <c r="C91" s="48" t="s">
+        <v>823</v>
+      </c>
+      <c r="D91" s="53" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="48">
         <v>2</v>
       </c>
       <c r="B92" s="48" t="s">
         <v>312</v>
       </c>
-      <c r="C92" s="53" t="s">
+      <c r="C92" s="48" t="s">
+        <v>312</v>
+      </c>
+      <c r="D92" s="53" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="48">
         <v>2</v>
       </c>
       <c r="B93" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="C93" s="53" t="s">
+      <c r="C93" s="48" t="s">
+        <v>314</v>
+      </c>
+      <c r="D93" s="53" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="48">
         <v>2</v>
       </c>
       <c r="B94" s="48" t="s">
         <v>327</v>
       </c>
-      <c r="C94" s="53" t="s">
+      <c r="C94" s="48" t="s">
+        <v>327</v>
+      </c>
+      <c r="D94" s="53" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="48">
         <v>2</v>
       </c>
       <c r="B95" s="48" t="s">
         <v>316</v>
       </c>
-      <c r="C95" s="53" t="s">
+      <c r="C95" s="48" t="s">
+        <v>316</v>
+      </c>
+      <c r="D95" s="53" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="48">
         <v>2</v>
       </c>
       <c r="B96" s="48" t="s">
         <v>318</v>
       </c>
-      <c r="C96" s="53" t="s">
+      <c r="C96" s="48" t="s">
+        <v>824</v>
+      </c>
+      <c r="D96" s="53" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="48">
         <v>2</v>
       </c>
       <c r="B97" s="48" t="s">
         <v>320</v>
       </c>
-      <c r="C97" s="53" t="s">
+      <c r="C97" s="48" t="s">
+        <v>320</v>
+      </c>
+      <c r="D97" s="53" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="48">
         <v>2</v>
       </c>
       <c r="B98" s="48" t="s">
         <v>337</v>
       </c>
-      <c r="C98" s="53" t="s">
+      <c r="C98" s="48" t="s">
+        <v>337</v>
+      </c>
+      <c r="D98" s="53" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="48">
         <v>2</v>
       </c>
       <c r="B99" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="C99" s="53" t="s">
+      <c r="C99" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="D99" s="53" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="48">
         <v>2</v>
       </c>
       <c r="B100" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="C100" s="53" t="s">
+      <c r="C100" s="48" t="s">
+        <v>825</v>
+      </c>
+      <c r="D100" s="53" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="48">
         <v>2</v>
       </c>
       <c r="B101" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="C101" s="53" t="s">
+      <c r="C101" s="48" t="s">
+        <v>826</v>
+      </c>
+      <c r="D101" s="53" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="48">
         <v>2</v>
       </c>
@@ -4509,241 +5196,307 @@
         <v>343</v>
       </c>
       <c r="C102" s="48" t="s">
+        <v>827</v>
+      </c>
+      <c r="D102" s="48" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="48">
         <v>2</v>
       </c>
       <c r="B103" s="48" t="s">
         <v>342</v>
       </c>
-      <c r="C103" s="53" t="s">
+      <c r="C103" s="48" t="s">
+        <v>342</v>
+      </c>
+      <c r="D103" s="53" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="48">
         <v>2</v>
       </c>
       <c r="B104" s="48" t="s">
         <v>329</v>
       </c>
-      <c r="C104" s="53" t="s">
+      <c r="C104" s="48" t="s">
+        <v>329</v>
+      </c>
+      <c r="D104" s="53" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="48">
         <v>2</v>
       </c>
       <c r="B105" s="48" t="s">
         <v>331</v>
       </c>
-      <c r="C105" s="53" t="s">
+      <c r="C105" s="48" t="s">
+        <v>331</v>
+      </c>
+      <c r="D105" s="53" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="48">
         <v>2</v>
       </c>
       <c r="B106" s="48" t="s">
         <v>333</v>
       </c>
-      <c r="C106" s="53" t="s">
+      <c r="C106" s="48" t="s">
+        <v>333</v>
+      </c>
+      <c r="D106" s="53" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="48">
         <v>2</v>
       </c>
       <c r="B107" s="48" t="s">
         <v>335</v>
       </c>
-      <c r="C107" s="53" t="s">
+      <c r="C107" s="48" t="s">
+        <v>335</v>
+      </c>
+      <c r="D107" s="53" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="48">
         <v>2</v>
       </c>
       <c r="B108" s="48" t="s">
         <v>346</v>
       </c>
-      <c r="C108" s="53" t="s">
+      <c r="C108" s="48" t="s">
+        <v>828</v>
+      </c>
+      <c r="D108" s="53" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="48">
         <v>2</v>
       </c>
       <c r="B109" s="48" t="s">
         <v>348</v>
       </c>
-      <c r="C109" s="53" t="s">
+      <c r="C109" s="48" t="s">
+        <v>829</v>
+      </c>
+      <c r="D109" s="53" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="48">
         <v>2</v>
       </c>
       <c r="B110" s="48" t="s">
         <v>350</v>
       </c>
-      <c r="C110" s="53" t="s">
+      <c r="C110" s="48" t="s">
+        <v>350</v>
+      </c>
+      <c r="D110" s="53" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="48">
         <v>2</v>
       </c>
       <c r="B111" s="48" t="s">
         <v>352</v>
       </c>
-      <c r="C111" s="53" t="s">
+      <c r="C111" s="48" t="s">
+        <v>352</v>
+      </c>
+      <c r="D111" s="53" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="48">
         <v>2</v>
       </c>
       <c r="B112" s="48" t="s">
         <v>356</v>
       </c>
-      <c r="C112" s="53" t="s">
+      <c r="C112" s="48" t="s">
+        <v>830</v>
+      </c>
+      <c r="D112" s="53" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="48">
         <v>2</v>
       </c>
       <c r="B113" s="48" t="s">
         <v>354</v>
       </c>
-      <c r="C113" s="53" t="s">
+      <c r="C113" s="48" t="s">
+        <v>354</v>
+      </c>
+      <c r="D113" s="53" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="48">
         <v>2</v>
       </c>
       <c r="B114" s="48" t="s">
         <v>358</v>
       </c>
-      <c r="C114" s="53" t="s">
+      <c r="C114" s="48" t="s">
+        <v>831</v>
+      </c>
+      <c r="D114" s="53" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="48">
         <v>2</v>
       </c>
       <c r="B115" s="48" t="s">
         <v>360</v>
       </c>
-      <c r="C115" s="53" t="s">
+      <c r="C115" s="48" t="s">
+        <v>360</v>
+      </c>
+      <c r="D115" s="53" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="48">
         <v>2</v>
       </c>
       <c r="B116" s="48" t="s">
         <v>362</v>
       </c>
-      <c r="C116" s="53" t="s">
+      <c r="C116" s="48" t="s">
+        <v>832</v>
+      </c>
+      <c r="D116" s="53" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="48">
         <v>2</v>
       </c>
       <c r="B117" s="48" t="s">
         <v>364</v>
       </c>
-      <c r="C117" s="53" t="s">
+      <c r="C117" s="48" t="s">
+        <v>833</v>
+      </c>
+      <c r="D117" s="53" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="48">
         <v>2</v>
       </c>
       <c r="B118" s="48" t="s">
         <v>370</v>
       </c>
-      <c r="C118" s="53" t="s">
+      <c r="C118" s="48" t="s">
+        <v>834</v>
+      </c>
+      <c r="D118" s="53" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="48">
         <v>2</v>
       </c>
       <c r="B119" s="48" t="s">
         <v>366</v>
       </c>
-      <c r="C119" s="53" t="s">
+      <c r="C119" s="48" t="s">
+        <v>835</v>
+      </c>
+      <c r="D119" s="53" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="48">
         <v>2</v>
       </c>
       <c r="B120" s="48" t="s">
         <v>368</v>
       </c>
-      <c r="C120" s="53" t="s">
+      <c r="C120" s="48" t="s">
+        <v>368</v>
+      </c>
+      <c r="D120" s="53" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="48">
         <v>2</v>
       </c>
       <c r="B121" s="48" t="s">
         <v>372</v>
       </c>
-      <c r="C121" s="53" t="s">
+      <c r="C121" s="48" t="s">
+        <v>836</v>
+      </c>
+      <c r="D121" s="53" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="48">
         <v>2</v>
       </c>
       <c r="B122" s="48" t="s">
         <v>374</v>
       </c>
-      <c r="C122" s="53" t="s">
+      <c r="C122" s="48" t="s">
+        <v>374</v>
+      </c>
+      <c r="D122" s="53" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="48">
         <v>2</v>
       </c>
       <c r="B123" s="48" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="53" t="s">
+      <c r="C123" s="48" t="s">
+        <v>837</v>
+      </c>
+      <c r="D123" s="53" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="48">
         <v>3</v>
       </c>
@@ -4751,10 +5504,13 @@
         <v>379</v>
       </c>
       <c r="C124" t="s">
+        <v>838</v>
+      </c>
+      <c r="D124" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="48">
         <v>3</v>
       </c>
@@ -4762,10 +5518,13 @@
         <v>381</v>
       </c>
       <c r="C125" t="s">
+        <v>381</v>
+      </c>
+      <c r="D125" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="48">
         <v>3</v>
       </c>
@@ -4773,10 +5532,13 @@
         <v>383</v>
       </c>
       <c r="C126" t="s">
+        <v>383</v>
+      </c>
+      <c r="D126" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="48">
         <v>3</v>
       </c>
@@ -4784,10 +5546,13 @@
         <v>385</v>
       </c>
       <c r="C127" t="s">
+        <v>385</v>
+      </c>
+      <c r="D127" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="48">
         <v>3</v>
       </c>
@@ -4795,10 +5560,13 @@
         <v>387</v>
       </c>
       <c r="C128" t="s">
+        <v>839</v>
+      </c>
+      <c r="D128" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="48">
         <v>3</v>
       </c>
@@ -4806,10 +5574,13 @@
         <v>389</v>
       </c>
       <c r="C129" t="s">
+        <v>389</v>
+      </c>
+      <c r="D129" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="48">
         <v>3</v>
       </c>
@@ -4817,10 +5588,13 @@
         <v>391</v>
       </c>
       <c r="C130" t="s">
+        <v>391</v>
+      </c>
+      <c r="D130" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="48">
         <v>3</v>
       </c>
@@ -4828,10 +5602,13 @@
         <v>393</v>
       </c>
       <c r="C131" t="s">
+        <v>840</v>
+      </c>
+      <c r="D131" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="48">
         <v>3</v>
       </c>
@@ -4839,10 +5616,13 @@
         <v>395</v>
       </c>
       <c r="C132" t="s">
+        <v>841</v>
+      </c>
+      <c r="D132" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="48">
         <v>3</v>
       </c>
@@ -4850,10 +5630,13 @@
         <v>397</v>
       </c>
       <c r="C133" t="s">
+        <v>397</v>
+      </c>
+      <c r="D133" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="48">
         <v>3</v>
       </c>
@@ -4861,10 +5644,13 @@
         <v>399</v>
       </c>
       <c r="C134" t="s">
+        <v>842</v>
+      </c>
+      <c r="D134" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="48">
         <v>3</v>
       </c>
@@ -4872,10 +5658,13 @@
         <v>401</v>
       </c>
       <c r="C135" t="s">
+        <v>401</v>
+      </c>
+      <c r="D135" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="48">
         <v>3</v>
       </c>
@@ -4883,10 +5672,13 @@
         <v>403</v>
       </c>
       <c r="C136" t="s">
+        <v>403</v>
+      </c>
+      <c r="D136" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="48">
         <v>3</v>
       </c>
@@ -4894,10 +5686,13 @@
         <v>405</v>
       </c>
       <c r="C137" t="s">
+        <v>405</v>
+      </c>
+      <c r="D137" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="48">
         <v>3</v>
       </c>
@@ -4905,10 +5700,13 @@
         <v>407</v>
       </c>
       <c r="C138" t="s">
+        <v>843</v>
+      </c>
+      <c r="D138" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="48">
         <v>3</v>
       </c>
@@ -4916,10 +5714,13 @@
         <v>409</v>
       </c>
       <c r="C139" t="s">
+        <v>844</v>
+      </c>
+      <c r="D139" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="48">
         <v>3</v>
       </c>
@@ -4927,10 +5728,13 @@
         <v>411</v>
       </c>
       <c r="C140" t="s">
+        <v>411</v>
+      </c>
+      <c r="D140" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="48">
         <v>3</v>
       </c>
@@ -4938,10 +5742,13 @@
         <v>414</v>
       </c>
       <c r="C141" t="s">
+        <v>414</v>
+      </c>
+      <c r="D141" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="48">
         <v>3</v>
       </c>
@@ -4949,10 +5756,13 @@
         <v>417</v>
       </c>
       <c r="C142" t="s">
+        <v>845</v>
+      </c>
+      <c r="D142" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="48">
         <v>3</v>
       </c>
@@ -4960,10 +5770,13 @@
         <v>419</v>
       </c>
       <c r="C143" t="s">
+        <v>846</v>
+      </c>
+      <c r="D143" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="48">
         <v>3</v>
       </c>
@@ -4971,10 +5784,13 @@
         <v>421</v>
       </c>
       <c r="C144" t="s">
+        <v>421</v>
+      </c>
+      <c r="D144" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="48">
         <v>3</v>
       </c>
@@ -4982,10 +5798,13 @@
         <v>209</v>
       </c>
       <c r="C145" t="s">
+        <v>209</v>
+      </c>
+      <c r="D145" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="48">
         <v>3</v>
       </c>
@@ -4993,10 +5812,13 @@
         <v>423</v>
       </c>
       <c r="C146" t="s">
+        <v>423</v>
+      </c>
+      <c r="D146" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="48">
         <v>3</v>
       </c>
@@ -5004,10 +5826,13 @@
         <v>425</v>
       </c>
       <c r="C147" t="s">
+        <v>425</v>
+      </c>
+      <c r="D147" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="48">
         <v>3</v>
       </c>
@@ -5015,21 +5840,27 @@
         <v>427</v>
       </c>
       <c r="C148" t="s">
+        <v>427</v>
+      </c>
+      <c r="D148" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="48">
         <v>3</v>
       </c>
       <c r="B149" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C149" t="s">
+        <v>715</v>
+      </c>
+      <c r="D149" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="48">
         <v>3</v>
       </c>
@@ -5037,10 +5868,13 @@
         <v>430</v>
       </c>
       <c r="C150" t="s">
+        <v>430</v>
+      </c>
+      <c r="D150" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="48">
         <v>3</v>
       </c>
@@ -5048,21 +5882,27 @@
         <v>432</v>
       </c>
       <c r="C151" t="s">
+        <v>847</v>
+      </c>
+      <c r="D151" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="48">
         <v>3</v>
       </c>
       <c r="B152" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="C152" s="53" t="s">
+      <c r="C152" s="48" t="s">
+        <v>848</v>
+      </c>
+      <c r="D152" s="53" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="48">
         <v>3</v>
       </c>
@@ -5070,10 +5910,13 @@
         <v>435</v>
       </c>
       <c r="C153" s="44" t="s">
+        <v>435</v>
+      </c>
+      <c r="D153" s="44" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="48">
         <v>3</v>
       </c>
@@ -5081,21 +5924,27 @@
         <v>436</v>
       </c>
       <c r="C154" s="44" t="s">
+        <v>436</v>
+      </c>
+      <c r="D154" s="44" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="48">
         <v>3</v>
       </c>
       <c r="B155" s="51" t="s">
         <v>439</v>
       </c>
-      <c r="C155" s="44" t="s">
+      <c r="C155" s="51" t="s">
+        <v>439</v>
+      </c>
+      <c r="D155" s="44" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="48">
         <v>3</v>
       </c>
@@ -5103,10 +5952,13 @@
         <v>322</v>
       </c>
       <c r="C156" s="44" t="s">
+        <v>322</v>
+      </c>
+      <c r="D156" s="44" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="48">
         <v>3</v>
       </c>
@@ -5114,10 +5966,13 @@
         <v>44</v>
       </c>
       <c r="C157" s="44" t="s">
+        <v>849</v>
+      </c>
+      <c r="D157" s="44" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="48">
         <v>3</v>
       </c>
@@ -5125,10 +5980,13 @@
         <v>145</v>
       </c>
       <c r="C158" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="D158" s="44" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="48">
         <v>3</v>
       </c>
@@ -5136,10 +5994,13 @@
         <v>160</v>
       </c>
       <c r="C159" s="44" t="s">
+        <v>160</v>
+      </c>
+      <c r="D159" s="44" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="48">
         <v>3</v>
       </c>
@@ -5147,10 +6008,13 @@
         <v>440</v>
       </c>
       <c r="C160" t="s">
+        <v>850</v>
+      </c>
+      <c r="D160" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="48">
         <v>3</v>
       </c>
@@ -5158,10 +6022,13 @@
         <v>442</v>
       </c>
       <c r="C161" t="s">
+        <v>851</v>
+      </c>
+      <c r="D161" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="48">
         <v>3</v>
       </c>
@@ -5169,10 +6036,13 @@
         <v>445</v>
       </c>
       <c r="C162" t="s">
+        <v>852</v>
+      </c>
+      <c r="D162" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="48">
         <v>3</v>
       </c>
@@ -5180,10 +6050,13 @@
         <v>447</v>
       </c>
       <c r="C163" t="s">
+        <v>853</v>
+      </c>
+      <c r="D163" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="48">
         <v>3</v>
       </c>
@@ -5191,10 +6064,13 @@
         <v>449</v>
       </c>
       <c r="C164" t="s">
+        <v>854</v>
+      </c>
+      <c r="D164" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="48">
         <v>3</v>
       </c>
@@ -5202,10 +6078,13 @@
         <v>451</v>
       </c>
       <c r="C165" t="s">
+        <v>855</v>
+      </c>
+      <c r="D165" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="48">
         <v>3</v>
       </c>
@@ -5213,10 +6092,13 @@
         <v>453</v>
       </c>
       <c r="C166" t="s">
+        <v>453</v>
+      </c>
+      <c r="D166" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="48">
         <v>3</v>
       </c>
@@ -5224,10 +6106,13 @@
         <v>455</v>
       </c>
       <c r="C167" t="s">
+        <v>856</v>
+      </c>
+      <c r="D167" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="48">
         <v>3</v>
       </c>
@@ -5235,10 +6120,13 @@
         <v>459</v>
       </c>
       <c r="C168" t="s">
+        <v>857</v>
+      </c>
+      <c r="D168" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="48">
         <v>3</v>
       </c>
@@ -5246,10 +6134,13 @@
         <v>457</v>
       </c>
       <c r="C169" t="s">
+        <v>858</v>
+      </c>
+      <c r="D169" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="48">
         <v>3</v>
       </c>
@@ -5257,10 +6148,13 @@
         <v>461</v>
       </c>
       <c r="C170" t="s">
+        <v>461</v>
+      </c>
+      <c r="D170" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="48">
         <v>3</v>
       </c>
@@ -5268,10 +6162,13 @@
         <v>467</v>
       </c>
       <c r="C171" t="s">
+        <v>467</v>
+      </c>
+      <c r="D171" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="48">
         <v>3</v>
       </c>
@@ -5279,10 +6176,13 @@
         <v>463</v>
       </c>
       <c r="C172" t="s">
+        <v>463</v>
+      </c>
+      <c r="D172" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="48">
         <v>3</v>
       </c>
@@ -5290,10 +6190,13 @@
         <v>465</v>
       </c>
       <c r="C173" t="s">
+        <v>465</v>
+      </c>
+      <c r="D173" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="48">
         <v>3</v>
       </c>
@@ -5301,10 +6204,13 @@
         <v>469</v>
       </c>
       <c r="C174" t="s">
+        <v>859</v>
+      </c>
+      <c r="D174" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="48">
         <v>3</v>
       </c>
@@ -5312,76 +6218,97 @@
         <v>471</v>
       </c>
       <c r="C175" t="s">
+        <v>860</v>
+      </c>
+      <c r="D175" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="48">
         <v>3</v>
       </c>
       <c r="B176" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C176" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>861</v>
+      </c>
+      <c r="D176" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="48">
         <v>3</v>
       </c>
       <c r="B177" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C177" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>862</v>
+      </c>
+      <c r="D177" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="48">
         <v>3</v>
       </c>
       <c r="B178" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C178" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>736</v>
+      </c>
+      <c r="D178" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="48">
         <v>3</v>
       </c>
       <c r="B179" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C179" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>863</v>
+      </c>
+      <c r="D179" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="48">
         <v>3</v>
       </c>
       <c r="B180" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C180" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>740</v>
+      </c>
+      <c r="D180" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="48">
         <v>3</v>
       </c>
       <c r="B181" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C181" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>864</v>
+      </c>
+      <c r="D181" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="48">
         <v>4</v>
       </c>
@@ -5389,10 +6316,13 @@
         <v>473</v>
       </c>
       <c r="C182" t="s">
+        <v>473</v>
+      </c>
+      <c r="D182" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="48">
         <v>4</v>
       </c>
@@ -5400,10 +6330,13 @@
         <v>475</v>
       </c>
       <c r="C183" t="s">
+        <v>475</v>
+      </c>
+      <c r="D183" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="48">
         <v>4</v>
       </c>
@@ -5411,10 +6344,13 @@
         <v>477</v>
       </c>
       <c r="C184" t="s">
+        <v>477</v>
+      </c>
+      <c r="D184" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="48">
         <v>4</v>
       </c>
@@ -5422,10 +6358,13 @@
         <v>479</v>
       </c>
       <c r="C185" t="s">
+        <v>479</v>
+      </c>
+      <c r="D185" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="48">
         <v>4</v>
       </c>
@@ -5433,10 +6372,13 @@
         <v>481</v>
       </c>
       <c r="C186" t="s">
+        <v>481</v>
+      </c>
+      <c r="D186" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="48">
         <v>4</v>
       </c>
@@ -5444,10 +6386,13 @@
         <v>483</v>
       </c>
       <c r="C187" t="s">
+        <v>483</v>
+      </c>
+      <c r="D187" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="48">
         <v>4</v>
       </c>
@@ -5455,10 +6400,13 @@
         <v>485</v>
       </c>
       <c r="C188" t="s">
+        <v>485</v>
+      </c>
+      <c r="D188" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="48">
         <v>4</v>
       </c>
@@ -5466,10 +6414,13 @@
         <v>487</v>
       </c>
       <c r="C189" t="s">
+        <v>487</v>
+      </c>
+      <c r="D189" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="48">
         <v>4</v>
       </c>
@@ -5477,10 +6428,13 @@
         <v>489</v>
       </c>
       <c r="C190" t="s">
+        <v>865</v>
+      </c>
+      <c r="D190" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="48">
         <v>4</v>
       </c>
@@ -5488,10 +6442,13 @@
         <v>491</v>
       </c>
       <c r="C191" t="s">
+        <v>866</v>
+      </c>
+      <c r="D191" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="48">
         <v>4</v>
       </c>
@@ -5499,10 +6456,13 @@
         <v>493</v>
       </c>
       <c r="C192" t="s">
+        <v>493</v>
+      </c>
+      <c r="D192" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="48">
         <v>4</v>
       </c>
@@ -5510,10 +6470,13 @@
         <v>495</v>
       </c>
       <c r="C193" t="s">
+        <v>495</v>
+      </c>
+      <c r="D193" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="48">
         <v>4</v>
       </c>
@@ -5521,10 +6484,13 @@
         <v>497</v>
       </c>
       <c r="C194" t="s">
+        <v>867</v>
+      </c>
+      <c r="D194" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="48">
         <v>4</v>
       </c>
@@ -5532,10 +6498,13 @@
         <v>499</v>
       </c>
       <c r="C195" t="s">
+        <v>868</v>
+      </c>
+      <c r="D195" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="48">
         <v>4</v>
       </c>
@@ -5543,10 +6512,13 @@
         <v>501</v>
       </c>
       <c r="C196" t="s">
+        <v>501</v>
+      </c>
+      <c r="D196" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="48">
         <v>4</v>
       </c>
@@ -5554,10 +6526,13 @@
         <v>503</v>
       </c>
       <c r="C197" t="s">
+        <v>869</v>
+      </c>
+      <c r="D197" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="48">
         <v>4</v>
       </c>
@@ -5565,10 +6540,13 @@
         <v>505</v>
       </c>
       <c r="C198" t="s">
+        <v>870</v>
+      </c>
+      <c r="D198" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="48">
         <v>4</v>
       </c>
@@ -5576,10 +6554,13 @@
         <v>507</v>
       </c>
       <c r="C199" t="s">
+        <v>507</v>
+      </c>
+      <c r="D199" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="48">
         <v>4</v>
       </c>
@@ -5587,10 +6568,13 @@
         <v>509</v>
       </c>
       <c r="C200" t="s">
+        <v>509</v>
+      </c>
+      <c r="D200" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="48">
         <v>4</v>
       </c>
@@ -5598,10 +6582,13 @@
         <v>511</v>
       </c>
       <c r="C201" t="s">
+        <v>511</v>
+      </c>
+      <c r="D201" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="48">
         <v>4</v>
       </c>
@@ -5609,10 +6596,13 @@
         <v>513</v>
       </c>
       <c r="C202" t="s">
+        <v>513</v>
+      </c>
+      <c r="D202" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="48">
         <v>4</v>
       </c>
@@ -5620,10 +6610,13 @@
         <v>515</v>
       </c>
       <c r="C203" t="s">
+        <v>515</v>
+      </c>
+      <c r="D203" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="48">
         <v>4</v>
       </c>
@@ -5631,10 +6624,13 @@
         <v>535</v>
       </c>
       <c r="C204" t="s">
+        <v>535</v>
+      </c>
+      <c r="D204" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="48">
         <v>4</v>
       </c>
@@ -5642,10 +6638,13 @@
         <v>519</v>
       </c>
       <c r="C205" t="s">
+        <v>871</v>
+      </c>
+      <c r="D205" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="48">
         <v>4</v>
       </c>
@@ -5653,10 +6652,13 @@
         <v>129</v>
       </c>
       <c r="C206" t="s">
+        <v>129</v>
+      </c>
+      <c r="D206" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="48">
         <v>4</v>
       </c>
@@ -5664,10 +6666,13 @@
         <v>522</v>
       </c>
       <c r="C207" t="s">
+        <v>872</v>
+      </c>
+      <c r="D207" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="48">
         <v>4</v>
       </c>
@@ -5675,10 +6680,13 @@
         <v>524</v>
       </c>
       <c r="C208" t="s">
+        <v>524</v>
+      </c>
+      <c r="D208" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="48">
         <v>4</v>
       </c>
@@ -5686,10 +6694,13 @@
         <v>526</v>
       </c>
       <c r="C209" t="s">
+        <v>873</v>
+      </c>
+      <c r="D209" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="48">
         <v>4</v>
       </c>
@@ -5697,10 +6708,13 @@
         <v>528</v>
       </c>
       <c r="C210" t="s">
+        <v>528</v>
+      </c>
+      <c r="D210" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A211" s="48">
         <v>4</v>
       </c>
@@ -5708,10 +6722,13 @@
         <v>530</v>
       </c>
       <c r="C211" t="s">
+        <v>874</v>
+      </c>
+      <c r="D211" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="48">
         <v>4</v>
       </c>
@@ -5719,10 +6736,13 @@
         <v>532</v>
       </c>
       <c r="C212" t="s">
+        <v>532</v>
+      </c>
+      <c r="D212" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="48">
         <v>4</v>
       </c>
@@ -5730,10 +6750,13 @@
         <v>533</v>
       </c>
       <c r="C213" t="s">
+        <v>875</v>
+      </c>
+      <c r="D213" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A214" s="48">
         <v>4</v>
       </c>
@@ -5741,10 +6764,13 @@
         <v>538</v>
       </c>
       <c r="C214" t="s">
+        <v>876</v>
+      </c>
+      <c r="D214" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A215" s="48">
         <v>4</v>
       </c>
@@ -5752,21 +6778,27 @@
         <v>541</v>
       </c>
       <c r="C215" t="s">
+        <v>541</v>
+      </c>
+      <c r="D215" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A216" s="48">
         <v>4</v>
       </c>
       <c r="B216" s="103" t="s">
-        <v>720</v>
-      </c>
-      <c r="C216" s="102" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>718</v>
+      </c>
+      <c r="C216" s="103" t="s">
+        <v>877</v>
+      </c>
+      <c r="D216" s="102" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A217" s="48">
         <v>4</v>
       </c>
@@ -5774,10 +6806,13 @@
         <v>543</v>
       </c>
       <c r="C217" t="s">
+        <v>543</v>
+      </c>
+      <c r="D217" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A218" s="48">
         <v>4</v>
       </c>
@@ -5785,10 +6820,13 @@
         <v>545</v>
       </c>
       <c r="C218" t="s">
+        <v>545</v>
+      </c>
+      <c r="D218" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="48">
         <v>4</v>
       </c>
@@ -5796,10 +6834,13 @@
         <v>549</v>
       </c>
       <c r="C219" t="s">
+        <v>878</v>
+      </c>
+      <c r="D219" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="48">
         <v>4</v>
       </c>
@@ -5807,10 +6848,13 @@
         <v>551</v>
       </c>
       <c r="C220" t="s">
+        <v>879</v>
+      </c>
+      <c r="D220" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="48">
         <v>4</v>
       </c>
@@ -5818,10 +6862,13 @@
         <v>553</v>
       </c>
       <c r="C221" t="s">
+        <v>880</v>
+      </c>
+      <c r="D221" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="48">
         <v>4</v>
       </c>
@@ -5829,10 +6876,13 @@
         <v>555</v>
       </c>
       <c r="C222" t="s">
+        <v>881</v>
+      </c>
+      <c r="D222" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="48">
         <v>4</v>
       </c>
@@ -5840,21 +6890,27 @@
         <v>557</v>
       </c>
       <c r="C223" t="s">
+        <v>557</v>
+      </c>
+      <c r="D223" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="48">
         <v>4</v>
       </c>
-      <c r="B224" t="s">
+      <c r="B224" s="44" t="s">
         <v>559</v>
       </c>
-      <c r="C224" t="s">
+      <c r="C224" s="44" t="s">
+        <v>559</v>
+      </c>
+      <c r="D224" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A225" s="48">
         <v>4</v>
       </c>
@@ -5862,10 +6918,13 @@
         <v>561</v>
       </c>
       <c r="C225" t="s">
+        <v>561</v>
+      </c>
+      <c r="D225" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A226" s="48">
         <v>4</v>
       </c>
@@ -5873,10 +6932,13 @@
         <v>563</v>
       </c>
       <c r="C226" t="s">
+        <v>882</v>
+      </c>
+      <c r="D226" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A227" s="48">
         <v>4</v>
       </c>
@@ -5884,10 +6946,13 @@
         <v>565</v>
       </c>
       <c r="C227" t="s">
+        <v>565</v>
+      </c>
+      <c r="D227" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A228" s="48">
         <v>4</v>
       </c>
@@ -5895,10 +6960,13 @@
         <v>567</v>
       </c>
       <c r="C228" t="s">
+        <v>567</v>
+      </c>
+      <c r="D228" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A229" s="48">
         <v>4</v>
       </c>
@@ -5906,10 +6974,13 @@
         <v>569</v>
       </c>
       <c r="C229" t="s">
+        <v>569</v>
+      </c>
+      <c r="D229" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A230" s="48">
         <v>4</v>
       </c>
@@ -5917,10 +6988,13 @@
         <v>571</v>
       </c>
       <c r="C230" t="s">
+        <v>883</v>
+      </c>
+      <c r="D230" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A231" s="48">
         <v>4</v>
       </c>
@@ -5928,10 +7002,13 @@
         <v>573</v>
       </c>
       <c r="C231" t="s">
+        <v>884</v>
+      </c>
+      <c r="D231" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A232" s="48">
         <v>4</v>
       </c>
@@ -5939,10 +7016,13 @@
         <v>575</v>
       </c>
       <c r="C232" t="s">
+        <v>885</v>
+      </c>
+      <c r="D232" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A233" s="48">
         <v>4</v>
       </c>
@@ -5950,10 +7030,13 @@
         <v>577</v>
       </c>
       <c r="C233" t="s">
+        <v>577</v>
+      </c>
+      <c r="D233" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A234" s="48">
         <v>4</v>
       </c>
@@ -5961,10 +7044,13 @@
         <v>579</v>
       </c>
       <c r="C234" t="s">
+        <v>886</v>
+      </c>
+      <c r="D234" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A235" s="48">
         <v>4</v>
       </c>
@@ -5972,10 +7058,13 @@
         <v>581</v>
       </c>
       <c r="C235" t="s">
+        <v>581</v>
+      </c>
+      <c r="D235" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A236" s="48">
         <v>4</v>
       </c>
@@ -5983,893 +7072,1136 @@
         <v>583</v>
       </c>
       <c r="C236" t="s">
+        <v>887</v>
+      </c>
+      <c r="D236" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A237" s="48">
         <v>4</v>
       </c>
       <c r="B237" t="s">
-        <v>585</v>
+        <v>793</v>
       </c>
       <c r="C237" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>888</v>
+      </c>
+      <c r="D237" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A238" s="48">
         <v>4</v>
       </c>
       <c r="B238" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C238" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>889</v>
+      </c>
+      <c r="D238" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A239" s="48">
         <v>4</v>
       </c>
       <c r="B239" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C239" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>890</v>
+      </c>
+      <c r="D239" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A240" s="48">
         <v>4</v>
       </c>
       <c r="B240" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C240" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>747</v>
+      </c>
+      <c r="D240" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A241" s="48">
         <v>4</v>
       </c>
       <c r="B241" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C241" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>891</v>
+      </c>
+      <c r="D241" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A242" s="48">
         <v>4</v>
       </c>
       <c r="B242" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C242" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>751</v>
+      </c>
+      <c r="D242" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A243" s="48">
         <v>4</v>
       </c>
       <c r="B243" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C243" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>753</v>
+      </c>
+      <c r="D243" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A244" s="48">
         <v>4</v>
       </c>
       <c r="B244" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C244" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>892</v>
+      </c>
+      <c r="D244" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="48">
         <v>4</v>
       </c>
       <c r="B245" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C245" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>893</v>
+      </c>
+      <c r="D245" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A246" s="48">
         <v>4</v>
       </c>
       <c r="B246" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C246" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>759</v>
+      </c>
+      <c r="D246" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="48">
         <v>5</v>
       </c>
       <c r="B247" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C247" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>720</v>
+      </c>
+      <c r="D247" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="48">
         <v>5</v>
       </c>
       <c r="B248" s="93" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C248" s="93" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>597</v>
+      </c>
+      <c r="D248" s="93" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A249" s="48">
         <v>5</v>
       </c>
       <c r="B249" s="93" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C249" s="93" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>599</v>
+      </c>
+      <c r="D249" s="93" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A250" s="48">
         <v>5</v>
       </c>
       <c r="B250" s="95" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C250" s="95" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>894</v>
+      </c>
+      <c r="D250" s="95" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A251" s="48">
         <v>5</v>
       </c>
       <c r="B251" s="93" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C251" s="93" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>895</v>
+      </c>
+      <c r="D251" s="93" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A252" s="48">
         <v>5</v>
       </c>
       <c r="B252" s="95" t="s">
-        <v>668</v>
-      </c>
-      <c r="C252" s="93" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>666</v>
+      </c>
+      <c r="C252" s="95" t="s">
+        <v>896</v>
+      </c>
+      <c r="D252" s="93" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A253" s="48">
         <v>5</v>
       </c>
       <c r="B253" s="93" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C253" s="93" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>775</v>
+      </c>
+      <c r="D253" s="93" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A254" s="48">
         <v>5</v>
       </c>
       <c r="B254" s="93" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C254" s="93" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>897</v>
+      </c>
+      <c r="D254" s="93" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A255" s="48">
         <v>5</v>
       </c>
       <c r="B255" s="93" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C255" s="93" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>601</v>
+      </c>
+      <c r="D255" s="93" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A256" s="48">
         <v>5</v>
       </c>
       <c r="B256" s="93" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C256" s="93" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>603</v>
+      </c>
+      <c r="D256" s="93" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A257" s="48">
         <v>5</v>
       </c>
       <c r="B257" s="93" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C257" s="93" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>611</v>
+      </c>
+      <c r="D257" s="93" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A258" s="48">
         <v>5</v>
       </c>
       <c r="B258" s="95" t="s">
-        <v>663</v>
-      </c>
-      <c r="C258" s="93" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>661</v>
+      </c>
+      <c r="C258" s="95" t="s">
+        <v>661</v>
+      </c>
+      <c r="D258" s="93" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A259" s="48">
         <v>5</v>
       </c>
       <c r="B259" s="93" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C259" s="93" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>614</v>
+      </c>
+      <c r="D259" s="93" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A260" s="48">
         <v>5</v>
       </c>
       <c r="B260" s="93" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C260" s="93" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>620</v>
+      </c>
+      <c r="D260" s="93" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A261" s="48">
         <v>5</v>
       </c>
       <c r="B261" s="93" t="s">
-        <v>624</v>
-      </c>
-      <c r="C261" s="94" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>622</v>
+      </c>
+      <c r="C261" s="93" t="s">
+        <v>622</v>
+      </c>
+      <c r="D261" s="94" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A262" s="48">
         <v>5</v>
       </c>
       <c r="B262" s="95" t="s">
-        <v>626</v>
-      </c>
-      <c r="C262" s="93" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>624</v>
+      </c>
+      <c r="C262" s="95" t="s">
+        <v>898</v>
+      </c>
+      <c r="D262" s="93" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A263" s="48">
         <v>5</v>
       </c>
       <c r="B263" s="93" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C263" s="93" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>899</v>
+      </c>
+      <c r="D263" s="93" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A264" s="48">
         <v>5</v>
       </c>
       <c r="B264" s="93" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C264" s="93" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>628</v>
+      </c>
+      <c r="D264" s="93" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A265" s="48">
         <v>5</v>
       </c>
       <c r="B265" s="93" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C265" s="93" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>616</v>
+      </c>
+      <c r="D265" s="93" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A266" s="48">
         <v>5</v>
       </c>
       <c r="B266" s="93" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C266" s="93" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>900</v>
+      </c>
+      <c r="D266" s="93" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A267" s="48">
         <v>5</v>
       </c>
       <c r="B267" s="93" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C267" s="93" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>632</v>
+      </c>
+      <c r="D267" s="93" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A268" s="48">
         <v>5</v>
       </c>
       <c r="B268" s="93" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C268" s="93" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>634</v>
+      </c>
+      <c r="D268" s="93" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A269" s="48">
         <v>5</v>
       </c>
       <c r="B269" s="93" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C269" s="93" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>636</v>
+      </c>
+      <c r="D269" s="93" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A270" s="48">
         <v>5</v>
       </c>
       <c r="B270" s="95" t="s">
-        <v>711</v>
-      </c>
-      <c r="C270" s="93" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>709</v>
+      </c>
+      <c r="C270" s="95" t="s">
+        <v>709</v>
+      </c>
+      <c r="D270" s="93" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A271" s="48">
         <v>5</v>
       </c>
       <c r="B271" s="95" t="s">
-        <v>766</v>
-      </c>
-      <c r="C271" s="93" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>763</v>
+      </c>
+      <c r="C271" s="95" t="s">
+        <v>763</v>
+      </c>
+      <c r="D271" s="93" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A272" s="48">
         <v>5</v>
       </c>
       <c r="B272" s="95" t="s">
-        <v>643</v>
-      </c>
-      <c r="C272" s="93" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>641</v>
+      </c>
+      <c r="C272" s="95" t="s">
+        <v>641</v>
+      </c>
+      <c r="D272" s="93" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A273" s="48">
         <v>5</v>
       </c>
       <c r="B273" s="95" t="s">
-        <v>645</v>
-      </c>
-      <c r="C273" s="93" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>643</v>
+      </c>
+      <c r="C273" s="95" t="s">
+        <v>643</v>
+      </c>
+      <c r="D273" s="93" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A274" s="48">
         <v>5</v>
       </c>
       <c r="B274" s="95" t="s">
-        <v>648</v>
-      </c>
-      <c r="C274" s="93" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>646</v>
+      </c>
+      <c r="C274" s="95" t="s">
+        <v>646</v>
+      </c>
+      <c r="D274" s="93" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A275" s="48">
         <v>5</v>
       </c>
       <c r="B275" s="95" t="s">
-        <v>650</v>
-      </c>
-      <c r="C275" s="93" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>648</v>
+      </c>
+      <c r="C275" s="95" t="s">
+        <v>648</v>
+      </c>
+      <c r="D275" s="93" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A276" s="48">
         <v>5</v>
       </c>
       <c r="B276" s="95" t="s">
-        <v>656</v>
-      </c>
-      <c r="C276" s="93" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>654</v>
+      </c>
+      <c r="C276" s="95" t="s">
+        <v>901</v>
+      </c>
+      <c r="D276" s="93" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A277" s="48">
         <v>5</v>
       </c>
       <c r="B277" s="93" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C277" s="93" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>650</v>
+      </c>
+      <c r="D277" s="93" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A278" s="48">
         <v>5</v>
       </c>
       <c r="B278" s="95" t="s">
-        <v>654</v>
-      </c>
-      <c r="C278" s="93" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>652</v>
+      </c>
+      <c r="C278" s="95" t="s">
+        <v>652</v>
+      </c>
+      <c r="D278" s="93" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A279" s="48">
         <v>5</v>
       </c>
       <c r="B279" s="93" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C279" s="93" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>656</v>
+      </c>
+      <c r="D279" s="93" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A280" s="48">
         <v>5</v>
       </c>
       <c r="B280" s="95" t="s">
-        <v>620</v>
-      </c>
-      <c r="C280" s="93" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>618</v>
+      </c>
+      <c r="C280" s="95" t="s">
+        <v>618</v>
+      </c>
+      <c r="D280" s="93" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A281" s="48">
         <v>5</v>
       </c>
       <c r="B281" s="95" t="s">
-        <v>640</v>
-      </c>
-      <c r="C281" s="93" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>638</v>
+      </c>
+      <c r="C281" s="95" t="s">
+        <v>638</v>
+      </c>
+      <c r="D281" s="93" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A282" s="48">
         <v>5</v>
       </c>
       <c r="B282" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C282" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>902</v>
+      </c>
+      <c r="D282" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A283" s="48">
         <v>5</v>
       </c>
       <c r="B283" s="93" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C283" s="93" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>903</v>
+      </c>
+      <c r="D283" s="93" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A284" s="48">
         <v>5</v>
       </c>
       <c r="B284" s="93" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C284" s="93" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>904</v>
+      </c>
+      <c r="D284" s="93" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A285" s="48">
         <v>5</v>
       </c>
       <c r="B285" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C285" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>905</v>
+      </c>
+      <c r="D285" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A286" s="48">
         <v>5</v>
       </c>
       <c r="B286" s="93" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C286" s="93" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>906</v>
+      </c>
+      <c r="D286" s="93" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A287" s="48">
         <v>5</v>
       </c>
       <c r="B287" s="93" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C287" s="93" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>907</v>
+      </c>
+      <c r="D287" s="93" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A288" s="48">
         <v>5</v>
       </c>
       <c r="B288" s="93" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C288" s="93" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>908</v>
+      </c>
+      <c r="D288" s="93" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A289" s="48">
         <v>5</v>
       </c>
       <c r="B289" s="93" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C289" s="93" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>673</v>
+      </c>
+      <c r="D289" s="93" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A290" s="48">
         <v>5</v>
       </c>
       <c r="B290" s="93" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C290" s="93" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>675</v>
+      </c>
+      <c r="D290" s="93" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A291" s="48">
         <v>5</v>
       </c>
       <c r="B291" s="93" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C291" s="93" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>677</v>
+      </c>
+      <c r="D291" s="93" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A292" s="48">
         <v>5</v>
       </c>
       <c r="B292" s="93" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C292" s="93" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>909</v>
+      </c>
+      <c r="D292" s="93" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A293" s="48">
         <v>5</v>
       </c>
       <c r="B293" s="93" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C293" s="93" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>910</v>
+      </c>
+      <c r="D293" s="93" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A294" s="48">
         <v>5</v>
       </c>
       <c r="B294" s="93" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C294" s="93" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>683</v>
+      </c>
+      <c r="D294" s="93" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A295" s="48">
         <v>5</v>
       </c>
       <c r="B295" s="93" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C295" s="93" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>707</v>
+      </c>
+      <c r="D295" s="93" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A296" s="48">
         <v>5</v>
       </c>
       <c r="B296" s="93" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C296" s="93" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>911</v>
+      </c>
+      <c r="D296" s="93" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A297" s="48">
         <v>5</v>
       </c>
       <c r="B297" s="93" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C297" s="93" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>687</v>
+      </c>
+      <c r="D297" s="93" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A298" s="48">
         <v>5</v>
       </c>
       <c r="B298" s="93" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C298" s="93" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>912</v>
+      </c>
+      <c r="D298" s="93" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A299" s="48">
         <v>5</v>
       </c>
       <c r="B299" s="93" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C299" s="93" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>913</v>
+      </c>
+      <c r="D299" s="93" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A300" s="48">
         <v>5</v>
       </c>
       <c r="B300" s="93" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C300" s="93" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>914</v>
+      </c>
+      <c r="D300" s="93" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A301" s="48">
         <v>5</v>
       </c>
       <c r="B301" s="93" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C301" s="93" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>695</v>
+      </c>
+      <c r="D301" s="93" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A302" s="48">
         <v>5</v>
       </c>
       <c r="B302" s="93" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C302" s="93" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>697</v>
+      </c>
+      <c r="D302" s="93" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A303" s="48">
         <v>5</v>
       </c>
       <c r="B303" s="93" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C303" s="93" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>699</v>
+      </c>
+      <c r="D303" s="93" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A304" s="48">
         <v>5</v>
       </c>
       <c r="B304" s="93" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C304" s="93" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>701</v>
+      </c>
+      <c r="D304" s="93" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A305" s="48">
         <v>5</v>
       </c>
       <c r="B305" s="93" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C305" s="93" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>703</v>
+      </c>
+      <c r="D305" s="93" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A306" s="48">
         <v>5</v>
       </c>
       <c r="B306" s="93" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C306" s="93" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>915</v>
+      </c>
+      <c r="D306" s="93" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A307" s="104">
         <v>5</v>
       </c>
       <c r="B307" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C307" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>761</v>
+      </c>
+      <c r="D307" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A308" s="104">
         <v>5</v>
       </c>
       <c r="B308" s="49" t="s">
-        <v>768</v>
-      </c>
-      <c r="C308" s="50" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>765</v>
+      </c>
+      <c r="C308" s="49" t="s">
+        <v>765</v>
+      </c>
+      <c r="D308" s="50" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A309" s="104">
         <v>5</v>
       </c>
       <c r="B309" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C309" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>916</v>
+      </c>
+      <c r="D309" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A310" s="104">
         <v>5</v>
       </c>
       <c r="B310" s="49" t="s">
-        <v>774</v>
-      </c>
-      <c r="C310" s="50" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>771</v>
+      </c>
+      <c r="C310" s="49" t="s">
+        <v>771</v>
+      </c>
+      <c r="D310" s="50" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A311" s="104">
         <v>5</v>
       </c>
       <c r="B311" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C311" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>917</v>
+      </c>
+      <c r="D311" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A312" s="104">
         <v>5</v>
       </c>
       <c r="B312" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="C312" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>918</v>
+      </c>
+      <c r="D312" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A313" s="104">
         <v>5</v>
       </c>
       <c r="B313" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C313" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>779</v>
+      </c>
+      <c r="D313" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A314" s="104">
         <v>5</v>
       </c>
       <c r="B314" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="C314" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>919</v>
+      </c>
+      <c r="D314" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A315" s="104">
         <v>5</v>
       </c>
       <c r="B315" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C315" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>920</v>
+      </c>
+      <c r="D315" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A316" s="104">
         <v>5</v>
       </c>
       <c r="B316" s="49" t="s">
-        <v>788</v>
-      </c>
-      <c r="C316" s="50" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="318" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="319" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="320" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+        <v>785</v>
+      </c>
+      <c r="C316" s="49" t="s">
+        <v>785</v>
+      </c>
+      <c r="D316" s="50" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="318" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="319" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="320" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -7559,11 +8891,11 @@
     <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <conditionalFormatting sqref="C248:C281">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  <conditionalFormatting sqref="B182:C215 B217:C238">
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B182:B215 B217:B238">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  <conditionalFormatting sqref="D248:D281">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7614,7 +8946,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>278</v>
@@ -8221,7 +9553,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C22" s="51" t="s">
         <v>547</v>
@@ -8525,10 +9857,10 @@
         <v>4</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C32" s="44" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -8651,7 +9983,7 @@
         <v>532</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G36" s="23" t="s">
         <v>533</v>
@@ -8684,7 +10016,7 @@
         <v>541</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G37" s="26" t="s">
         <v>541</v>
@@ -8714,7 +10046,7 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="27" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="F38" s="90" t="s">
         <v>543</v>
@@ -8723,7 +10055,7 @@
         <v>541</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="I38" s="23" t="s">
         <v>533</v>
@@ -8732,7 +10064,7 @@
         <v>533</v>
       </c>
       <c r="K38" s="26" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="L38" s="92" t="s">
         <v>543</v>
@@ -8759,10 +10091,10 @@
         <v>541</v>
       </c>
       <c r="I39" s="26" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="J39" s="26" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="K39" s="90" t="s">
         <v>543</v>
@@ -8829,10 +10161,10 @@
         <v>5</v>
       </c>
       <c r="B42" s="51" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C42" s="51" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -8853,28 +10185,28 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="32" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F43" s="33" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G43" s="33" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="H43" s="33" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="I43" s="33" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="J43" s="33" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="K43" s="33" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="L43" s="34" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
@@ -8886,28 +10218,28 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="35" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G44" s="97" t="s">
+        <v>652</v>
+      </c>
+      <c r="H44" s="96" t="s">
+        <v>652</v>
+      </c>
+      <c r="I44" s="96" t="s">
+        <v>652</v>
+      </c>
+      <c r="J44" s="96" t="s">
         <v>654</v>
       </c>
-      <c r="H44" s="96" t="s">
-        <v>654</v>
-      </c>
-      <c r="I44" s="96" t="s">
-        <v>654</v>
-      </c>
-      <c r="J44" s="96" t="s">
-        <v>656</v>
-      </c>
       <c r="K44" s="31" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="L44" s="36" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
@@ -8919,28 +10251,28 @@
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="35" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F45" s="100" t="s">
+        <v>654</v>
+      </c>
+      <c r="G45" s="51" t="s">
+        <v>648</v>
+      </c>
+      <c r="H45" s="101" t="s">
         <v>656</v>
       </c>
-      <c r="G45" s="51" t="s">
-        <v>650</v>
-      </c>
-      <c r="H45" s="101" t="s">
-        <v>658</v>
-      </c>
       <c r="I45" s="101" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="K45" s="97" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="L45" s="36" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
@@ -8952,28 +10284,28 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="99" t="s">
+        <v>654</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="G46" s="51" t="s">
+        <v>648</v>
+      </c>
+      <c r="H46" s="101" t="s">
         <v>656</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="I46" s="101" t="s">
+        <v>656</v>
+      </c>
+      <c r="J46" s="51" t="s">
         <v>648</v>
       </c>
-      <c r="G46" s="51" t="s">
-        <v>650</v>
-      </c>
-      <c r="H46" s="101" t="s">
-        <v>658</v>
-      </c>
-      <c r="I46" s="101" t="s">
-        <v>658</v>
-      </c>
-      <c r="J46" s="51" t="s">
-        <v>650</v>
-      </c>
       <c r="K46" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="L46" s="98" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
@@ -8985,28 +10317,28 @@
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="35" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F47" s="96" t="s">
+        <v>654</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="H47" s="101" t="s">
         <v>656</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="H47" s="101" t="s">
-        <v>658</v>
-      </c>
       <c r="I47" s="101" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="K47" s="96" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="L47" s="36" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
@@ -9018,28 +10350,28 @@
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="35" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F48" s="31" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G48" s="97" t="s">
+        <v>652</v>
+      </c>
+      <c r="H48" s="97" t="s">
         <v>654</v>
       </c>
-      <c r="H48" s="97" t="s">
-        <v>656</v>
-      </c>
       <c r="I48" s="97" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="J48" s="96" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="K48" s="31" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="L48" s="36" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
@@ -9051,28 +10383,28 @@
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="35" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F49" s="31" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G49" s="31" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="H49" s="31" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="I49" s="31" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="J49" s="31" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="K49" s="31" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="L49" s="36" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
@@ -9084,28 +10416,28 @@
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="37" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G50" s="38" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="H50" s="38" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="I50" s="38" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="J50" s="38" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="K50" s="38" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="L50" s="39" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
@@ -13218,7 +14550,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="51" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -13272,7 +14604,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -13374,13 +14706,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -13392,13 +14724,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -13506,7 +14838,7 @@
         <v>11</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E20" s="48"/>
       <c r="F20" s="1"/>
@@ -13590,13 +14922,13 @@
         <v>2</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E25" s="48"/>
       <c r="F25" s="1"/>
@@ -13608,13 +14940,13 @@
         <v>2</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E26" s="48"/>
       <c r="F26" s="1"/>
@@ -13650,7 +14982,7 @@
         <v>24</v>
       </c>
       <c r="D28" s="51" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
@@ -13722,7 +15054,7 @@
         <v>11</v>
       </c>
       <c r="D32" s="51" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -13794,7 +15126,7 @@
         <v>18</v>
       </c>
       <c r="D36" s="44" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -13806,13 +15138,13 @@
         <v>3</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -13824,13 +15156,13 @@
         <v>3</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -13866,7 +15198,7 @@
         <v>24</v>
       </c>
       <c r="D40" s="51" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
@@ -13938,7 +15270,7 @@
         <v>11</v>
       </c>
       <c r="D44" s="51" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -14022,13 +15354,13 @@
         <v>4</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -14040,13 +15372,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D50" s="51" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -14082,7 +15414,7 @@
         <v>24</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>763</v>
+        <v>792</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -14154,7 +15486,7 @@
         <v>11</v>
       </c>
       <c r="D56" s="51" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
@@ -14172,7 +15504,7 @@
         <v>13</v>
       </c>
       <c r="D57" s="51" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
@@ -14190,7 +15522,7 @@
         <v>15</v>
       </c>
       <c r="D58" s="51" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
@@ -14208,7 +15540,7 @@
         <v>17</v>
       </c>
       <c r="D59" s="51" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
@@ -14226,7 +15558,7 @@
         <v>18</v>
       </c>
       <c r="D60" s="51" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
@@ -14238,13 +15570,13 @@
         <v>5</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D61" s="51" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
@@ -14256,13 +15588,13 @@
         <v>5</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D62" s="51" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
@@ -14280,7 +15612,7 @@
         <v>21</v>
       </c>
       <c r="D63" s="51" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
@@ -14298,7 +15630,7 @@
         <v>24</v>
       </c>
       <c r="D64" s="51" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>

--- a/epepep_structure.xlsx
+++ b/epepep_structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\annwa\OneDrive\Desktop\Workspace\epepep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BFD159-966D-490D-864F-D79A2B0095A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD30A85-16C8-48EA-B58A-18DA281AAF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1028" yWindow="2055" windowWidth="12262" windowHeight="8933" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9802" yWindow="0" windowWidth="11881" windowHeight="12863" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Word" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="925">
   <si>
     <t>Unit</t>
   </si>
@@ -2347,12 +2347,6 @@
     <t>jau5 se1</t>
   </si>
   <si>
-    <t>妥</t>
-  </si>
-  <si>
-    <t>to5</t>
-  </si>
-  <si>
     <t>勇敢</t>
   </si>
   <si>
@@ -2362,9 +2356,6 @@
     <t>妥何染第件笑權</t>
   </si>
   <si>
-    <t>妥妥妥妥妥染染染染染何何何權妥染妥權件笑笑第何染權第件笑笑件件權染權第笑笑第何妥妥妥何權權何染染染染妥妥妥妥染染妥染染染妥妥妥妥</t>
-  </si>
-  <si>
     <t>猛獸</t>
   </si>
   <si>
@@ -2825,6 +2816,21 @@
   </si>
   <si>
     <t>只（是）</t>
+  </si>
+  <si>
+    <t>Voice</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>jung5</t>
+  </si>
+  <si>
+    <t>勇勇勇勇勇染染染染染何何何權勇染勇權件笑笑第何染權第件笑笑件件權染權第笑笑第何勇勇勇何權權何染染染染勇勇勇勇染染勇染染染勇勇勇勇</t>
   </si>
 </sst>
 </file>
@@ -3216,7 +3222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3512,6 +3518,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3765,16 +3772,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1008"/>
+  <dimension ref="A1:E1008"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="104" customWidth="1"/>
-    <col min="2" max="3" width="12.59765625" style="49" customWidth="1"/>
-    <col min="4" max="4" width="12.59765625" style="50" customWidth="1"/>
-    <col min="5" max="7" width="12.59765625" customWidth="1"/>
+    <col min="2" max="4" width="12.59765625" style="49" customWidth="1"/>
+    <col min="5" max="5" width="12.59765625" style="50" customWidth="1"/>
+    <col min="6" max="8" width="12.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
@@ -3782,13 +3789,16 @@
         <v>36</v>
       </c>
       <c r="C1" s="46" t="s">
-        <v>921</v>
-      </c>
-      <c r="D1" s="52" t="s">
+        <v>918</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>920</v>
+      </c>
+      <c r="E1" s="52" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="48">
         <v>1</v>
       </c>
@@ -3798,11 +3808,14 @@
       <c r="C2" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="D2" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E2" s="50" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="48">
         <v>1</v>
       </c>
@@ -3812,11 +3825,14 @@
       <c r="C3" s="47" t="s">
         <v>135</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E3" s="50" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="48">
         <v>1</v>
       </c>
@@ -3824,13 +3840,16 @@
         <v>40</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>795</v>
-      </c>
-      <c r="D4" s="50" t="s">
+        <v>792</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E4" s="50" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="48">
         <v>1</v>
       </c>
@@ -3840,11 +3859,14 @@
       <c r="C5" s="47" t="s">
         <v>137</v>
       </c>
-      <c r="D5" s="50" t="s">
+      <c r="D5" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E5" s="50" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="48">
         <v>1</v>
       </c>
@@ -3854,11 +3876,14 @@
       <c r="C6" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E6" s="50" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="48">
         <v>1</v>
       </c>
@@ -3866,13 +3891,16 @@
         <v>139</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>796</v>
-      </c>
-      <c r="D7" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E7" s="50" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="48">
         <v>1</v>
       </c>
@@ -3882,11 +3910,14 @@
       <c r="C8" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="D8" s="50" t="s">
+      <c r="D8" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E8" s="50" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="48">
         <v>1</v>
       </c>
@@ -3894,13 +3925,16 @@
         <v>143</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>797</v>
-      </c>
-      <c r="D9" s="50" t="s">
+        <v>794</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E9" s="50" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="48">
         <v>1</v>
       </c>
@@ -3910,11 +3944,14 @@
       <c r="C10" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="D10" s="50" t="s">
+      <c r="D10" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E10" s="50" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="48">
         <v>1</v>
       </c>
@@ -3924,11 +3961,14 @@
       <c r="C11" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E11" s="50" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="48">
         <v>1</v>
       </c>
@@ -3938,11 +3978,14 @@
       <c r="C12" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="D12" s="50" t="s">
+      <c r="D12" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E12" s="50" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="48">
         <v>1</v>
       </c>
@@ -3952,11 +3995,14 @@
       <c r="C13" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="50" t="s">
+      <c r="D13" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E13" s="50" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="48">
         <v>1</v>
       </c>
@@ -3966,11 +4012,14 @@
       <c r="C14" s="47" t="s">
         <v>152</v>
       </c>
-      <c r="D14" s="50" t="s">
+      <c r="D14" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E14" s="50" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="48">
         <v>1</v>
       </c>
@@ -3980,11 +4029,14 @@
       <c r="C15" s="47" t="s">
         <v>154</v>
       </c>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E15" s="50" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="48">
         <v>1</v>
       </c>
@@ -3994,11 +4046,14 @@
       <c r="C16" s="47" t="s">
         <v>161</v>
       </c>
-      <c r="D16" s="50" t="s">
+      <c r="D16" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E16" s="50" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="48">
         <v>1</v>
       </c>
@@ -4008,11 +4063,14 @@
       <c r="C17" s="47" t="s">
         <v>163</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="D17" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E17" s="50" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="48">
         <v>1</v>
       </c>
@@ -4020,13 +4078,16 @@
         <v>165</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>798</v>
-      </c>
-      <c r="D18" s="50" t="s">
+        <v>795</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E18" s="50" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="48">
         <v>1</v>
       </c>
@@ -4034,13 +4095,16 @@
         <v>167</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>799</v>
-      </c>
-      <c r="D19" s="50" t="s">
+        <v>796</v>
+      </c>
+      <c r="D19" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E19" s="50" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="48">
         <v>1</v>
       </c>
@@ -4050,11 +4114,14 @@
       <c r="C20" s="47" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="50" t="s">
+      <c r="D20" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E20" s="50" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="48">
         <v>1</v>
       </c>
@@ -4062,13 +4129,16 @@
         <v>133</v>
       </c>
       <c r="C21" s="47" t="s">
+        <v>919</v>
+      </c>
+      <c r="D21" s="47" t="s">
         <v>922</v>
       </c>
-      <c r="D21" s="50" t="s">
+      <c r="E21" s="50" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="48">
         <v>1</v>
       </c>
@@ -4076,13 +4146,16 @@
         <v>173</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>800</v>
-      </c>
-      <c r="D22" s="50" t="s">
+        <v>797</v>
+      </c>
+      <c r="D22" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E22" s="50" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="48">
         <v>1</v>
       </c>
@@ -4092,11 +4165,14 @@
       <c r="C23" s="47" t="s">
         <v>171</v>
       </c>
-      <c r="D23" s="50" t="s">
+      <c r="D23" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E23" s="50" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="48">
         <v>1</v>
       </c>
@@ -4106,11 +4182,14 @@
       <c r="C24" s="47" t="s">
         <v>229</v>
       </c>
-      <c r="D24" s="50" t="s">
+      <c r="D24" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E24" s="50" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="48">
         <v>1</v>
       </c>
@@ -4118,13 +4197,16 @@
         <v>175</v>
       </c>
       <c r="C25" s="47" t="s">
-        <v>801</v>
-      </c>
-      <c r="D25" s="50" t="s">
+        <v>798</v>
+      </c>
+      <c r="D25" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E25" s="50" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="48">
         <v>1</v>
       </c>
@@ -4134,11 +4216,14 @@
       <c r="C26" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="D26" s="50" t="s">
+      <c r="D26" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E26" s="50" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="48">
         <v>1</v>
       </c>
@@ -4148,11 +4233,14 @@
       <c r="C27" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="D27" s="50" t="s">
+      <c r="D27" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E27" s="50" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="48">
         <v>1</v>
       </c>
@@ -4162,11 +4250,14 @@
       <c r="C28" s="47" t="s">
         <v>273</v>
       </c>
-      <c r="D28" s="50" t="s">
+      <c r="D28" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E28" s="50" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="48">
         <v>1</v>
       </c>
@@ -4176,25 +4267,31 @@
       <c r="C29" s="47" t="s">
         <v>205</v>
       </c>
-      <c r="D29" s="50" t="s">
+      <c r="D29" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E29" s="50" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="48">
         <v>1</v>
       </c>
       <c r="B30" s="47" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C30" s="47" t="s">
-        <v>169</v>
-      </c>
-      <c r="D30" s="50" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>799</v>
+      </c>
+      <c r="D30" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E30" s="50" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="48">
         <v>1</v>
       </c>
@@ -4204,109 +4301,133 @@
       <c r="C31" s="47" t="s">
         <v>214</v>
       </c>
-      <c r="D31" s="50" t="s">
+      <c r="D31" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E31" s="50" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="48">
         <v>1</v>
       </c>
       <c r="B32" s="47" t="s">
-        <v>55</v>
+        <v>169</v>
       </c>
       <c r="C32" s="47" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="50" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>169</v>
+      </c>
+      <c r="D32" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E32" s="50" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="48">
         <v>1</v>
       </c>
       <c r="B33" s="47" t="s">
-        <v>217</v>
+        <v>179</v>
       </c>
       <c r="C33" s="47" t="s">
-        <v>217</v>
-      </c>
-      <c r="D33" s="50" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+      <c r="D33" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E33" s="50" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="48">
         <v>1</v>
       </c>
       <c r="B34" s="47" t="s">
-        <v>57</v>
+        <v>210</v>
       </c>
       <c r="C34" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="D34" s="50" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>210</v>
+      </c>
+      <c r="D34" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E34" s="50" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="48">
         <v>1</v>
       </c>
       <c r="B35" s="47" t="s">
-        <v>179</v>
+        <v>255</v>
       </c>
       <c r="C35" s="47" t="s">
-        <v>179</v>
-      </c>
-      <c r="D35" s="50" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>800</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E35" s="50" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="48">
         <v>1</v>
       </c>
       <c r="B36" s="47" t="s">
-        <v>177</v>
+        <v>55</v>
       </c>
       <c r="C36" s="47" t="s">
-        <v>802</v>
-      </c>
-      <c r="D36" s="50" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+      <c r="D36" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E36" s="50" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="48">
         <v>1</v>
       </c>
       <c r="B37" s="47" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C37" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="D37" s="50" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>217</v>
+      </c>
+      <c r="D37" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E37" s="50" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="48">
         <v>1</v>
       </c>
       <c r="B38" s="47" t="s">
-        <v>255</v>
+        <v>57</v>
       </c>
       <c r="C38" s="47" t="s">
-        <v>803</v>
-      </c>
-      <c r="D38" s="50" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>57</v>
+      </c>
+      <c r="D38" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E38" s="50" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="48">
         <v>1</v>
       </c>
@@ -4316,11 +4437,14 @@
       <c r="C39" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="D39" s="50" t="s">
+      <c r="D39" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E39" s="50" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="48">
         <v>1</v>
       </c>
@@ -4330,11 +4454,14 @@
       <c r="C40" s="47" t="s">
         <v>183</v>
       </c>
-      <c r="D40" s="50" t="s">
+      <c r="D40" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E40" s="50" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="48">
         <v>1</v>
       </c>
@@ -4344,11 +4471,14 @@
       <c r="C41" s="47" t="s">
         <v>184</v>
       </c>
-      <c r="D41" s="50" t="s">
+      <c r="D41" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E41" s="50" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="48">
         <v>1</v>
       </c>
@@ -4358,11 +4488,14 @@
       <c r="C42" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="D42" s="50" t="s">
+      <c r="D42" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E42" s="50" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="48">
         <v>1</v>
       </c>
@@ -4370,13 +4503,16 @@
         <v>188</v>
       </c>
       <c r="C43" s="47" t="s">
-        <v>804</v>
-      </c>
-      <c r="D43" s="50" t="s">
+        <v>801</v>
+      </c>
+      <c r="D43" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E43" s="50" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="48">
         <v>1</v>
       </c>
@@ -4386,11 +4522,14 @@
       <c r="C44" s="47" t="s">
         <v>190</v>
       </c>
-      <c r="D44" s="50" t="s">
+      <c r="D44" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E44" s="50" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="48">
         <v>1</v>
       </c>
@@ -4400,11 +4539,14 @@
       <c r="C45" s="47" t="s">
         <v>192</v>
       </c>
-      <c r="D45" s="50" t="s">
+      <c r="D45" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E45" s="50" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="48">
         <v>1</v>
       </c>
@@ -4414,11 +4556,14 @@
       <c r="C46" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="D46" s="50" t="s">
+      <c r="D46" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E46" s="50" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="48">
         <v>1</v>
       </c>
@@ -4428,11 +4573,14 @@
       <c r="C47" s="47" t="s">
         <v>196</v>
       </c>
-      <c r="D47" s="50" t="s">
+      <c r="D47" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E47" s="50" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="48">
         <v>1</v>
       </c>
@@ -4442,11 +4590,14 @@
       <c r="C48" s="47" t="s">
         <v>198</v>
       </c>
-      <c r="D48" s="50" t="s">
+      <c r="D48" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E48" s="50" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="48">
         <v>1</v>
       </c>
@@ -4456,11 +4607,14 @@
       <c r="C49" s="47" t="s">
         <v>200</v>
       </c>
-      <c r="D49" s="50" t="s">
+      <c r="D49" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E49" s="50" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="48">
         <v>1</v>
       </c>
@@ -4470,11 +4624,14 @@
       <c r="C50" s="47" t="s">
         <v>194</v>
       </c>
-      <c r="D50" s="50" t="s">
+      <c r="D50" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E50" s="50" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="48">
         <v>1</v>
       </c>
@@ -4484,11 +4641,14 @@
       <c r="C51" s="47" t="s">
         <v>203</v>
       </c>
-      <c r="D51" s="50" t="s">
+      <c r="D51" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="E51" s="50" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="48">
         <v>1</v>
       </c>
@@ -4498,11 +4658,14 @@
       <c r="C52" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="D52" s="50" t="s">
+      <c r="D52" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E52" s="50" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="48">
         <v>1</v>
       </c>
@@ -4512,11 +4675,14 @@
       <c r="C53" s="47" t="s">
         <v>207</v>
       </c>
-      <c r="D53" s="50" t="s">
+      <c r="D53" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E53" s="50" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="48">
         <v>1</v>
       </c>
@@ -4526,11 +4692,14 @@
       <c r="C54" s="47" t="s">
         <v>236</v>
       </c>
-      <c r="D54" s="50" t="s">
+      <c r="D54" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E54" s="50" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="48">
         <v>1</v>
       </c>
@@ -4540,11 +4709,14 @@
       <c r="C55" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D55" s="50" t="s">
+      <c r="D55" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E55" s="50" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="48">
         <v>1</v>
       </c>
@@ -4554,11 +4726,14 @@
       <c r="C56" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="D56" s="50" t="s">
+      <c r="D56" s="47" t="s">
+        <v>922</v>
+      </c>
+      <c r="E56" s="50" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="48">
         <v>1</v>
       </c>
@@ -4566,13 +4741,16 @@
         <v>219</v>
       </c>
       <c r="C57" s="49" t="s">
-        <v>805</v>
-      </c>
-      <c r="D57" s="50" t="s">
+        <v>802</v>
+      </c>
+      <c r="D57" s="49" t="s">
+        <v>921</v>
+      </c>
+      <c r="E57" s="50" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="48">
         <v>1</v>
       </c>
@@ -4580,13 +4758,16 @@
         <v>221</v>
       </c>
       <c r="C58" s="49" t="s">
-        <v>806</v>
-      </c>
-      <c r="D58" s="50" t="s">
+        <v>803</v>
+      </c>
+      <c r="D58" s="49" t="s">
+        <v>921</v>
+      </c>
+      <c r="E58" s="50" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="48">
         <v>1</v>
       </c>
@@ -4594,13 +4775,16 @@
         <v>223</v>
       </c>
       <c r="C59" s="49" t="s">
-        <v>807</v>
-      </c>
-      <c r="D59" s="50" t="s">
+        <v>804</v>
+      </c>
+      <c r="D59" s="49" t="s">
+        <v>922</v>
+      </c>
+      <c r="E59" s="50" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="48">
         <v>1</v>
       </c>
@@ -4608,13 +4792,16 @@
         <v>225</v>
       </c>
       <c r="C60" s="49" t="s">
-        <v>808</v>
-      </c>
-      <c r="D60" s="50" t="s">
+        <v>805</v>
+      </c>
+      <c r="D60" s="49" t="s">
+        <v>922</v>
+      </c>
+      <c r="E60" s="50" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="48">
         <v>1</v>
       </c>
@@ -4622,13 +4809,16 @@
         <v>239</v>
       </c>
       <c r="C61" s="49" t="s">
-        <v>809</v>
-      </c>
-      <c r="D61" s="50" t="s">
+        <v>806</v>
+      </c>
+      <c r="D61" s="49" t="s">
+        <v>921</v>
+      </c>
+      <c r="E61" s="50" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="48">
         <v>1</v>
       </c>
@@ -4638,11 +4828,14 @@
       <c r="C62" s="49" t="s">
         <v>241</v>
       </c>
-      <c r="D62" s="50" t="s">
+      <c r="D62" s="49" t="s">
+        <v>921</v>
+      </c>
+      <c r="E62" s="50" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="48">
         <v>1</v>
       </c>
@@ -4650,13 +4843,16 @@
         <v>243</v>
       </c>
       <c r="C63" s="49" t="s">
-        <v>810</v>
-      </c>
-      <c r="D63" s="50" t="s">
+        <v>807</v>
+      </c>
+      <c r="D63" s="49" t="s">
+        <v>922</v>
+      </c>
+      <c r="E63" s="50" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="48">
         <v>1</v>
       </c>
@@ -4664,13 +4860,16 @@
         <v>245</v>
       </c>
       <c r="C64" s="49" t="s">
-        <v>811</v>
-      </c>
-      <c r="D64" s="50" t="s">
+        <v>808</v>
+      </c>
+      <c r="D64" s="49" t="s">
+        <v>922</v>
+      </c>
+      <c r="E64" s="50" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="48">
         <v>1</v>
       </c>
@@ -4678,13 +4877,16 @@
         <v>247</v>
       </c>
       <c r="C65" s="49" t="s">
-        <v>812</v>
-      </c>
-      <c r="D65" s="50" t="s">
+        <v>809</v>
+      </c>
+      <c r="D65" s="49" t="s">
+        <v>921</v>
+      </c>
+      <c r="E65" s="50" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="48">
         <v>1</v>
       </c>
@@ -4692,13 +4894,16 @@
         <v>249</v>
       </c>
       <c r="C66" s="49" t="s">
-        <v>813</v>
-      </c>
-      <c r="D66" s="50" t="s">
+        <v>810</v>
+      </c>
+      <c r="D66" s="49" t="s">
+        <v>921</v>
+      </c>
+      <c r="E66" s="50" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="48">
         <v>1</v>
       </c>
@@ -4706,13 +4911,16 @@
         <v>251</v>
       </c>
       <c r="C67" s="49" t="s">
-        <v>814</v>
-      </c>
-      <c r="D67" s="50" t="s">
+        <v>811</v>
+      </c>
+      <c r="D67" s="49" t="s">
+        <v>922</v>
+      </c>
+      <c r="E67" s="50" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="48">
         <v>1</v>
       </c>
@@ -4722,11 +4930,14 @@
       <c r="C68" s="49" t="s">
         <v>253</v>
       </c>
-      <c r="D68" s="50" t="s">
+      <c r="D68" s="49" t="s">
+        <v>922</v>
+      </c>
+      <c r="E68" s="50" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="48">
         <v>1</v>
       </c>
@@ -4734,13 +4945,16 @@
         <v>257</v>
       </c>
       <c r="C69" s="49" t="s">
-        <v>815</v>
-      </c>
-      <c r="D69" s="50" t="s">
+        <v>812</v>
+      </c>
+      <c r="D69" s="49" t="s">
+        <v>921</v>
+      </c>
+      <c r="E69" s="50" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="48">
         <v>1</v>
       </c>
@@ -4750,11 +4964,14 @@
       <c r="C70" s="49" t="s">
         <v>259</v>
       </c>
-      <c r="D70" s="50" t="s">
+      <c r="D70" s="49" t="s">
+        <v>921</v>
+      </c>
+      <c r="E70" s="50" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="48">
         <v>1</v>
       </c>
@@ -4762,13 +4979,16 @@
         <v>261</v>
       </c>
       <c r="C71" s="49" t="s">
-        <v>816</v>
-      </c>
-      <c r="D71" s="50" t="s">
+        <v>813</v>
+      </c>
+      <c r="D71" s="49" t="s">
+        <v>922</v>
+      </c>
+      <c r="E71" s="50" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="48">
         <v>1</v>
       </c>
@@ -4776,13 +4996,16 @@
         <v>263</v>
       </c>
       <c r="C72" s="49" t="s">
-        <v>817</v>
-      </c>
-      <c r="D72" s="50" t="s">
+        <v>814</v>
+      </c>
+      <c r="D72" s="49" t="s">
+        <v>922</v>
+      </c>
+      <c r="E72" s="50" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="48">
         <v>2</v>
       </c>
@@ -4792,11 +5015,14 @@
       <c r="C73" s="48" t="s">
         <v>279</v>
       </c>
-      <c r="D73" s="53" t="s">
+      <c r="D73" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E73" s="53" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="48">
         <v>2</v>
       </c>
@@ -4806,11 +5032,14 @@
       <c r="C74" s="48" t="s">
         <v>281</v>
       </c>
-      <c r="D74" s="53" t="s">
+      <c r="D74" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E74" s="53" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="48">
         <v>2</v>
       </c>
@@ -4820,11 +5049,14 @@
       <c r="C75" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="D75" s="53" t="s">
+      <c r="D75" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E75" s="53" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="48">
         <v>2</v>
       </c>
@@ -4834,11 +5066,14 @@
       <c r="C76" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="D76" s="53" t="s">
+      <c r="D76" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E76" s="53" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="48">
         <v>2</v>
       </c>
@@ -4846,13 +5081,16 @@
         <v>323</v>
       </c>
       <c r="C77" s="48" t="s">
-        <v>818</v>
-      </c>
-      <c r="D77" s="53" t="s">
+        <v>815</v>
+      </c>
+      <c r="D77" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E77" s="53" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="48">
         <v>2</v>
       </c>
@@ -4860,13 +5098,16 @@
         <v>285</v>
       </c>
       <c r="C78" s="48" t="s">
-        <v>819</v>
-      </c>
-      <c r="D78" s="53" t="s">
+        <v>816</v>
+      </c>
+      <c r="D78" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E78" s="53" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="48">
         <v>2</v>
       </c>
@@ -4876,11 +5117,14 @@
       <c r="C79" s="48" t="s">
         <v>287</v>
       </c>
-      <c r="D79" s="53" t="s">
+      <c r="D79" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E79" s="53" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="48">
         <v>2</v>
       </c>
@@ -4888,13 +5132,16 @@
         <v>64</v>
       </c>
       <c r="C80" s="48" t="s">
-        <v>820</v>
-      </c>
-      <c r="D80" s="53" t="s">
+        <v>817</v>
+      </c>
+      <c r="D80" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E80" s="53" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="48">
         <v>2</v>
       </c>
@@ -4904,11 +5151,14 @@
       <c r="C81" s="48" t="s">
         <v>289</v>
       </c>
-      <c r="D81" s="53" t="s">
+      <c r="D81" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E81" s="53" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="48">
         <v>2</v>
       </c>
@@ -4918,11 +5168,14 @@
       <c r="C82" s="48" t="s">
         <v>291</v>
       </c>
-      <c r="D82" s="53" t="s">
+      <c r="D82" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E82" s="53" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="48">
         <v>2</v>
       </c>
@@ -4932,11 +5185,14 @@
       <c r="C83" s="48" t="s">
         <v>293</v>
       </c>
-      <c r="D83" s="53" t="s">
+      <c r="D83" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E83" s="53" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="48">
         <v>2</v>
       </c>
@@ -4946,11 +5202,14 @@
       <c r="C84" s="48" t="s">
         <v>295</v>
       </c>
-      <c r="D84" s="53" t="s">
+      <c r="D84" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E84" s="53" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="48">
         <v>2</v>
       </c>
@@ -4960,11 +5219,14 @@
       <c r="C85" s="48" t="s">
         <v>297</v>
       </c>
-      <c r="D85" s="53" t="s">
+      <c r="D85" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E85" s="53" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="48">
         <v>2</v>
       </c>
@@ -4974,11 +5236,14 @@
       <c r="C86" s="48" t="s">
         <v>300</v>
       </c>
-      <c r="D86" s="53" t="s">
+      <c r="D86" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E86" s="53" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="48">
         <v>2</v>
       </c>
@@ -4986,13 +5251,16 @@
         <v>301</v>
       </c>
       <c r="C87" s="48" t="s">
-        <v>821</v>
-      </c>
-      <c r="D87" s="53" t="s">
+        <v>818</v>
+      </c>
+      <c r="D87" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E87" s="53" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="48">
         <v>2</v>
       </c>
@@ -5000,13 +5268,16 @@
         <v>303</v>
       </c>
       <c r="C88" s="48" t="s">
-        <v>822</v>
-      </c>
-      <c r="D88" s="53" t="s">
+        <v>819</v>
+      </c>
+      <c r="D88" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E88" s="53" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="48">
         <v>2</v>
       </c>
@@ -5016,11 +5287,14 @@
       <c r="C89" s="48" t="s">
         <v>305</v>
       </c>
-      <c r="D89" s="53" t="s">
+      <c r="D89" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E89" s="53" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="48">
         <v>2</v>
       </c>
@@ -5030,11 +5304,14 @@
       <c r="C90" s="48" t="s">
         <v>307</v>
       </c>
-      <c r="D90" s="53" t="s">
+      <c r="D90" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E90" s="53" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="48">
         <v>2</v>
       </c>
@@ -5042,13 +5319,16 @@
         <v>310</v>
       </c>
       <c r="C91" s="48" t="s">
-        <v>823</v>
-      </c>
-      <c r="D91" s="53" t="s">
+        <v>820</v>
+      </c>
+      <c r="D91" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E91" s="53" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="48">
         <v>2</v>
       </c>
@@ -5058,11 +5338,14 @@
       <c r="C92" s="48" t="s">
         <v>312</v>
       </c>
-      <c r="D92" s="53" t="s">
+      <c r="D92" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E92" s="53" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="48">
         <v>2</v>
       </c>
@@ -5072,11 +5355,14 @@
       <c r="C93" s="48" t="s">
         <v>314</v>
       </c>
-      <c r="D93" s="53" t="s">
+      <c r="D93" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E93" s="53" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="48">
         <v>2</v>
       </c>
@@ -5086,11 +5372,14 @@
       <c r="C94" s="48" t="s">
         <v>327</v>
       </c>
-      <c r="D94" s="53" t="s">
+      <c r="D94" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E94" s="53" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="48">
         <v>2</v>
       </c>
@@ -5100,11 +5389,14 @@
       <c r="C95" s="48" t="s">
         <v>316</v>
       </c>
-      <c r="D95" s="53" t="s">
+      <c r="D95" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E95" s="53" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="48">
         <v>2</v>
       </c>
@@ -5112,13 +5404,16 @@
         <v>318</v>
       </c>
       <c r="C96" s="48" t="s">
-        <v>824</v>
-      </c>
-      <c r="D96" s="53" t="s">
+        <v>821</v>
+      </c>
+      <c r="D96" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E96" s="53" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="48">
         <v>2</v>
       </c>
@@ -5128,11 +5423,14 @@
       <c r="C97" s="48" t="s">
         <v>320</v>
       </c>
-      <c r="D97" s="53" t="s">
+      <c r="D97" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E97" s="53" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="48">
         <v>2</v>
       </c>
@@ -5142,11 +5440,14 @@
       <c r="C98" s="48" t="s">
         <v>337</v>
       </c>
-      <c r="D98" s="53" t="s">
+      <c r="D98" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E98" s="53" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="48">
         <v>2</v>
       </c>
@@ -5156,11 +5457,14 @@
       <c r="C99" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="D99" s="53" t="s">
+      <c r="D99" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E99" s="53" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="48">
         <v>2</v>
       </c>
@@ -5168,13 +5472,16 @@
         <v>59</v>
       </c>
       <c r="C100" s="48" t="s">
-        <v>825</v>
-      </c>
-      <c r="D100" s="53" t="s">
+        <v>822</v>
+      </c>
+      <c r="D100" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E100" s="53" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="48">
         <v>2</v>
       </c>
@@ -5182,13 +5489,16 @@
         <v>61</v>
       </c>
       <c r="C101" s="48" t="s">
-        <v>826</v>
-      </c>
-      <c r="D101" s="53" t="s">
+        <v>823</v>
+      </c>
+      <c r="D101" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E101" s="53" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="48">
         <v>2</v>
       </c>
@@ -5196,13 +5506,16 @@
         <v>343</v>
       </c>
       <c r="C102" s="48" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="D102" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E102" s="48" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="48">
         <v>2</v>
       </c>
@@ -5212,11 +5525,14 @@
       <c r="C103" s="48" t="s">
         <v>342</v>
       </c>
-      <c r="D103" s="53" t="s">
+      <c r="D103" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E103" s="53" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="48">
         <v>2</v>
       </c>
@@ -5226,11 +5542,14 @@
       <c r="C104" s="48" t="s">
         <v>329</v>
       </c>
-      <c r="D104" s="53" t="s">
+      <c r="D104" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E104" s="53" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="48">
         <v>2</v>
       </c>
@@ -5240,11 +5559,14 @@
       <c r="C105" s="48" t="s">
         <v>331</v>
       </c>
-      <c r="D105" s="53" t="s">
+      <c r="D105" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E105" s="53" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="48">
         <v>2</v>
       </c>
@@ -5254,11 +5576,14 @@
       <c r="C106" s="48" t="s">
         <v>333</v>
       </c>
-      <c r="D106" s="53" t="s">
+      <c r="D106" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E106" s="53" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="48">
         <v>2</v>
       </c>
@@ -5268,11 +5593,14 @@
       <c r="C107" s="48" t="s">
         <v>335</v>
       </c>
-      <c r="D107" s="53" t="s">
+      <c r="D107" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E107" s="53" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="48">
         <v>2</v>
       </c>
@@ -5280,13 +5608,16 @@
         <v>346</v>
       </c>
       <c r="C108" s="48" t="s">
-        <v>828</v>
-      </c>
-      <c r="D108" s="53" t="s">
+        <v>825</v>
+      </c>
+      <c r="D108" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E108" s="53" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="48">
         <v>2</v>
       </c>
@@ -5294,13 +5625,16 @@
         <v>348</v>
       </c>
       <c r="C109" s="48" t="s">
-        <v>829</v>
-      </c>
-      <c r="D109" s="53" t="s">
+        <v>826</v>
+      </c>
+      <c r="D109" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E109" s="53" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="48">
         <v>2</v>
       </c>
@@ -5310,11 +5644,14 @@
       <c r="C110" s="48" t="s">
         <v>350</v>
       </c>
-      <c r="D110" s="53" t="s">
+      <c r="D110" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E110" s="53" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="48">
         <v>2</v>
       </c>
@@ -5324,11 +5661,14 @@
       <c r="C111" s="48" t="s">
         <v>352</v>
       </c>
-      <c r="D111" s="53" t="s">
+      <c r="D111" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E111" s="53" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="48">
         <v>2</v>
       </c>
@@ -5336,13 +5676,16 @@
         <v>356</v>
       </c>
       <c r="C112" s="48" t="s">
-        <v>830</v>
-      </c>
-      <c r="D112" s="53" t="s">
+        <v>827</v>
+      </c>
+      <c r="D112" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E112" s="53" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="48">
         <v>2</v>
       </c>
@@ -5352,11 +5695,14 @@
       <c r="C113" s="48" t="s">
         <v>354</v>
       </c>
-      <c r="D113" s="53" t="s">
+      <c r="D113" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E113" s="53" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="48">
         <v>2</v>
       </c>
@@ -5364,13 +5710,16 @@
         <v>358</v>
       </c>
       <c r="C114" s="48" t="s">
-        <v>831</v>
-      </c>
-      <c r="D114" s="53" t="s">
+        <v>828</v>
+      </c>
+      <c r="D114" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E114" s="53" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="48">
         <v>2</v>
       </c>
@@ -5380,11 +5729,14 @@
       <c r="C115" s="48" t="s">
         <v>360</v>
       </c>
-      <c r="D115" s="53" t="s">
+      <c r="D115" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E115" s="53" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="48">
         <v>2</v>
       </c>
@@ -5392,13 +5744,16 @@
         <v>362</v>
       </c>
       <c r="C116" s="48" t="s">
-        <v>832</v>
-      </c>
-      <c r="D116" s="53" t="s">
+        <v>829</v>
+      </c>
+      <c r="D116" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E116" s="53" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="48">
         <v>2</v>
       </c>
@@ -5406,13 +5761,16 @@
         <v>364</v>
       </c>
       <c r="C117" s="48" t="s">
-        <v>833</v>
-      </c>
-      <c r="D117" s="53" t="s">
+        <v>830</v>
+      </c>
+      <c r="D117" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E117" s="53" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="48">
         <v>2</v>
       </c>
@@ -5420,13 +5778,16 @@
         <v>370</v>
       </c>
       <c r="C118" s="48" t="s">
-        <v>834</v>
-      </c>
-      <c r="D118" s="53" t="s">
+        <v>831</v>
+      </c>
+      <c r="D118" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E118" s="53" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="48">
         <v>2</v>
       </c>
@@ -5434,13 +5795,16 @@
         <v>366</v>
       </c>
       <c r="C119" s="48" t="s">
-        <v>835</v>
-      </c>
-      <c r="D119" s="53" t="s">
+        <v>832</v>
+      </c>
+      <c r="D119" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E119" s="53" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="48">
         <v>2</v>
       </c>
@@ -5450,11 +5814,14 @@
       <c r="C120" s="48" t="s">
         <v>368</v>
       </c>
-      <c r="D120" s="53" t="s">
+      <c r="D120" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E120" s="53" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="48">
         <v>2</v>
       </c>
@@ -5462,13 +5829,16 @@
         <v>372</v>
       </c>
       <c r="C121" s="48" t="s">
-        <v>836</v>
-      </c>
-      <c r="D121" s="53" t="s">
+        <v>833</v>
+      </c>
+      <c r="D121" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E121" s="53" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="48">
         <v>2</v>
       </c>
@@ -5478,11 +5848,14 @@
       <c r="C122" s="48" t="s">
         <v>374</v>
       </c>
-      <c r="D122" s="53" t="s">
+      <c r="D122" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E122" s="53" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="48">
         <v>2</v>
       </c>
@@ -5490,13 +5863,16 @@
         <v>376</v>
       </c>
       <c r="C123" s="48" t="s">
-        <v>837</v>
-      </c>
-      <c r="D123" s="53" t="s">
+        <v>834</v>
+      </c>
+      <c r="D123" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E123" s="53" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="48">
         <v>3</v>
       </c>
@@ -5504,13 +5880,16 @@
         <v>379</v>
       </c>
       <c r="C124" t="s">
-        <v>838</v>
-      </c>
-      <c r="D124" t="s">
+        <v>835</v>
+      </c>
+      <c r="D124" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E124" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="48">
         <v>3</v>
       </c>
@@ -5520,11 +5899,14 @@
       <c r="C125" t="s">
         <v>381</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D125" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E125" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="48">
         <v>3</v>
       </c>
@@ -5534,11 +5916,14 @@
       <c r="C126" t="s">
         <v>383</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D126" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E126" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="48">
         <v>3</v>
       </c>
@@ -5548,11 +5933,14 @@
       <c r="C127" t="s">
         <v>385</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D127" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E127" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="48">
         <v>3</v>
       </c>
@@ -5560,13 +5948,16 @@
         <v>387</v>
       </c>
       <c r="C128" t="s">
-        <v>839</v>
-      </c>
-      <c r="D128" t="s">
+        <v>836</v>
+      </c>
+      <c r="D128" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E128" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="48">
         <v>3</v>
       </c>
@@ -5576,11 +5967,14 @@
       <c r="C129" t="s">
         <v>389</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D129" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E129" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="48">
         <v>3</v>
       </c>
@@ -5590,11 +5984,14 @@
       <c r="C130" t="s">
         <v>391</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D130" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E130" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="48">
         <v>3</v>
       </c>
@@ -5602,13 +5999,16 @@
         <v>393</v>
       </c>
       <c r="C131" t="s">
-        <v>840</v>
-      </c>
-      <c r="D131" t="s">
+        <v>837</v>
+      </c>
+      <c r="D131" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E131" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="48">
         <v>3</v>
       </c>
@@ -5616,13 +6016,16 @@
         <v>395</v>
       </c>
       <c r="C132" t="s">
-        <v>841</v>
-      </c>
-      <c r="D132" t="s">
+        <v>838</v>
+      </c>
+      <c r="D132" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E132" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="48">
         <v>3</v>
       </c>
@@ -5632,11 +6035,14 @@
       <c r="C133" t="s">
         <v>397</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D133" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E133" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="48">
         <v>3</v>
       </c>
@@ -5644,13 +6050,16 @@
         <v>399</v>
       </c>
       <c r="C134" t="s">
-        <v>842</v>
-      </c>
-      <c r="D134" t="s">
+        <v>839</v>
+      </c>
+      <c r="D134" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E134" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="48">
         <v>3</v>
       </c>
@@ -5660,11 +6069,14 @@
       <c r="C135" t="s">
         <v>401</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D135" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E135" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="48">
         <v>3</v>
       </c>
@@ -5674,11 +6086,14 @@
       <c r="C136" t="s">
         <v>403</v>
       </c>
-      <c r="D136" t="s">
+      <c r="D136" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E136" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="48">
         <v>3</v>
       </c>
@@ -5688,11 +6103,14 @@
       <c r="C137" t="s">
         <v>405</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D137" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E137" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="48">
         <v>3</v>
       </c>
@@ -5700,13 +6118,16 @@
         <v>407</v>
       </c>
       <c r="C138" t="s">
-        <v>843</v>
-      </c>
-      <c r="D138" t="s">
+        <v>840</v>
+      </c>
+      <c r="D138" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E138" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="48">
         <v>3</v>
       </c>
@@ -5714,13 +6135,16 @@
         <v>409</v>
       </c>
       <c r="C139" t="s">
-        <v>844</v>
-      </c>
-      <c r="D139" t="s">
+        <v>841</v>
+      </c>
+      <c r="D139" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E139" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="48">
         <v>3</v>
       </c>
@@ -5730,11 +6154,14 @@
       <c r="C140" t="s">
         <v>411</v>
       </c>
-      <c r="D140" t="s">
+      <c r="D140" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E140" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="48">
         <v>3</v>
       </c>
@@ -5744,11 +6171,14 @@
       <c r="C141" t="s">
         <v>414</v>
       </c>
-      <c r="D141" t="s">
+      <c r="D141" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E141" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="48">
         <v>3</v>
       </c>
@@ -5756,13 +6186,16 @@
         <v>417</v>
       </c>
       <c r="C142" t="s">
-        <v>845</v>
-      </c>
-      <c r="D142" t="s">
+        <v>842</v>
+      </c>
+      <c r="D142" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E142" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="48">
         <v>3</v>
       </c>
@@ -5770,13 +6203,16 @@
         <v>419</v>
       </c>
       <c r="C143" t="s">
-        <v>846</v>
-      </c>
-      <c r="D143" t="s">
+        <v>843</v>
+      </c>
+      <c r="D143" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E143" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="48">
         <v>3</v>
       </c>
@@ -5786,11 +6222,14 @@
       <c r="C144" t="s">
         <v>421</v>
       </c>
-      <c r="D144" t="s">
+      <c r="D144" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E144" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="48">
         <v>3</v>
       </c>
@@ -5800,11 +6239,14 @@
       <c r="C145" t="s">
         <v>209</v>
       </c>
-      <c r="D145" t="s">
+      <c r="D145" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E145" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="48">
         <v>3</v>
       </c>
@@ -5814,11 +6256,14 @@
       <c r="C146" t="s">
         <v>423</v>
       </c>
-      <c r="D146" t="s">
+      <c r="D146" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E146" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="48">
         <v>3</v>
       </c>
@@ -5828,11 +6273,14 @@
       <c r="C147" t="s">
         <v>425</v>
       </c>
-      <c r="D147" t="s">
+      <c r="D147" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E147" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="48">
         <v>3</v>
       </c>
@@ -5842,11 +6290,14 @@
       <c r="C148" t="s">
         <v>427</v>
       </c>
-      <c r="D148" t="s">
+      <c r="D148" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E148" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="48">
         <v>3</v>
       </c>
@@ -5856,11 +6307,14 @@
       <c r="C149" t="s">
         <v>715</v>
       </c>
-      <c r="D149" t="s">
+      <c r="D149" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E149" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="48">
         <v>3</v>
       </c>
@@ -5870,11 +6324,14 @@
       <c r="C150" t="s">
         <v>430</v>
       </c>
-      <c r="D150" t="s">
+      <c r="D150" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E150" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="48">
         <v>3</v>
       </c>
@@ -5882,13 +6339,16 @@
         <v>432</v>
       </c>
       <c r="C151" t="s">
-        <v>847</v>
-      </c>
-      <c r="D151" t="s">
+        <v>844</v>
+      </c>
+      <c r="D151" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E151" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="48">
         <v>3</v>
       </c>
@@ -5896,13 +6356,16 @@
         <v>126</v>
       </c>
       <c r="C152" s="48" t="s">
-        <v>848</v>
-      </c>
-      <c r="D152" s="53" t="s">
+        <v>845</v>
+      </c>
+      <c r="D152" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E152" s="53" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="48">
         <v>3</v>
       </c>
@@ -5912,11 +6375,14 @@
       <c r="C153" s="44" t="s">
         <v>435</v>
       </c>
-      <c r="D153" s="44" t="s">
+      <c r="D153" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E153" s="44" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="48">
         <v>3</v>
       </c>
@@ -5926,11 +6392,14 @@
       <c r="C154" s="44" t="s">
         <v>436</v>
       </c>
-      <c r="D154" s="44" t="s">
+      <c r="D154" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E154" s="44" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="48">
         <v>3</v>
       </c>
@@ -5940,11 +6409,14 @@
       <c r="C155" s="51" t="s">
         <v>439</v>
       </c>
-      <c r="D155" s="44" t="s">
+      <c r="D155" s="51" t="s">
+        <v>922</v>
+      </c>
+      <c r="E155" s="44" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="48">
         <v>3</v>
       </c>
@@ -5954,11 +6426,14 @@
       <c r="C156" s="44" t="s">
         <v>322</v>
       </c>
-      <c r="D156" s="44" t="s">
+      <c r="D156" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E156" s="44" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="48">
         <v>3</v>
       </c>
@@ -5966,13 +6441,16 @@
         <v>44</v>
       </c>
       <c r="C157" s="44" t="s">
-        <v>849</v>
-      </c>
-      <c r="D157" s="44" t="s">
+        <v>846</v>
+      </c>
+      <c r="D157" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E157" s="44" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="48">
         <v>3</v>
       </c>
@@ -5982,11 +6460,14 @@
       <c r="C158" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="D158" s="44" t="s">
+      <c r="D158" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E158" s="44" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="48">
         <v>3</v>
       </c>
@@ -5996,11 +6477,14 @@
       <c r="C159" s="44" t="s">
         <v>160</v>
       </c>
-      <c r="D159" s="44" t="s">
+      <c r="D159" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E159" s="44" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="48">
         <v>3</v>
       </c>
@@ -6008,13 +6492,16 @@
         <v>440</v>
       </c>
       <c r="C160" t="s">
-        <v>850</v>
-      </c>
-      <c r="D160" t="s">
+        <v>847</v>
+      </c>
+      <c r="D160" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E160" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="48">
         <v>3</v>
       </c>
@@ -6022,13 +6509,16 @@
         <v>442</v>
       </c>
       <c r="C161" t="s">
-        <v>851</v>
-      </c>
-      <c r="D161" t="s">
+        <v>848</v>
+      </c>
+      <c r="D161" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E161" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="48">
         <v>3</v>
       </c>
@@ -6036,13 +6526,16 @@
         <v>445</v>
       </c>
       <c r="C162" t="s">
-        <v>852</v>
-      </c>
-      <c r="D162" t="s">
+        <v>849</v>
+      </c>
+      <c r="D162" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E162" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="48">
         <v>3</v>
       </c>
@@ -6050,13 +6543,16 @@
         <v>447</v>
       </c>
       <c r="C163" t="s">
-        <v>853</v>
-      </c>
-      <c r="D163" t="s">
+        <v>850</v>
+      </c>
+      <c r="D163" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E163" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="48">
         <v>3</v>
       </c>
@@ -6064,13 +6560,16 @@
         <v>449</v>
       </c>
       <c r="C164" t="s">
-        <v>854</v>
-      </c>
-      <c r="D164" t="s">
+        <v>851</v>
+      </c>
+      <c r="D164" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E164" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="48">
         <v>3</v>
       </c>
@@ -6078,13 +6577,16 @@
         <v>451</v>
       </c>
       <c r="C165" t="s">
-        <v>855</v>
-      </c>
-      <c r="D165" t="s">
+        <v>852</v>
+      </c>
+      <c r="D165" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E165" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="48">
         <v>3</v>
       </c>
@@ -6094,11 +6596,14 @@
       <c r="C166" t="s">
         <v>453</v>
       </c>
-      <c r="D166" t="s">
+      <c r="D166" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E166" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="48">
         <v>3</v>
       </c>
@@ -6106,13 +6611,16 @@
         <v>455</v>
       </c>
       <c r="C167" t="s">
-        <v>856</v>
-      </c>
-      <c r="D167" t="s">
+        <v>853</v>
+      </c>
+      <c r="D167" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E167" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="48">
         <v>3</v>
       </c>
@@ -6120,13 +6628,16 @@
         <v>459</v>
       </c>
       <c r="C168" t="s">
-        <v>857</v>
-      </c>
-      <c r="D168" t="s">
+        <v>854</v>
+      </c>
+      <c r="D168" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E168" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="48">
         <v>3</v>
       </c>
@@ -6134,13 +6645,16 @@
         <v>457</v>
       </c>
       <c r="C169" t="s">
-        <v>858</v>
-      </c>
-      <c r="D169" t="s">
+        <v>855</v>
+      </c>
+      <c r="D169" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E169" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="48">
         <v>3</v>
       </c>
@@ -6150,11 +6664,14 @@
       <c r="C170" t="s">
         <v>461</v>
       </c>
-      <c r="D170" t="s">
+      <c r="D170" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E170" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="48">
         <v>3</v>
       </c>
@@ -6164,11 +6681,14 @@
       <c r="C171" t="s">
         <v>467</v>
       </c>
-      <c r="D171" t="s">
+      <c r="D171" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E171" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="48">
         <v>3</v>
       </c>
@@ -6178,11 +6698,14 @@
       <c r="C172" t="s">
         <v>463</v>
       </c>
-      <c r="D172" t="s">
+      <c r="D172" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E172" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="48">
         <v>3</v>
       </c>
@@ -6192,11 +6715,14 @@
       <c r="C173" t="s">
         <v>465</v>
       </c>
-      <c r="D173" t="s">
+      <c r="D173" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E173" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A174" s="48">
         <v>3</v>
       </c>
@@ -6204,13 +6730,16 @@
         <v>469</v>
       </c>
       <c r="C174" t="s">
-        <v>859</v>
-      </c>
-      <c r="D174" t="s">
+        <v>856</v>
+      </c>
+      <c r="D174" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E174" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A175" s="48">
         <v>3</v>
       </c>
@@ -6218,13 +6747,16 @@
         <v>471</v>
       </c>
       <c r="C175" t="s">
-        <v>860</v>
-      </c>
-      <c r="D175" t="s">
+        <v>857</v>
+      </c>
+      <c r="D175" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E175" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A176" s="48">
         <v>3</v>
       </c>
@@ -6232,13 +6764,16 @@
         <v>732</v>
       </c>
       <c r="C176" t="s">
-        <v>861</v>
-      </c>
-      <c r="D176" t="s">
+        <v>858</v>
+      </c>
+      <c r="D176" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E176" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A177" s="48">
         <v>3</v>
       </c>
@@ -6246,13 +6781,16 @@
         <v>734</v>
       </c>
       <c r="C177" t="s">
-        <v>862</v>
-      </c>
-      <c r="D177" t="s">
+        <v>859</v>
+      </c>
+      <c r="D177" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E177" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A178" s="48">
         <v>3</v>
       </c>
@@ -6262,11 +6800,14 @@
       <c r="C178" t="s">
         <v>736</v>
       </c>
-      <c r="D178" t="s">
+      <c r="D178" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E178" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="48">
         <v>3</v>
       </c>
@@ -6274,13 +6815,16 @@
         <v>738</v>
       </c>
       <c r="C179" t="s">
-        <v>863</v>
-      </c>
-      <c r="D179" t="s">
+        <v>860</v>
+      </c>
+      <c r="D179" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E179" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="48">
         <v>3</v>
       </c>
@@ -6290,11 +6834,14 @@
       <c r="C180" t="s">
         <v>740</v>
       </c>
-      <c r="D180" t="s">
+      <c r="D180" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E180" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="48">
         <v>3</v>
       </c>
@@ -6302,13 +6849,16 @@
         <v>742</v>
       </c>
       <c r="C181" t="s">
-        <v>864</v>
-      </c>
-      <c r="D181" t="s">
+        <v>861</v>
+      </c>
+      <c r="D181" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E181" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A182" s="48">
         <v>4</v>
       </c>
@@ -6318,11 +6868,14 @@
       <c r="C182" t="s">
         <v>473</v>
       </c>
-      <c r="D182" t="s">
+      <c r="D182" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E182" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="48">
         <v>4</v>
       </c>
@@ -6332,11 +6885,14 @@
       <c r="C183" t="s">
         <v>475</v>
       </c>
-      <c r="D183" t="s">
+      <c r="D183" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E183" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A184" s="48">
         <v>4</v>
       </c>
@@ -6346,137 +6902,167 @@
       <c r="C184" t="s">
         <v>477</v>
       </c>
-      <c r="D184" t="s">
+      <c r="D184" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E184" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A185" s="48">
         <v>4</v>
       </c>
       <c r="B185" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C185" t="s">
-        <v>479</v>
-      </c>
-      <c r="D185" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>481</v>
+      </c>
+      <c r="D185" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E185" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A186" s="48">
         <v>4</v>
       </c>
       <c r="B186" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C186" t="s">
-        <v>481</v>
-      </c>
-      <c r="D186" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>485</v>
+      </c>
+      <c r="D186" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E186" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A187" s="48">
         <v>4</v>
       </c>
       <c r="B187" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C187" t="s">
-        <v>483</v>
-      </c>
-      <c r="D187" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>487</v>
+      </c>
+      <c r="D187" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E187" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A188" s="48">
         <v>4</v>
       </c>
       <c r="B188" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="C188" t="s">
-        <v>485</v>
-      </c>
-      <c r="D188" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>493</v>
+      </c>
+      <c r="D188" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E188" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A189" s="48">
         <v>4</v>
       </c>
       <c r="B189" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="C189" t="s">
-        <v>487</v>
-      </c>
-      <c r="D189" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>495</v>
+      </c>
+      <c r="D189" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E189" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A190" s="48">
         <v>4</v>
       </c>
       <c r="B190" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="C190" t="s">
-        <v>865</v>
-      </c>
-      <c r="D190" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>479</v>
+      </c>
+      <c r="D190" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E190" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A191" s="48">
         <v>4</v>
       </c>
       <c r="B191" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="C191" t="s">
-        <v>866</v>
-      </c>
-      <c r="D191" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>483</v>
+      </c>
+      <c r="D191" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E191" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A192" s="48">
         <v>4</v>
       </c>
       <c r="B192" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C192" t="s">
-        <v>493</v>
-      </c>
-      <c r="D192" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>862</v>
+      </c>
+      <c r="D192" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E192" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A193" s="48">
         <v>4</v>
       </c>
       <c r="B193" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C193" t="s">
-        <v>495</v>
-      </c>
-      <c r="D193" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>863</v>
+      </c>
+      <c r="D193" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E193" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A194" s="48">
         <v>4</v>
       </c>
@@ -6484,13 +7070,16 @@
         <v>497</v>
       </c>
       <c r="C194" t="s">
-        <v>867</v>
-      </c>
-      <c r="D194" t="s">
+        <v>864</v>
+      </c>
+      <c r="D194" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E194" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A195" s="48">
         <v>4</v>
       </c>
@@ -6498,13 +7087,16 @@
         <v>499</v>
       </c>
       <c r="C195" t="s">
-        <v>868</v>
-      </c>
-      <c r="D195" t="s">
+        <v>865</v>
+      </c>
+      <c r="D195" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E195" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A196" s="48">
         <v>4</v>
       </c>
@@ -6514,11 +7106,14 @@
       <c r="C196" t="s">
         <v>501</v>
       </c>
-      <c r="D196" t="s">
+      <c r="D196" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E196" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A197" s="48">
         <v>4</v>
       </c>
@@ -6526,153 +7121,186 @@
         <v>503</v>
       </c>
       <c r="C197" t="s">
-        <v>869</v>
-      </c>
-      <c r="D197" t="s">
+        <v>866</v>
+      </c>
+      <c r="D197" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E197" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A198" s="48">
         <v>4</v>
       </c>
       <c r="B198" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C198" t="s">
-        <v>870</v>
-      </c>
-      <c r="D198" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>507</v>
+      </c>
+      <c r="D198" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E198" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A199" s="48">
         <v>4</v>
       </c>
       <c r="B199" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C199" t="s">
-        <v>507</v>
-      </c>
-      <c r="D199" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>509</v>
+      </c>
+      <c r="D199" s="48" t="s">
+        <v>922</v>
+      </c>
+      <c r="E199" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A200" s="48">
         <v>4</v>
       </c>
       <c r="B200" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C200" t="s">
-        <v>509</v>
-      </c>
-      <c r="D200" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>511</v>
+      </c>
+      <c r="D200" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E200" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A201" s="48">
         <v>4</v>
       </c>
       <c r="B201" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C201" t="s">
-        <v>511</v>
-      </c>
-      <c r="D201" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>513</v>
+      </c>
+      <c r="D201" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E201" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A202" s="48">
         <v>4</v>
       </c>
       <c r="B202" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C202" t="s">
-        <v>513</v>
-      </c>
-      <c r="D202" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>515</v>
+      </c>
+      <c r="D202" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E202" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A203" s="48">
         <v>4</v>
       </c>
       <c r="B203" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="C203" t="s">
-        <v>515</v>
-      </c>
-      <c r="D203" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>535</v>
+      </c>
+      <c r="D203" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E203" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A204" s="48">
         <v>4</v>
       </c>
       <c r="B204" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="C204" t="s">
-        <v>535</v>
-      </c>
-      <c r="D204" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>868</v>
+      </c>
+      <c r="D204" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E204" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A205" s="48">
         <v>4</v>
       </c>
       <c r="B205" t="s">
-        <v>519</v>
+        <v>129</v>
       </c>
       <c r="C205" t="s">
-        <v>871</v>
-      </c>
-      <c r="D205" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>129</v>
+      </c>
+      <c r="D205" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E205" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A206" s="48">
         <v>4</v>
       </c>
       <c r="B206" t="s">
-        <v>129</v>
+        <v>522</v>
       </c>
       <c r="C206" t="s">
-        <v>129</v>
-      </c>
-      <c r="D206" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>869</v>
+      </c>
+      <c r="D206" s="48" t="s">
+        <v>921</v>
+      </c>
+      <c r="E206" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A207" s="48">
         <v>4</v>
       </c>
       <c r="B207" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="C207" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="D207" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>922</v>
+      </c>
+      <c r="E207" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A208" s="48">
         <v>4</v>
       </c>
@@ -6683,10 +7311,13 @@
         <v>524</v>
       </c>
       <c r="D208" t="s">
+        <v>922</v>
+      </c>
+      <c r="E208" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A209" s="48">
         <v>4</v>
       </c>
@@ -6694,83 +7325,101 @@
         <v>526</v>
       </c>
       <c r="C209" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="D209" t="s">
+        <v>922</v>
+      </c>
+      <c r="E209" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A210" s="48">
         <v>4</v>
       </c>
       <c r="B210" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="C210" t="s">
-        <v>528</v>
+        <v>873</v>
       </c>
       <c r="D210" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>922</v>
+      </c>
+      <c r="E210" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A211" s="48">
         <v>4</v>
       </c>
       <c r="B211" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C211" t="s">
-        <v>874</v>
+        <v>528</v>
       </c>
       <c r="D211" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>922</v>
+      </c>
+      <c r="E211" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A212" s="48">
         <v>4</v>
       </c>
       <c r="B212" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C212" t="s">
-        <v>532</v>
+        <v>871</v>
       </c>
       <c r="D212" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>922</v>
+      </c>
+      <c r="E212" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A213" s="48">
         <v>4</v>
       </c>
       <c r="B213" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C213" t="s">
-        <v>875</v>
+        <v>532</v>
       </c>
       <c r="D213" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>922</v>
+      </c>
+      <c r="E213" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A214" s="48">
         <v>4</v>
       </c>
       <c r="B214" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="C214" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="D214" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>922</v>
+      </c>
+      <c r="E214" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A215" s="48">
         <v>4</v>
       </c>
@@ -6781,10 +7430,13 @@
         <v>541</v>
       </c>
       <c r="D215" t="s">
+        <v>922</v>
+      </c>
+      <c r="E215" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A216" s="48">
         <v>4</v>
       </c>
@@ -6792,13 +7444,16 @@
         <v>718</v>
       </c>
       <c r="C216" s="103" t="s">
-        <v>877</v>
-      </c>
-      <c r="D216" s="102" t="s">
+        <v>874</v>
+      </c>
+      <c r="D216" s="103" t="s">
+        <v>922</v>
+      </c>
+      <c r="E216" s="102" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A217" s="48">
         <v>4</v>
       </c>
@@ -6809,10 +7464,13 @@
         <v>543</v>
       </c>
       <c r="D217" t="s">
+        <v>922</v>
+      </c>
+      <c r="E217" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A218" s="48">
         <v>4</v>
       </c>
@@ -6823,10 +7481,13 @@
         <v>545</v>
       </c>
       <c r="D218" t="s">
+        <v>922</v>
+      </c>
+      <c r="E218" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A219" s="48">
         <v>4</v>
       </c>
@@ -6834,13 +7495,16 @@
         <v>549</v>
       </c>
       <c r="C219" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="D219" t="s">
+        <v>921</v>
+      </c>
+      <c r="E219" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A220" s="48">
         <v>4</v>
       </c>
@@ -6848,13 +7512,16 @@
         <v>551</v>
       </c>
       <c r="C220" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="D220" t="s">
+        <v>921</v>
+      </c>
+      <c r="E220" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A221" s="48">
         <v>4</v>
       </c>
@@ -6862,13 +7529,16 @@
         <v>553</v>
       </c>
       <c r="C221" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="D221" t="s">
+        <v>922</v>
+      </c>
+      <c r="E221" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A222" s="48">
         <v>4</v>
       </c>
@@ -6876,13 +7546,16 @@
         <v>555</v>
       </c>
       <c r="C222" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="D222" t="s">
+        <v>922</v>
+      </c>
+      <c r="E222" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A223" s="48">
         <v>4</v>
       </c>
@@ -6893,10 +7566,13 @@
         <v>557</v>
       </c>
       <c r="D223" t="s">
+        <v>921</v>
+      </c>
+      <c r="E223" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A224" s="48">
         <v>4</v>
       </c>
@@ -6906,11 +7582,14 @@
       <c r="C224" s="44" t="s">
         <v>559</v>
       </c>
-      <c r="D224" t="s">
+      <c r="D224" s="105" t="s">
+        <v>922</v>
+      </c>
+      <c r="E224" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A225" s="48">
         <v>4</v>
       </c>
@@ -6920,11 +7599,14 @@
       <c r="C225" t="s">
         <v>561</v>
       </c>
-      <c r="D225" t="s">
+      <c r="D225" s="105" t="s">
+        <v>921</v>
+      </c>
+      <c r="E225" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="226" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A226" s="48">
         <v>4</v>
       </c>
@@ -6932,13 +7614,16 @@
         <v>563</v>
       </c>
       <c r="C226" t="s">
-        <v>882</v>
-      </c>
-      <c r="D226" t="s">
+        <v>879</v>
+      </c>
+      <c r="D226" s="105" t="s">
+        <v>922</v>
+      </c>
+      <c r="E226" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="227" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A227" s="48">
         <v>4</v>
       </c>
@@ -6948,11 +7633,14 @@
       <c r="C227" t="s">
         <v>565</v>
       </c>
-      <c r="D227" t="s">
+      <c r="D227" s="105" t="s">
+        <v>921</v>
+      </c>
+      <c r="E227" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A228" s="48">
         <v>4</v>
       </c>
@@ -6962,11 +7650,14 @@
       <c r="C228" t="s">
         <v>567</v>
       </c>
-      <c r="D228" t="s">
+      <c r="D228" s="105" t="s">
+        <v>922</v>
+      </c>
+      <c r="E228" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A229" s="48">
         <v>4</v>
       </c>
@@ -6976,11 +7667,14 @@
       <c r="C229" t="s">
         <v>569</v>
       </c>
-      <c r="D229" t="s">
+      <c r="D229" s="105" t="s">
+        <v>921</v>
+      </c>
+      <c r="E229" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A230" s="48">
         <v>4</v>
       </c>
@@ -6988,13 +7682,16 @@
         <v>571</v>
       </c>
       <c r="C230" t="s">
-        <v>883</v>
-      </c>
-      <c r="D230" t="s">
+        <v>880</v>
+      </c>
+      <c r="D230" s="105" t="s">
+        <v>922</v>
+      </c>
+      <c r="E230" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="231" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A231" s="48">
         <v>4</v>
       </c>
@@ -7002,13 +7699,16 @@
         <v>573</v>
       </c>
       <c r="C231" t="s">
-        <v>884</v>
-      </c>
-      <c r="D231" t="s">
+        <v>881</v>
+      </c>
+      <c r="D231" s="105" t="s">
+        <v>921</v>
+      </c>
+      <c r="E231" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A232" s="48">
         <v>4</v>
       </c>
@@ -7016,13 +7716,16 @@
         <v>575</v>
       </c>
       <c r="C232" t="s">
-        <v>885</v>
-      </c>
-      <c r="D232" t="s">
+        <v>882</v>
+      </c>
+      <c r="D232" s="105" t="s">
+        <v>921</v>
+      </c>
+      <c r="E232" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="233" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A233" s="48">
         <v>4</v>
       </c>
@@ -7032,11 +7735,14 @@
       <c r="C233" t="s">
         <v>577</v>
       </c>
-      <c r="D233" t="s">
+      <c r="D233" s="105" t="s">
+        <v>922</v>
+      </c>
+      <c r="E233" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A234" s="48">
         <v>4</v>
       </c>
@@ -7044,13 +7750,16 @@
         <v>579</v>
       </c>
       <c r="C234" t="s">
-        <v>886</v>
-      </c>
-      <c r="D234" t="s">
+        <v>883</v>
+      </c>
+      <c r="D234" s="105" t="s">
+        <v>922</v>
+      </c>
+      <c r="E234" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A235" s="48">
         <v>4</v>
       </c>
@@ -7060,11 +7769,14 @@
       <c r="C235" t="s">
         <v>581</v>
       </c>
-      <c r="D235" t="s">
+      <c r="D235" s="105" t="s">
+        <v>921</v>
+      </c>
+      <c r="E235" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A236" s="48">
         <v>4</v>
       </c>
@@ -7072,27 +7784,33 @@
         <v>583</v>
       </c>
       <c r="C236" t="s">
-        <v>887</v>
-      </c>
-      <c r="D236" t="s">
+        <v>884</v>
+      </c>
+      <c r="D236" s="105" t="s">
+        <v>921</v>
+      </c>
+      <c r="E236" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A237" s="48">
         <v>4</v>
       </c>
       <c r="B237" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C237" t="s">
-        <v>888</v>
-      </c>
-      <c r="D237" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>885</v>
+      </c>
+      <c r="D237" s="105" t="s">
+        <v>922</v>
+      </c>
+      <c r="E237" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A238" s="48">
         <v>4</v>
       </c>
@@ -7100,13 +7818,16 @@
         <v>585</v>
       </c>
       <c r="C238" t="s">
-        <v>889</v>
-      </c>
-      <c r="D238" t="s">
+        <v>886</v>
+      </c>
+      <c r="D238" s="105" t="s">
+        <v>922</v>
+      </c>
+      <c r="E238" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="239" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A239" s="48">
         <v>4</v>
       </c>
@@ -7114,13 +7835,16 @@
         <v>745</v>
       </c>
       <c r="C239" t="s">
-        <v>890</v>
-      </c>
-      <c r="D239" t="s">
+        <v>887</v>
+      </c>
+      <c r="D239" s="105" t="s">
+        <v>922</v>
+      </c>
+      <c r="E239" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A240" s="48">
         <v>4</v>
       </c>
@@ -7130,11 +7854,14 @@
       <c r="C240" t="s">
         <v>747</v>
       </c>
-      <c r="D240" t="s">
+      <c r="D240" s="105" t="s">
+        <v>921</v>
+      </c>
+      <c r="E240" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A241" s="48">
         <v>4</v>
       </c>
@@ -7142,13 +7869,16 @@
         <v>749</v>
       </c>
       <c r="C241" t="s">
-        <v>891</v>
-      </c>
-      <c r="D241" t="s">
+        <v>888</v>
+      </c>
+      <c r="D241" s="105" t="s">
+        <v>922</v>
+      </c>
+      <c r="E241" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="242" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A242" s="48">
         <v>4</v>
       </c>
@@ -7158,11 +7888,14 @@
       <c r="C242" t="s">
         <v>751</v>
       </c>
-      <c r="D242" t="s">
+      <c r="D242" s="105" t="s">
+        <v>921</v>
+      </c>
+      <c r="E242" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="243" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A243" s="48">
         <v>4</v>
       </c>
@@ -7172,11 +7905,14 @@
       <c r="C243" t="s">
         <v>753</v>
       </c>
-      <c r="D243" t="s">
+      <c r="D243" s="105" t="s">
+        <v>922</v>
+      </c>
+      <c r="E243" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A244" s="48">
         <v>4</v>
       </c>
@@ -7184,13 +7920,16 @@
         <v>755</v>
       </c>
       <c r="C244" t="s">
-        <v>892</v>
-      </c>
-      <c r="D244" t="s">
+        <v>889</v>
+      </c>
+      <c r="D244" s="105" t="s">
+        <v>921</v>
+      </c>
+      <c r="E244" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A245" s="48">
         <v>4</v>
       </c>
@@ -7198,13 +7937,16 @@
         <v>757</v>
       </c>
       <c r="C245" t="s">
-        <v>893</v>
-      </c>
-      <c r="D245" t="s">
+        <v>890</v>
+      </c>
+      <c r="D245" s="105" t="s">
+        <v>922</v>
+      </c>
+      <c r="E245" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A246" s="48">
         <v>4</v>
       </c>
@@ -7214,11 +7956,14 @@
       <c r="C246" t="s">
         <v>759</v>
       </c>
-      <c r="D246" t="s">
+      <c r="D246" s="105" t="s">
+        <v>921</v>
+      </c>
+      <c r="E246" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="48">
         <v>5</v>
       </c>
@@ -7228,11 +7973,14 @@
       <c r="C247" t="s">
         <v>720</v>
       </c>
-      <c r="D247" t="s">
+      <c r="D247" s="105" t="s">
+        <v>921</v>
+      </c>
+      <c r="E247" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A248" s="48">
         <v>5</v>
       </c>
@@ -7243,10 +7991,13 @@
         <v>597</v>
       </c>
       <c r="D248" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E248" s="93" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A249" s="48">
         <v>5</v>
       </c>
@@ -7257,10 +8008,13 @@
         <v>599</v>
       </c>
       <c r="D249" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E249" s="93" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A250" s="48">
         <v>5</v>
       </c>
@@ -7268,13 +8022,16 @@
         <v>664</v>
       </c>
       <c r="C250" s="95" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="D250" s="95" t="s">
+        <v>921</v>
+      </c>
+      <c r="E250" s="95" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A251" s="48">
         <v>5</v>
       </c>
@@ -7282,13 +8039,16 @@
         <v>605</v>
       </c>
       <c r="C251" s="93" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="D251" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E251" s="93" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="252" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A252" s="48">
         <v>5</v>
       </c>
@@ -7296,27 +8056,33 @@
         <v>666</v>
       </c>
       <c r="C252" s="95" t="s">
-        <v>896</v>
-      </c>
-      <c r="D252" s="93" t="s">
+        <v>893</v>
+      </c>
+      <c r="D252" s="95" t="s">
+        <v>922</v>
+      </c>
+      <c r="E252" s="93" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A253" s="48">
         <v>5</v>
       </c>
       <c r="B253" s="93" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="C253" s="93" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="D253" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E253" s="93" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="254" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A254" s="48">
         <v>5</v>
       </c>
@@ -7324,27 +8090,33 @@
         <v>607</v>
       </c>
       <c r="C254" s="93" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="D254" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E254" s="93" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="255" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A255" s="48">
         <v>5</v>
       </c>
-      <c r="B255" s="93" t="s">
-        <v>601</v>
-      </c>
-      <c r="C255" s="93" t="s">
-        <v>601</v>
+      <c r="B255" t="s">
+        <v>784</v>
+      </c>
+      <c r="C255" t="s">
+        <v>899</v>
       </c>
       <c r="D255" s="93" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>921</v>
+      </c>
+      <c r="E255" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A256" s="48">
         <v>5</v>
       </c>
@@ -7355,10 +8127,13 @@
         <v>603</v>
       </c>
       <c r="D256" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E256" s="93" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="257" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A257" s="48">
         <v>5</v>
       </c>
@@ -7369,10 +8144,13 @@
         <v>611</v>
       </c>
       <c r="D257" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E257" s="93" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="258" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A258" s="48">
         <v>5</v>
       </c>
@@ -7382,11 +8160,14 @@
       <c r="C258" s="95" t="s">
         <v>661</v>
       </c>
-      <c r="D258" s="93" t="s">
+      <c r="D258" s="95" t="s">
+        <v>921</v>
+      </c>
+      <c r="E258" s="93" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="259" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A259" s="48">
         <v>5</v>
       </c>
@@ -7397,10 +8178,13 @@
         <v>614</v>
       </c>
       <c r="D259" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E259" s="93" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="260" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A260" s="48">
         <v>5</v>
       </c>
@@ -7411,10 +8195,13 @@
         <v>620</v>
       </c>
       <c r="D260" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E260" s="93" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="261" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A261" s="48">
         <v>5</v>
       </c>
@@ -7424,11 +8211,14 @@
       <c r="C261" s="93" t="s">
         <v>622</v>
       </c>
-      <c r="D261" s="94" t="s">
+      <c r="D261" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E261" s="94" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="262" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A262" s="48">
         <v>5</v>
       </c>
@@ -7436,13 +8226,16 @@
         <v>624</v>
       </c>
       <c r="C262" s="95" t="s">
-        <v>898</v>
-      </c>
-      <c r="D262" s="93" t="s">
+        <v>895</v>
+      </c>
+      <c r="D262" s="95" t="s">
+        <v>922</v>
+      </c>
+      <c r="E262" s="93" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A263" s="48">
         <v>5</v>
       </c>
@@ -7450,13 +8243,16 @@
         <v>626</v>
       </c>
       <c r="C263" s="93" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="D263" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E263" s="93" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A264" s="48">
         <v>5</v>
       </c>
@@ -7467,10 +8263,13 @@
         <v>628</v>
       </c>
       <c r="D264" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E264" s="93" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="265" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A265" s="48">
         <v>5</v>
       </c>
@@ -7481,10 +8280,13 @@
         <v>616</v>
       </c>
       <c r="D265" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E265" s="93" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="266" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A266" s="48">
         <v>5</v>
       </c>
@@ -7492,13 +8294,16 @@
         <v>630</v>
       </c>
       <c r="C266" s="93" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="D266" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E266" s="93" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="267" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A267" s="48">
         <v>5</v>
       </c>
@@ -7509,150 +8314,183 @@
         <v>632</v>
       </c>
       <c r="D267" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E267" s="93" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="268" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A268" s="48">
         <v>5</v>
       </c>
-      <c r="B268" s="93" t="s">
-        <v>634</v>
-      </c>
-      <c r="C268" s="93" t="s">
-        <v>634</v>
-      </c>
-      <c r="D268" s="93" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B268" s="95" t="s">
+        <v>643</v>
+      </c>
+      <c r="C268" s="95" t="s">
+        <v>643</v>
+      </c>
+      <c r="D268" s="95" t="s">
+        <v>921</v>
+      </c>
+      <c r="E268" s="93" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A269" s="48">
         <v>5</v>
       </c>
       <c r="B269" s="93" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C269" s="93" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D269" s="93" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>922</v>
+      </c>
+      <c r="E269" s="93" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A270" s="48">
         <v>5</v>
       </c>
-      <c r="B270" s="95" t="s">
-        <v>709</v>
-      </c>
-      <c r="C270" s="95" t="s">
-        <v>709</v>
+      <c r="B270" s="93" t="s">
+        <v>636</v>
+      </c>
+      <c r="C270" s="93" t="s">
+        <v>636</v>
       </c>
       <c r="D270" s="93" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>922</v>
+      </c>
+      <c r="E270" s="93" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A271" s="48">
         <v>5</v>
       </c>
       <c r="B271" s="95" t="s">
-        <v>763</v>
+        <v>709</v>
       </c>
       <c r="C271" s="95" t="s">
-        <v>763</v>
-      </c>
-      <c r="D271" s="93" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>709</v>
+      </c>
+      <c r="D271" s="95" t="s">
+        <v>922</v>
+      </c>
+      <c r="E271" s="93" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A272" s="48">
         <v>5</v>
       </c>
-      <c r="B272" s="95" t="s">
-        <v>641</v>
-      </c>
-      <c r="C272" s="95" t="s">
-        <v>641</v>
+      <c r="B272" s="93" t="s">
+        <v>650</v>
+      </c>
+      <c r="C272" s="93" t="s">
+        <v>650</v>
       </c>
       <c r="D272" s="93" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>922</v>
+      </c>
+      <c r="E272" s="93" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A273" s="48">
         <v>5</v>
       </c>
       <c r="B273" s="95" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C273" s="95" t="s">
-        <v>643</v>
-      </c>
-      <c r="D273" s="93" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>640</v>
+      </c>
+      <c r="D273" s="95" t="s">
+        <v>922</v>
+      </c>
+      <c r="E273" s="93" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A274" s="48">
         <v>5</v>
       </c>
       <c r="B274" s="95" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="C274" s="95" t="s">
-        <v>646</v>
-      </c>
-      <c r="D274" s="93" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>641</v>
+      </c>
+      <c r="D274" s="95" t="s">
+        <v>922</v>
+      </c>
+      <c r="E274" s="93" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A275" s="48">
         <v>5</v>
       </c>
       <c r="B275" s="95" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C275" s="95" t="s">
-        <v>648</v>
-      </c>
-      <c r="D275" s="93" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>646</v>
+      </c>
+      <c r="D275" s="95" t="s">
+        <v>922</v>
+      </c>
+      <c r="E275" s="93" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A276" s="48">
         <v>5</v>
       </c>
       <c r="B276" s="95" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="C276" s="95" t="s">
-        <v>901</v>
-      </c>
-      <c r="D276" s="93" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>648</v>
+      </c>
+      <c r="D276" s="95" t="s">
+        <v>922</v>
+      </c>
+      <c r="E276" s="93" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A277" s="48">
         <v>5</v>
       </c>
-      <c r="B277" s="93" t="s">
-        <v>650</v>
-      </c>
-      <c r="C277" s="93" t="s">
-        <v>650</v>
-      </c>
-      <c r="D277" s="93" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B277" s="95" t="s">
+        <v>654</v>
+      </c>
+      <c r="C277" s="95" t="s">
+        <v>898</v>
+      </c>
+      <c r="D277" s="95" t="s">
+        <v>922</v>
+      </c>
+      <c r="E277" s="93" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A278" s="48">
         <v>5</v>
       </c>
@@ -7662,11 +8500,14 @@
       <c r="C278" s="95" t="s">
         <v>652</v>
       </c>
-      <c r="D278" s="93" t="s">
+      <c r="D278" s="95" t="s">
+        <v>922</v>
+      </c>
+      <c r="E278" s="93" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="279" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A279" s="48">
         <v>5</v>
       </c>
@@ -7677,52 +8518,64 @@
         <v>656</v>
       </c>
       <c r="D279" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E279" s="93" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="280" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A280" s="48">
         <v>5</v>
       </c>
-      <c r="B280" s="95" t="s">
-        <v>618</v>
-      </c>
-      <c r="C280" s="95" t="s">
-        <v>618</v>
+      <c r="B280" s="93" t="s">
+        <v>601</v>
+      </c>
+      <c r="C280" s="93" t="s">
+        <v>601</v>
       </c>
       <c r="D280" s="93" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>921</v>
+      </c>
+      <c r="E280" s="93" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A281" s="48">
         <v>5</v>
       </c>
       <c r="B281" s="95" t="s">
-        <v>638</v>
+        <v>618</v>
       </c>
       <c r="C281" s="95" t="s">
-        <v>638</v>
-      </c>
-      <c r="D281" s="93" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>618</v>
+      </c>
+      <c r="D281" s="95" t="s">
+        <v>921</v>
+      </c>
+      <c r="E281" s="93" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A282" s="48">
         <v>5</v>
       </c>
-      <c r="B282" t="s">
-        <v>787</v>
-      </c>
-      <c r="C282" t="s">
-        <v>902</v>
-      </c>
-      <c r="D282" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B282" s="95" t="s">
+        <v>638</v>
+      </c>
+      <c r="C282" s="95" t="s">
+        <v>638</v>
+      </c>
+      <c r="D282" s="95" t="s">
+        <v>921</v>
+      </c>
+      <c r="E282" s="93" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A283" s="48">
         <v>5</v>
       </c>
@@ -7730,13 +8583,16 @@
         <v>659</v>
       </c>
       <c r="C283" s="93" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="D283" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E283" s="93" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="284" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A284" s="48">
         <v>5</v>
       </c>
@@ -7744,13 +8600,16 @@
         <v>662</v>
       </c>
       <c r="C284" s="93" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="D284" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E284" s="93" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="285" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A285" s="48">
         <v>5</v>
       </c>
@@ -7758,13 +8617,16 @@
         <v>722</v>
       </c>
       <c r="C285" t="s">
-        <v>905</v>
-      </c>
-      <c r="D285" t="s">
+        <v>902</v>
+      </c>
+      <c r="D285" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E285" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="286" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A286" s="48">
         <v>5</v>
       </c>
@@ -7772,13 +8634,16 @@
         <v>667</v>
       </c>
       <c r="C286" s="93" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="D286" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E286" s="93" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="287" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A287" s="48">
         <v>5</v>
       </c>
@@ -7786,13 +8651,16 @@
         <v>669</v>
       </c>
       <c r="C287" s="93" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="D287" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E287" s="93" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="288" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A288" s="48">
         <v>5</v>
       </c>
@@ -7800,13 +8668,16 @@
         <v>671</v>
       </c>
       <c r="C288" s="93" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="D288" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E288" s="93" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="289" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A289" s="48">
         <v>5</v>
       </c>
@@ -7817,10 +8688,13 @@
         <v>673</v>
       </c>
       <c r="D289" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E289" s="93" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="290" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A290" s="48">
         <v>5</v>
       </c>
@@ -7831,10 +8705,13 @@
         <v>675</v>
       </c>
       <c r="D290" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E290" s="93" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="291" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A291" s="48">
         <v>5</v>
       </c>
@@ -7845,10 +8722,13 @@
         <v>677</v>
       </c>
       <c r="D291" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E291" s="93" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="292" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A292" s="48">
         <v>5</v>
       </c>
@@ -7856,13 +8736,16 @@
         <v>679</v>
       </c>
       <c r="C292" s="93" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="D292" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E292" s="93" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="293" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A293" s="48">
         <v>5</v>
       </c>
@@ -7870,13 +8753,16 @@
         <v>681</v>
       </c>
       <c r="C293" s="93" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="D293" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E293" s="93" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="294" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A294" s="48">
         <v>5</v>
       </c>
@@ -7887,10 +8773,13 @@
         <v>683</v>
       </c>
       <c r="D294" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E294" s="93" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="295" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A295" s="48">
         <v>5</v>
       </c>
@@ -7901,10 +8790,13 @@
         <v>707</v>
       </c>
       <c r="D295" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E295" s="93" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="296" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A296" s="48">
         <v>5</v>
       </c>
@@ -7912,13 +8804,16 @@
         <v>685</v>
       </c>
       <c r="C296" s="93" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D296" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E296" s="93" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="297" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A297" s="48">
         <v>5</v>
       </c>
@@ -7929,10 +8824,13 @@
         <v>687</v>
       </c>
       <c r="D297" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E297" s="93" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="298" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A298" s="48">
         <v>5</v>
       </c>
@@ -7940,13 +8838,16 @@
         <v>689</v>
       </c>
       <c r="C298" s="93" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="D298" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E298" s="93" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="299" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A299" s="48">
         <v>5</v>
       </c>
@@ -7954,13 +8855,16 @@
         <v>691</v>
       </c>
       <c r="C299" s="93" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="D299" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E299" s="93" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="300" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A300" s="48">
         <v>5</v>
       </c>
@@ -7968,13 +8872,16 @@
         <v>693</v>
       </c>
       <c r="C300" s="93" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="D300" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E300" s="93" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A301" s="48">
         <v>5</v>
       </c>
@@ -7985,10 +8892,13 @@
         <v>695</v>
       </c>
       <c r="D301" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E301" s="93" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="302" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A302" s="48">
         <v>5</v>
       </c>
@@ -7999,10 +8909,13 @@
         <v>697</v>
       </c>
       <c r="D302" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E302" s="93" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="303" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A303" s="48">
         <v>5</v>
       </c>
@@ -8013,10 +8926,13 @@
         <v>699</v>
       </c>
       <c r="D303" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E303" s="93" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="304" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A304" s="48">
         <v>5</v>
       </c>
@@ -8027,10 +8943,13 @@
         <v>701</v>
       </c>
       <c r="D304" s="93" t="s">
+        <v>921</v>
+      </c>
+      <c r="E304" s="93" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="305" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A305" s="48">
         <v>5</v>
       </c>
@@ -8041,10 +8960,13 @@
         <v>703</v>
       </c>
       <c r="D305" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E305" s="93" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="306" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A306" s="48">
         <v>5</v>
       </c>
@@ -8052,13 +8974,16 @@
         <v>705</v>
       </c>
       <c r="C306" s="93" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="D306" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E306" s="93" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="307" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A307" s="104">
         <v>5</v>
       </c>
@@ -8068,140 +8993,170 @@
       <c r="C307" t="s">
         <v>761</v>
       </c>
-      <c r="D307" t="s">
+      <c r="D307" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E307" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="308" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A308" s="104">
         <v>5</v>
       </c>
       <c r="B308" s="49" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C308" s="49" t="s">
-        <v>765</v>
-      </c>
-      <c r="D308" s="50" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>763</v>
+      </c>
+      <c r="D308" s="49" t="s">
+        <v>921</v>
+      </c>
+      <c r="E308" s="50" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A309" s="104">
         <v>5</v>
       </c>
       <c r="B309" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="C309" t="s">
-        <v>916</v>
-      </c>
-      <c r="D309" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="310" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>913</v>
+      </c>
+      <c r="D309" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E309" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A310" s="104">
         <v>5</v>
       </c>
       <c r="B310" s="49" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C310" s="49" t="s">
-        <v>771</v>
-      </c>
-      <c r="D310" s="50" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>768</v>
+      </c>
+      <c r="D310" s="49" t="s">
+        <v>921</v>
+      </c>
+      <c r="E310" s="50" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A311" s="104">
         <v>5</v>
       </c>
       <c r="B311" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C311" t="s">
-        <v>917</v>
-      </c>
-      <c r="D311" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>914</v>
+      </c>
+      <c r="D311" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E311" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A312" s="104">
         <v>5</v>
       </c>
       <c r="B312" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="C312" t="s">
-        <v>918</v>
-      </c>
-      <c r="D312" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>915</v>
+      </c>
+      <c r="D312" s="49" t="s">
+        <v>921</v>
+      </c>
+      <c r="E312" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A313" s="104">
         <v>5</v>
       </c>
       <c r="B313" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C313" t="s">
-        <v>779</v>
-      </c>
-      <c r="D313" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="314" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>776</v>
+      </c>
+      <c r="D313" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E313" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A314" s="104">
         <v>5</v>
       </c>
       <c r="B314" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="C314" t="s">
-        <v>919</v>
-      </c>
-      <c r="D314" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="315" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>916</v>
+      </c>
+      <c r="D314" s="49" t="s">
+        <v>921</v>
+      </c>
+      <c r="E314" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A315" s="104">
         <v>5</v>
       </c>
       <c r="B315" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C315" t="s">
-        <v>920</v>
-      </c>
-      <c r="D315" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="316" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>917</v>
+      </c>
+      <c r="D315" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="E315" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A316" s="104">
         <v>5</v>
       </c>
       <c r="B316" s="49" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C316" s="49" t="s">
-        <v>785</v>
-      </c>
-      <c r="D316" s="50" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="318" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="319" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="320" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+        <v>782</v>
+      </c>
+      <c r="D316" s="49" t="s">
+        <v>921</v>
+      </c>
+      <c r="E316" s="50" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="318" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="319" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="320" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -8891,11 +9846,11 @@
     <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <conditionalFormatting sqref="B182:C215 B217:C238">
+  <conditionalFormatting sqref="B182:D215 B217:D238 D239:D247">
     <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D248:D281">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="E256:E282 E248:E254">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10164,7 +11119,7 @@
         <v>658</v>
       </c>
       <c r="C42" s="51" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -15414,7 +16369,7 @@
         <v>24</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -15504,7 +16459,7 @@
         <v>13</v>
       </c>
       <c r="D57" s="51" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
@@ -15522,7 +16477,7 @@
         <v>15</v>
       </c>
       <c r="D58" s="51" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
@@ -15594,7 +16549,7 @@
         <v>21</v>
       </c>
       <c r="D62" s="51" t="s">
-        <v>768</v>
+        <v>924</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
@@ -15612,7 +16567,7 @@
         <v>21</v>
       </c>
       <c r="D63" s="51" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
@@ -15630,7 +16585,7 @@
         <v>24</v>
       </c>
       <c r="D64" s="51" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
